--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -38,7 +38,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,6 +95,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -474,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Built 2026-10-06 from every article in content/guides and content/fun-facts. Nothing on the site has been changed. Every number is a counted value, not a formula.</t>
+          <t>Built 2026-10-06 from every article in content/guides and content/fun-facts. Nothing on the site has been changed. Every number is a counted value, not a formula. The 55 legal guides are set aside for later (owner, 2026-10-06), so every count below except Articles checked leaves them out.</t>
         </is>
       </c>
     </row>
@@ -507,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>424</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7">
@@ -517,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
@@ -557,7 +565,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -567,7 +575,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -577,7 +585,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +595,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +605,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +645,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -650,11 +658,22 @@
         <v>4</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>Rules applied (owner, 2026-10-05): combine several pages from one site into one entry naming the pages; drop a source whose every claim another listed source covers; keep 3 to 5; separate laws and separate studies stay separate, with the reason stated; common keeper knowledge may stand unsourced; never cite the site itself.</t>
         </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Legal guides set aside for later (owner, 2026-10-06)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1842,9 +1861,9 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr"/>
@@ -2381,9 +2400,9 @@
           <t>Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr"/>
@@ -3556,9 +3575,9 @@
           <t>Combine myfwc.com into one entry linking the site and naming the pages: Florida Fish and Wildlife Conservation Commission: Prohibited Species List; Florida Fish and Wildlife Conservation Commission: Argentine Black and White Tegu; Florida Fish and Wildlife Conservation Commission: Proposed Rule Change, 2025.</t>
         </is>
       </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr"/>
@@ -3950,9 +3969,9 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr"/>
@@ -4223,9 +4242,9 @@
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr"/>
@@ -4758,9 +4777,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J101" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr"/>
@@ -5004,9 +5023,9 @@
           <t>Keep animallaw.info entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J107" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr"/>
@@ -6195,9 +6214,9 @@
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr"/>
-      <c r="J136" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J136" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr"/>
@@ -6496,9 +6515,9 @@
           <t>Combine law.cornell.edu into one entry naming the pages unless each backs a distinct rule or listing. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J143" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J143" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr"/>
@@ -6859,9 +6878,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J152" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J152" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr"/>
@@ -7549,9 +7568,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J170" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J170" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr"/>
@@ -8060,9 +8079,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J183" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J183" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr"/>
@@ -9161,9 +9180,9 @@
           <t>Keep animallaw.info entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J210" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J210" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K210" s="5" t="inlineStr"/>
@@ -9848,9 +9867,9 @@
       <c r="G227" s="5" t="inlineStr"/>
       <c r="H227" s="5" t="inlineStr"/>
       <c r="I227" s="5" t="inlineStr"/>
-      <c r="J227" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J227" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K227" s="5" t="inlineStr"/>
@@ -9973,9 +9992,9 @@
           <t>Combine zoek.officielebekendmakingen.nl into one entry linking the site and naming the pages: the folded-ear and hairless cat measure, with the explanatory note; the Dutch policy rule on brachycephalic dogs. Combine animallaw.info into one entry naming the pages unless each backs a distinct rule or listing. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J230" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J230" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K230" s="5" t="inlineStr"/>
@@ -10519,9 +10538,9 @@
           <t>Keep dep.nj.gov entries separate, reason stated. Keep ilga.gov entries separate, reason stated. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J244" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J244" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K244" s="5" t="inlineStr"/>
@@ -11124,9 +11143,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J259" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J259" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K259" s="5" t="inlineStr"/>
@@ -11537,9 +11556,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J270" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J270" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K270" s="5" t="inlineStr"/>
@@ -12286,9 +12305,9 @@
       <c r="G289" s="5" t="inlineStr"/>
       <c r="H289" s="5" t="inlineStr"/>
       <c r="I289" s="5" t="inlineStr"/>
-      <c r="J289" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J289" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K289" s="5" t="inlineStr"/>
@@ -12403,9 +12422,9 @@
           <t>Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing. Combining brings it from 6 to 4, inside 3 to 5.</t>
         </is>
       </c>
-      <c r="J292" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J292" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K292" s="5" t="inlineStr"/>
@@ -12450,9 +12469,9 @@
           <t>Keep law.cornell.edu entries separate, reason stated. Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J293" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J293" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr"/>
@@ -12544,9 +12563,9 @@
           <t>Keep animallaw.info entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J295" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J295" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K295" s="5" t="inlineStr"/>
@@ -12809,9 +12828,9 @@
       <c r="G302" s="5" t="inlineStr"/>
       <c r="H302" s="5" t="inlineStr"/>
       <c r="I302" s="5" t="inlineStr"/>
-      <c r="J302" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J302" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr"/>
@@ -13608,9 +13627,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J323" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J323" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K323" s="5" t="inlineStr"/>
@@ -14381,9 +14400,9 @@
           <t>Keep law.cornell.edu entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J342" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J342" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K342" s="5" t="inlineStr"/>
@@ -14658,9 +14677,9 @@
           <t>Keep dab.hawaii.gov entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J349" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J349" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr"/>
@@ -15290,9 +15309,9 @@
           <t>Combine aphis.usda.gov into one entry naming the pages unless each backs a distinct rule or listing. Combining brings it from 6 to 5, inside 3 to 5.</t>
         </is>
       </c>
-      <c r="J365" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J365" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K365" s="5" t="inlineStr"/>
@@ -15957,9 +15976,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J382" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J382" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K382" s="5" t="inlineStr"/>
@@ -16258,9 +16277,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J389" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J389" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K389" s="5" t="inlineStr"/>
@@ -16617,9 +16636,9 @@
           <t>Combine dab.hawaii.gov into one entry naming the pages unless each backs a distinct rule or listing. Combining brings it from 7 to 5, inside 3 to 5.</t>
         </is>
       </c>
-      <c r="J398" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J398" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K398" s="5" t="inlineStr"/>
@@ -17249,9 +17268,9 @@
       <c r="G414" s="5" t="inlineStr"/>
       <c r="H414" s="5" t="inlineStr"/>
       <c r="I414" s="5" t="inlineStr"/>
-      <c r="J414" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J414" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K414" s="5" t="inlineStr"/>
@@ -17588,9 +17607,9 @@
       <c r="G423" s="5" t="inlineStr"/>
       <c r="H423" s="5" t="inlineStr"/>
       <c r="I423" s="5" t="inlineStr"/>
-      <c r="J423" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J423" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K423" s="5" t="inlineStr"/>
@@ -18224,9 +18243,9 @@
           <t>Keep admincode.legislature.state.al.us entries separate, reason stated. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J439" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J439" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K439" s="5" t="inlineStr"/>
@@ -19162,9 +19181,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J461" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J461" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr"/>
@@ -19521,9 +19540,9 @@
       <c r="G470" s="5" t="inlineStr"/>
       <c r="H470" s="5" t="inlineStr"/>
       <c r="I470" s="5" t="inlineStr"/>
-      <c r="J470" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J470" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K470" s="5" t="inlineStr"/>
@@ -20415,9 +20434,9 @@
           <t>Keep dab.hawaii.gov entries separate, reason stated. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J492" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J492" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr"/>
@@ -21125,9 +21144,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J510" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J510" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K510" s="5" t="inlineStr"/>
@@ -21492,9 +21511,9 @@
           <t>Combine wildlife.utah.gov into one entry naming the pages unless each backs a distinct rule or listing. Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J519" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J519" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K519" s="5" t="inlineStr"/>
@@ -22667,9 +22686,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J548" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J548" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K548" s="5" t="inlineStr"/>
@@ -24065,9 +24084,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J582" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J582" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K582" s="5" t="inlineStr"/>
@@ -24564,9 +24583,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J595" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J595" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K595" s="5" t="inlineStr"/>
@@ -24915,9 +24934,9 @@
       <c r="G604" s="5" t="inlineStr"/>
       <c r="H604" s="5" t="inlineStr"/>
       <c r="I604" s="5" t="inlineStr"/>
-      <c r="J604" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J604" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K604" s="5" t="inlineStr"/>
@@ -25489,9 +25508,9 @@
       <c r="G618" s="5" t="inlineStr"/>
       <c r="H618" s="5" t="inlineStr"/>
       <c r="I618" s="5" t="inlineStr"/>
-      <c r="J618" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J618" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K618" s="5" t="inlineStr"/>
@@ -25805,9 +25824,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J626" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J626" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K626" s="5" t="inlineStr"/>
@@ -26402,9 +26421,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J641" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J641" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K641" s="5" t="inlineStr"/>
@@ -26679,9 +26698,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J648" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J648" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K648" s="5" t="inlineStr"/>
@@ -26932,9 +26951,9 @@
       <c r="G655" s="5" t="inlineStr"/>
       <c r="H655" s="5" t="inlineStr"/>
       <c r="I655" s="5" t="inlineStr"/>
-      <c r="J655" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J655" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K655" s="5" t="inlineStr"/>
@@ -27139,9 +27158,9 @@
           <t>Keep animallaw.info entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J660" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J660" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K660" s="5" t="inlineStr"/>
@@ -27670,9 +27689,9 @@
           <t>Keep the state law entries, reason stated; trim only the non-legal entries another source already covers.</t>
         </is>
       </c>
-      <c r="J673" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J673" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K673" s="5" t="inlineStr"/>
@@ -28212,9 +28231,9 @@
       <c r="G687" s="5" t="inlineStr"/>
       <c r="H687" s="5" t="inlineStr"/>
       <c r="I687" s="5" t="inlineStr"/>
-      <c r="J687" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J687" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K687" s="5" t="inlineStr"/>
@@ -28508,9 +28527,9 @@
       <c r="G695" s="5" t="inlineStr"/>
       <c r="H695" s="5" t="inlineStr"/>
       <c r="I695" s="5" t="inlineStr"/>
-      <c r="J695" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J695" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K695" s="5" t="inlineStr"/>
@@ -29085,9 +29104,9 @@
       <c r="G710" s="5" t="inlineStr"/>
       <c r="H710" s="5" t="inlineStr"/>
       <c r="I710" s="5" t="inlineStr"/>
-      <c r="J710" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J710" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K710" s="5" t="inlineStr"/>
@@ -29612,9 +29631,9 @@
           <t>Keep dep.nj.gov entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J723" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J723" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K723" s="5" t="inlineStr"/>
@@ -29920,9 +29939,9 @@
       <c r="G731" s="5" t="inlineStr"/>
       <c r="H731" s="5" t="inlineStr"/>
       <c r="I731" s="5" t="inlineStr"/>
-      <c r="J731" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J731" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K731" s="5" t="inlineStr"/>
@@ -30783,9 +30802,9 @@
       <c r="G752" s="5" t="inlineStr"/>
       <c r="H752" s="5" t="inlineStr"/>
       <c r="I752" s="5" t="inlineStr"/>
-      <c r="J752" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J752" s="8" t="inlineStr">
+        <is>
+          <t>Later (legal)</t>
         </is>
       </c>
       <c r="K752" s="5" t="inlineStr"/>

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -38,7 +38,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -78,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +103,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -658,7 +666,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -9230,7 +9237,7 @@
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>FIX_PLAN: the 50 to 68F comfort band; Merck (65 to 80F) and PetMD (55 to 70F) run warmer. Settle one band with sources.</t>
+          <t>FIX_PLAN: the 50 to 68F comfort band; Merck (65 to 80F) and PetMD (55 to 70F) run warmer. Settle one band with sources. 2026-10-06: sources disagree. VCA (listed on the heat stress guide) 50 to 68F; PetMD 55 to 70F, never over 80; LafeberVet 59 to 70F; Merck 65 to 80F adapted range. The setup guide lists PetMD, LafeberVet and Merck but not VCA. Owner call.</t>
         </is>
       </c>
     </row>
@@ -13019,14 +13026,14 @@
       <c r="G307" s="5" t="inlineStr"/>
       <c r="H307" s="5" t="inlineStr"/>
       <c r="I307" s="5" t="inlineStr"/>
-      <c r="J307" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J307" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K307" s="5" t="inlineStr">
         <is>
-          <t>FIX_PLAN: no listed source for the skin toxin harming tankmates of other species, or the small net as a handling option.</t>
+          <t>FIX_PLAN: no listed source for the skin toxin harming tankmates of other species, or the small net as a handling option. 2026-10-06: tankmate line tied to Smithsonian; net option removed.</t>
         </is>
       </c>
     </row>
@@ -16905,14 +16912,14 @@
       <c r="G405" s="5" t="inlineStr"/>
       <c r="H405" s="5" t="inlineStr"/>
       <c r="I405" s="5" t="inlineStr"/>
-      <c r="J405" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J405" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K405" s="5" t="inlineStr">
         <is>
-          <t>FIX_PLAN: Tankarium is still listed and says guppies are not salt tolerant, against the page. Swap it for Chervinski 1984 (Journal of Fish Biology) or trim it.</t>
+          <t>FIX_PLAN: Tankarium is still listed and says guppies are not salt tolerant, against the page. Swap it for Chervinski 1984 (Journal of Fish Biology) or trim it. 2026-10-06: Tankarium replaced by Merck; Chervinski 1984 added. 4 sources.</t>
         </is>
       </c>
     </row>
@@ -21640,12 +21647,16 @@
           <t>Delete the duplicate entry. Combine aquariumcoop.com into one entry linking the site and naming the pages: Molly Fish Care Guide; Care Guide for Mollies.</t>
         </is>
       </c>
-      <c r="J522" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K522" s="5" t="inlineStr"/>
+      <c r="J522" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K522" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: duplicate Aquarium Co-Op entry removed; 3 sources.</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="5" t="inlineStr">
@@ -30970,12 +30981,16 @@
           <t>Replace each placeholder with the real page it names, or remove it; never leave a link to the site itself.</t>
         </is>
       </c>
-      <c r="J756" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K756" s="5" t="inlineStr"/>
+      <c r="J756" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K756" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: placeholders replaced with the real pages: VCA (stressed dog signs, fears and anxiety, kitten hiding) in one entry, AVMA JAVMA News Back-to-Work Pet Anxiety, and ACVB What Is a Veterinary Behaviorist. Coal Creek dropped (no page found that the article needs). Cat stress signs reworded to what VCA says: dilated pupils, flat ears, hunched posture.</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="5" t="inlineStr">
@@ -31110,14 +31125,14 @@
       <c r="G760" s="5" t="inlineStr"/>
       <c r="H760" s="5" t="inlineStr"/>
       <c r="I760" s="5" t="inlineStr"/>
-      <c r="J760" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J760" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K760" s="5" t="inlineStr">
         <is>
-          <t>FIX_PLAN: no listed source for 5 to 15 minute sessions about twice a week, larger and hardier than American green tree frogs, or skin breathing. Source or soften during the sweep.</t>
+          <t>FIX_PLAN: no listed source for 5 to 15 minute sessions about twice a week, larger and hardier than American green tree frogs, or skin breathing. Source or soften during the sweep. 2026-10-06: unsourced claims rewritten to the listed sources (see FIX_PLAN archive).</t>
         </is>
       </c>
     </row>

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -9237,7 +9237,7 @@
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>FIX_PLAN: the 50 to 68F comfort band; Merck (65 to 80F) and PetMD (55 to 70F) run warmer. Settle one band with sources. 2026-10-06: sources disagree. VCA (listed on the heat stress guide) 50 to 68F; PetMD 55 to 70F, never over 80; LafeberVet 59 to 70F; Merck 65 to 80F adapted range. The setup guide lists PetMD, LafeberVet and Merck but not VCA. Owner call.</t>
+          <t>FIX_PLAN: the 50 to 68F comfort band; Merck (65 to 80F) and PetMD (55 to 70F) run warmer. Settle one band with sources. 2026-10-06: sources disagree. VCA (listed on the heat stress guide) 50 to 68F; PetMD 55 to 70F, never over 80; LafeberVet 59 to 70F; Merck 65 to 80F adapted range. The setup guide lists PetMD, LafeberVet and Merck but not VCA. Owner call. Settled 2026-10-06 (owner): 55 to 70F everywhere.</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K668" s="5" t="inlineStr"/>
+      <c r="K668" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: PetMD chinchilla care sheet added for the settled 55 to 70F band (11 sources; trim in step 5).</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="5" t="inlineStr">

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Built 2026-10-06 from every article in content/guides and content/fun-facts. Nothing on the site has been changed. Every number is a counted value, not a formula. The 55 legal guides are set aside for later (owner, 2026-10-06), so every count below except Articles checked leaves them out.</t>
+          <t>Built 2026-10-06 from every article in content/guides and content/fun-facts; updated after each fix batch. Every number is a counted value, not a formula. The 55 legal guides are set aside for later (owner, 2026-10-06), so every count below except Articles checked leaves them out. Finding counts cover rows still marked Review.</t>
         </is>
       </c>
     </row>
@@ -523,113 +523,113 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>387</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Look fine as they are</t>
+          <t>Fixed so far</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>No Sources block</t>
+          <t>Look fine as they are</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Under 3 sources</t>
+          <t>No Sources block</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Same site listed 2+ times</t>
+          <t>Under 3 sources</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>290</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of those, a site to combine</t>
+          <t>Same site listed 2+ times</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>209</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of those, kept with a reason (laws, studies, agencies)</t>
+          <t xml:space="preserve">  of those, a site to combine</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Over 5 even after combining</t>
+          <t xml:space="preserve">  of those, kept with a reason (laws, studies, agencies)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of those, legal guides (state laws expected)</t>
+          <t>Over 5 even after combining</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Combining alone brings it inside 3 to 5</t>
+          <t xml:space="preserve">  of those, legal guides (state laws expected)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Duplicate URL</t>
+          <t>Combining alone brings it inside 3 to 5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Self-citation</t>
+          <t>Duplicate URL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -639,47 +639,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Placeholder links to the BeastlyFacts homepage</t>
+          <t>Self-citation</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Placeholder links to the BeastlyFacts homepage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Has an Also consulted list</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Unsourced claims carried over from FIX_PLAN</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Rules applied (owner, 2026-10-05): combine several pages from one site into one entry naming the pages; drop a source whose every claim another listed source covers; keep 3 to 5; separate laws and separate studies stay separate, with the reason stated; common keeper knowledge may stand unsourced; never cite the site itself.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Rules applied (owner, 2026-10-05): combine several pages from one site into one entry naming the pages; drop a source whose every claim another listed source covers; keep 3 to 5; separate laws and separate studies stay separate, with the reason stated; common keeper knowledge may stand unsourced; never cite the site itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Legal guides set aside for later (owner, 2026-10-06)</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1666,7 +1677,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>2</v>
@@ -1676,13 +1687,13 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Ackie Monitor Care; ReptiFiles: Where to Buy an Ackie Monitor; ReptiFiles: Ackie Monitor Parasites</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Ackie Monitor Care; Where to Buy an Ackie Monitor; Ackie Monitor Parasites.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -1690,7 +1701,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1814,7 +1829,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>1</v>
@@ -1824,13 +1839,13 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 6 times: ReptiFiles: Ackie Monitor Metabolic Bone Disease; ReptiFiles: Ackie Monitor Obesity; ReptiFiles: Ackie Monitor Parasites; ReptiFiles: Respiratory Infection in Ackie Monitors; ReptiFiles: Egg Cycling in Ackie Monitors; ReptiFiles: Egg Binding in Ackie Monitors</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
+          <t>Only 1 source.</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Ackie Monitor Metabolic Bone Disease; Ackie Monitor Obesity; Ackie Monitor Parasites; Respiratory Infection in Ackie Monitors; Egg Cycling in Ackie Monitors; Egg Binding in Ackie Monitors. Combining brings it from 6 to 1, inside 3 to 5.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -1838,7 +1853,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1892,7 +1911,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>1</v>
@@ -1902,13 +1921,13 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 6 times: ReptiFiles: Ackie Monitor Enclosure Size Requirements; ReptiFiles: Ackie Monitor UVB Lighting; ReptiFiles: Ackie Monitor Temperatures &amp; Heating; ReptiFiles: Ackie Monitor Humidity Requirements; ReptiFiles: Egg Cycling in Ackie Monitors; ReptiFiles: Ackie Monitor Enclosure Shopping List</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
+          <t>Only 1 source.</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Ackie Monitor Enclosure Size Requirements; Ackie Monitor UVB Lighting; Ackie Monitor Temperatures &amp; Heating; Ackie Monitor Humidity Requirements; Egg Cycling in Ackie Monitors; Ackie Monitor Enclosure Shopping List. Combining brings it from 6 to 1, inside 3 to 5.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
@@ -1916,7 +1935,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2255,7 +2278,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>3</v>
@@ -2263,23 +2286,19 @@
       <c r="F39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Feeding African Grey Parrots; VCA Animal Hospitals: Recognizing the Signs of Illness in Pet Birds</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Feeding African Grey Parrots; Recognizing the Signs of Illness in Pet Birds.</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2298,7 +2317,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>3</v>
@@ -2306,23 +2325,19 @@
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Biting and Screaming in Birds; VCA Animal Hospitals: Taming, Training and Talking to Birds</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Biting and Screaming in Birds; Taming, Training and Talking to Birds.</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2341,7 +2356,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>2</v>
@@ -2351,13 +2366,13 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Common Conditions of Pet Birds; VCA Animal Hospitals: Veterinary Care, New Bird Visit</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Common Conditions of Pet Birds; Veterinary Care, New Bird Visit.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -2365,7 +2380,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2431,7 +2450,7 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>3</v>
@@ -2439,23 +2458,19 @@
       <c r="F43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Overview of Pet Birds (cage size and bar spacing table); Merck Veterinary Manual: Management of Pet Birds; Merck Veterinary Manual: Toxicoses of Pet Birds</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Overview of Pet Birds (cage size and bar spacing table); Management of Pet Birds; Toxicoses of Pet Birds.</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2521,7 +2536,7 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>8</v>
@@ -2531,17 +2546,17 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>wolf.org listed 3 times: Mech (1999), Alpha status, dominance, and division of labor in wolf packs, Canadian Journal of Zoology 77:1196-1203 (PDF, International Wolf Center); Mech, Whatever Happened to the Term Alpha Wolf?, International Wolf, Winter 2008, pages 4-8 (PDF); Mech (2000), Leadership in Wolf, Canis lupus, Packs, Canadian Field-Naturalist 114(2):259-263 (PDF) | davemech.org listed 2 times: Wolf News and Information (Dave Mech's official site, alpha wolf concept and print history of The Wolf); Schenkel's Classic Wolf Behavior Study Available in English (davemech.org) | sciencedirect.com listed 2 times: Ripple et al. (2025), The strength of the Yellowstone trophic cascade after wolf reintroduction, Global Ecology and Conservation 58:e03428; MacNulty et al. (2025), Flawed analysis invalidates claim of a strong Yellowstone trophic cascade after wolf reintroduction: A comment on Ripple et al. (2025), Global Ecology and Conservation 63:e03899 | 11 sources, 8 after combining same-site entries.</t>
+          <t>wolf.org listed 3 times: Mech (1999), Alpha status, dominance, and division of labor in wolf packs, Canadian Journal of Zoology 77:1196-1203 (PDF, International Wolf Center); Mech, Whatever Happened to the Term Alpha Wolf?, International Wolf, Winter 2008, pages 4-8 (PDF); Mech (2000), Leadership in Wolf, Canis lupus, Packs, Canadian Field-Naturalist 114(2):259-263 (PDF) | sciencedirect.com listed 2 times: Ripple et al. (2025), The strength of the Yellowstone trophic cascade after wolf reintroduction, Global Ecology and Conservation 58:e03428; MacNulty et al. (2025), Flawed analysis invalidates claim of a strong Yellowstone trophic cascade after wolf reintroduction: A comment on Ripple et al. (2025), Global Ecology and Conservation 63:e03899 | 10 sources, 8 after combining same-site entries.</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>sciencedirect.com: separate studies, each with its own authors and year; one combined entry could not credit them.</t>
+          <t>Kept separate: separate papers and articles by L. David Mech, each with its own year and journal.</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Combine wolf.org into one entry linking the site and naming the pages: Mech (1999), Alpha status, dominance, and division of labor in wolf packs, Canadian Journal of Zoology 77:1196-1203 (PDF, International Wolf Center); Mech, Whatever Happened to the Term Alpha Wolf?, International Wolf, Winter 2008, pages 4-8 (PDF); Mech (2000), Leadership in Wolf, Canis lupus, Packs, Canadian Field-Naturalist 114(2):259-263 (PDF). Combine davemech.org into one entry linking the site and naming the pages: Wolf News and Information (Dave Mech's official site, alpha wolf concept and print history of The Wolf); Schenkel's Classic Wolf Behavior Study Available in English (davemech.org). Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
@@ -2549,7 +2564,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 11 to 10 entries. 2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2638,7 +2657,7 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>4</v>
@@ -2646,23 +2665,19 @@
       <c r="F48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>shrimpscience.com listed 2 times: Amano Shrimp - Shrimp Science; Molting and Common Problems - Shrimp Science</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Combine shrimpscience.com into one entry linking the site and naming the pages: Amano Shrimp - Shrimp Science; Molting and Common Problems - Shrimp Science.</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2854,18 +2869,26 @@
           <t>vin.com listed 2 times: R. Loh, "Common Disease Conditions in Axolotls," WSAVA 2015 World Congress Proceedings (via VIN); R. Loh, "Water Quality Explained: How It Can Affect Your Axolotl's Health," WSAVA 2015 World Congress Proceedings (via VIN)</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: two separate WSAVA 2015 proceedings papers by R. Loh.</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Combine vin.com into one entry linking the site and naming the pages: R. Loh, "Common Disease Conditions in Axolotls," WSAVA 2015 World Congress Proceedings (via VIN); How It Can Affect Your Axolotl's Health," WSAVA 2015 World Congress Proceedings (via VIN).</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3036,7 +3059,7 @@
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>2</v>
@@ -3046,13 +3069,13 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>aqueon.com listed 2 times: Aqueon: Aquarium Disease Prevention; Aqueon: The Ultimate Guide to Angelfish | merckvetmanual.com listed 2 times: Merck Veterinary Manual: Parasitic Diseases of Fish; Merck Veterinary Manual: Viral Diseases of Fish</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Combine aqueon.com into one entry linking the site and naming the pages: Aquarium Disease Prevention; The Ultimate Guide to Angelfish. Combine merckvetmanual.com into one entry linking the site and naming the pages: Parasitic Diseases of Fish; Viral Diseases of Fish.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -3060,7 +3083,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3114,7 +3141,7 @@
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>3</v>
@@ -3122,23 +3149,19 @@
       <c r="F60" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>practicalfishkeeping.co.uk listed 3 times: How to Cycle a Fish Tank: The Complete Guide - Practical Fishkeeping; Frequently Asked Questions on Ammonia - Practical Fishkeeping; Frequently Asked Questions on Fishless Cycling - Practical Fishkeeping</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>Combine practicalfishkeeping.co.uk into one entry linking the site and naming the pages: The Complete Guide - Practical Fishkeeping; Frequently Asked Questions on Ammonia - Practical Fishkeeping; Frequently Asked Questions on Fishless Cycling - Practical Fishkeeping.</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -3157,7 +3180,7 @@
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>2</v>
@@ -3167,21 +3190,29 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Overview, Types, and Features of Aquatic Systems; Merck Veterinary Manual: Aquatic Life Support System Components; Merck Veterinary Manual: Management of Aquarium Fish | extension.rwfm.tamu.edu listed 2 times: SRAC Publication No. 452: Recirculating Aquaculture Tank Production Systems, Management of Recirculating Systems (Masser, Rakocy, and Losordo, 1999); SRAC Publication No. 4502: How to Start a Biofilter (DeLong and Losordo, NC State University, 2012)</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>extension.rwfm.tamu.edu listed 2 times: SRAC Publication No. 452: Recirculating Aquaculture Tank Production Systems, Management of Recirculating Systems (Masser, Rakocy, and Losordo, 1999); SRAC Publication No. 4502: How to Start a Biofilter (DeLong and Losordo, NC State University, 2012)</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: two separate SRAC publications with different authors and years.</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Overview, Types, and Features of Aquatic Systems; Aquatic Life Support System Components; Management of Aquarium Fish. Combine extension.rwfm.tamu.edu into one entry linking the site and naming the pages: Recirculating Aquaculture Tank Production Systems, Management of Recirculating Systems (Masser, Rakocy, and Losordo, 1999); How to Start a Biofilter (DeLong and Losordo, NC State University, 2012).</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries. 2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -3313,7 +3344,7 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>5</v>
@@ -3321,23 +3352,19 @@
       <c r="F65" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>cafishvet.com listed 2 times: Fish Vet: Old Tank Syndrome (Jessie Sanders, DVM, DABVP Fish Practice); Fish Vet: Dechlorinator for Fish Systems (Jessie Sanders, DVM, DABVP Fish Practice)</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>Combine cafishvet.com into one entry linking the site and naming the pages: Old Tank Syndrome (Jessie Sanders, DVM, DABVP Fish Practice); Dechlorinator for Fish Systems (Jessie Sanders, DVM, DABVP Fish Practice). Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -3434,7 +3461,7 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>3</v>
@@ -3442,23 +3469,19 @@
       <c r="F68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Feeding Your Tegu; ReptiFiles: Tegu Brumation</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Feeding Your Tegu; Tegu Brumation.</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -3477,7 +3500,7 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>4</v>
@@ -3485,23 +3508,19 @@
       <c r="F69" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Tegu Handling Tips; ReptiFiles: Tegu Sexing</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Tegu Handling Tips; Tegu Sexing.</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -3520,7 +3539,7 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>2</v>
@@ -3530,13 +3549,13 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 4 times: ReptiFiles: Argentine and Colombian Tegu Care; ReptiFiles: Dehydration in Tegus; ReptiFiles: Prolapse in Tegus; ReptiFiles: Scale Rot in Tegus</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Argentine and Colombian Tegu Care; Dehydration in Tegus; Prolapse in Tegus; Scale Rot in Tegus.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
@@ -3544,7 +3563,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3606,7 +3629,7 @@
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>2</v>
@@ -3616,13 +3639,13 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Argentine and Colombian Tegu Care; ReptiFiles: Tegu Substrate Options; ReptiFiles: Scale Rot in Tegus</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Argentine and Colombian Tegu Care; Tegu Substrate Options; Scale Rot in Tegus.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
@@ -3630,7 +3653,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3696,7 +3723,7 @@
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>4</v>
@@ -3704,23 +3731,19 @@
       <c r="F74" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Digestive Disorders of Pet Birds; Merck Veterinary Manual: Mycotic Diseases of Pet Birds (Macrorhabdus ornithogaster Infection)</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Digestive Disorders of Pet Birds; Mycotic Diseases of Pet Birds (Macrorhabdus ornithogaster Infection).</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -3739,7 +3762,7 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>4</v>
@@ -3747,23 +3770,19 @@
       <c r="F75" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Polyoma Virus Infection in Birds; VCA Animal Hospitals: Psittacine Beak and Feather Disease in Pet Birds</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Polyoma Virus Infection in Birds; Psittacine Beak and Feather Disease in Pet Birds.</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -4273,7 +4292,7 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5" t="n">
         <v>4</v>
@@ -4281,23 +4300,19 @@
       <c r="F89" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Ball Python Terrarium Size &amp; Lighting; ReptiFiles: Ball Python Substrate Options</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Ball Python Terrarium Size &amp; Lighting; Ball Python Substrate Options.</t>
-        </is>
-      </c>
-      <c r="J89" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -4351,7 +4366,7 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>3</v>
@@ -4359,23 +4374,19 @@
       <c r="F91" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>animaldiversity.org listed 2 times: Python regius (Ball Python), Animal Diversity Web (University of Michigan); Pantherophis guttatus (Corn Snake), Animal Diversity Web (University of Michigan)</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Combine animaldiversity.org into one entry linking the site and naming the pages: Python regius (Ball Python), Animal Diversity Web (University of Michigan); Pantherophis guttatus (Corn Snake), Animal Diversity Web (University of Michigan).</t>
-        </is>
-      </c>
-      <c r="J91" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -4585,7 +4596,7 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>3</v>
@@ -4593,23 +4604,19 @@
       <c r="F97" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>articles.hepper.com listed 2 times: Hepper: How Long Can a Bearded Dragon Go Without Eating; Hepper: Bearded Dragon Brumation</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>Combine articles.hepper.com into one entry linking the site and naming the pages: How Long Can a Bearded Dragon Go Without Eating; Bearded Dragon Brumation.</t>
-        </is>
-      </c>
-      <c r="J97" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -4628,7 +4635,7 @@
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E98" s="5" t="n">
         <v>3</v>
@@ -4636,23 +4643,19 @@
       <c r="F98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Owning Bearded Dragons; VCA Animal Hospitals: Bearded Dragons, Diseases</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Owning Bearded Dragons; Bearded Dragons, Diseases.</t>
-        </is>
-      </c>
-      <c r="J98" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -4718,7 +4721,7 @@
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E100" s="5" t="n">
         <v>5</v>
@@ -4726,23 +4729,19 @@
       <c r="F100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 4 times: VCA Animal Hospitals: Bearded Dragons - Diseases; VCA Animal Hospitals: Bearded Dragons - Problems; VCA Animal Hospitals: Annual Veterinary Visit for Reptiles; VCA Animal Hospitals: Owning Bearded Dragons | merckvetmanual.com listed 2 times: Merck Veterinary Manual: Emergencies of Reptiles; Merck Veterinary Manual: Nutritional, Metabolic, and Endocrine Diseases of Reptiles</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr"/>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Bearded Dragons - Diseases; Bearded Dragons - Problems; Annual Veterinary Visit for Reptiles; Owning Bearded Dragons. Combine merckvetmanual.com into one entry linking the site and naming the pages: Emergencies of Reptiles; Nutritional, Metabolic, and Endocrine Diseases of Reptiles. Combining brings it from 9 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J100" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 9 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -4886,7 +4885,7 @@
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>4</v>
@@ -4894,23 +4893,19 @@
       <c r="F104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Feeding Bearded Dragons; VCA Animal Hospitals: Bearded Dragon Housing</t>
-        </is>
-      </c>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Feeding Bearded Dragons; Bearded Dragon Housing.</t>
-        </is>
-      </c>
-      <c r="J104" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="n"/>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -4929,7 +4924,7 @@
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>3</v>
@@ -4937,23 +4932,19 @@
       <c r="F105" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: How Long Do Leopard Geckos Live?, PetMD; How Long Do Bearded Dragons Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: How Long Do Leopard Geckos Live?, PetMD; How Long Do Bearded Dragons Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J105" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -5206,7 +5197,7 @@
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>6</v>
@@ -5216,7 +5207,7 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Parasitic Diseases of Fish; Merck Veterinary Manual: Bacterial Diseases of Fish | pmc.ncbi.nlm.nih.gov listed 4 times: Annelies M. Declercq, Freddy Haesebrouck, Wim Van den Broeck, Peter Bossier and Annemie Decostere, Veterinary Research 44:27 (2013): Columnaris disease in fish, a review with emphasis on bacterium-host interactions; Ana Silvia Pedrazzani, Murilo Henrique Quintiliano, Frederico Bolfe, Luisa Silva de Sousa and Antonio Ostrensky, Frontiers in Veterinary Science 7:606388 (2020): Tilapia On-Farm Welfare Assessment Protocol for Semi-intensive Production Systems; Catherine Pfefferli and Anna Jazwinska, Regeneration 2(2):72-83 (2015): The art of fin regeneration in zebrafish; Stefanie Wendler, Nils Hartmann, Beate Hoppe and Christoph Englert, Aging Cell 14(5):857-866 (2015): Age-dependent decline in fin regenerative capacity in the short-lived fish Nothobranchius furzeri | 7 sources, 6 after combining same-site entries.</t>
+          <t>pmc.ncbi.nlm.nih.gov listed 4 times: Annelies M. Declercq, Freddy Haesebrouck, Wim Van den Broeck, Peter Bossier and Annemie Decostere, Veterinary Research 44:27 (2013): Columnaris disease in fish, a review with emphasis on bacterium-host interactions; Ana Silvia Pedrazzani, Murilo Henrique Quintiliano, Frederico Bolfe, Luisa Silva de Sousa and Antonio Ostrensky, Frontiers in Veterinary Science 7:606388 (2020): Tilapia On-Farm Welfare Assessment Protocol for Semi-intensive Production Systems; Catherine Pfefferli and Anna Jazwinska, Regeneration 2(2):72-83 (2015): The art of fin regeneration in zebrafish; Stefanie Wendler, Nils Hartmann, Beate Hoppe and Christoph Englert, Aging Cell 14(5):857-866 (2015): Age-dependent decline in fin regenerative capacity in the short-lived fish Nothobranchius furzeri | 6 sources, 6 after combining same-site entries.</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -5226,7 +5217,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Parasitic Diseases of Fish; Bacterial Diseases of Fish. Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
@@ -5234,7 +5225,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K112" s="5" t="inlineStr"/>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 7 to 6 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -5288,7 +5283,7 @@
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E114" s="5" t="n">
         <v>3</v>
@@ -5296,23 +5291,19 @@
       <c r="F114" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: Betta Fish Care Sheet, PetMD; Goldfish Care Sheet, PetMD</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Betta Fish Care Sheet, PetMD; Goldfish Care Sheet, PetMD.</t>
-        </is>
-      </c>
-      <c r="J114" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n"/>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -5374,7 +5365,7 @@
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>2</v>
@@ -5384,13 +5375,13 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Bearded Dragon Substrate Options; ReptiFiles: How to Build a Bioactive Terrarium for Your Reptile; ReptiFiles: The Quick Guide to Bioactive Vivarium Maintenance</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Bearded Dragon Substrate Options; How to Build a Bioactive Terrarium for Your Reptile; The Quick Guide to Bioactive Vivarium Maintenance.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J116" s="6" t="inlineStr">
@@ -5398,7 +5389,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -5417,7 +5412,7 @@
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>4</v>
@@ -5425,23 +5420,19 @@
       <c r="F117" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Recognizing the Signs of Illness in Pet Birds; VCA Animal Hospitals: Respiratory Disease in Birds</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Recognizing the Signs of Illness in Pet Birds; Respiratory Disease in Birds.</t>
-        </is>
-      </c>
-      <c r="J117" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="5" t="n"/>
+      <c r="I117" s="5" t="n"/>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5460,7 +5451,7 @@
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>3</v>
@@ -5468,23 +5459,19 @@
       <c r="F118" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 3 times: VCA Animal Hospitals: Chronic Egg Laying in Birds; VCA Animal Hospitals: Egg Binding in Birds; VCA Animal Hospitals: Sexual Behavior in Birds</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Chronic Egg Laying in Birds; Egg Binding in Birds; Sexual Behavior in Birds.</t>
-        </is>
-      </c>
-      <c r="J118" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="5" t="n"/>
+      <c r="I118" s="5" t="n"/>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -5503,7 +5490,7 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E119" s="5" t="n">
         <v>3</v>
@@ -5511,23 +5498,19 @@
       <c r="F119" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>lafeber.com listed 3 times: Lafeber Pet Birds: Size of Aviary; Lafeber Pet Birds: Finches Behavior; Lafeber Pet Birds: Canary Personality, Food &amp; Care</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Size of Aviary; Finches Behavior; Canary Personality, Food &amp; Care.</t>
-        </is>
-      </c>
-      <c r="J119" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -5546,7 +5529,7 @@
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E120" s="5" t="n">
         <v>3</v>
@@ -5554,23 +5537,19 @@
       <c r="F120" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Birds, Abnormal Droppings; VCA Animal Hospitals: Recognizing the Signs of Illness in Pet Birds | merckvetmanual.com listed 2 times: Merck Veterinary Manual: Reproductive Disorders of Pet Birds; Merck Veterinary Manual: Digestive Disorders of Pet Birds</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Birds, Abnormal Droppings; Recognizing the Signs of Illness in Pet Birds. Combine merckvetmanual.com into one entry linking the site and naming the pages: Reproductive Disorders of Pet Birds; Digestive Disorders of Pet Birds.</t>
-        </is>
-      </c>
-      <c r="J120" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n"/>
+      <c r="I120" s="5" t="n"/>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -5589,7 +5568,7 @@
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E121" s="5" t="n">
         <v>5</v>
@@ -5597,23 +5576,19 @@
       <c r="F121" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Transporting Your Bird, Car and Air Travel; VCA Animal Hospitals: Nursing Care for Sick Pet Birds</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Transporting Your Bird, Car and Air Travel; Nursing Care for Sick Pet Birds. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J121" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="5" t="n"/>
+      <c r="I121" s="5" t="n"/>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -5632,7 +5607,7 @@
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>4</v>
@@ -5640,23 +5615,19 @@
       <c r="F122" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Skin and Feather Disorders of Pet Birds; Merck Veterinary Manual: Miscellaneous Diseases of Pet Birds</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Skin and Feather Disorders of Pet Birds; Miscellaneous Diseases of Pet Birds.</t>
-        </is>
-      </c>
-      <c r="J122" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="5" t="n"/>
+      <c r="I122" s="5" t="n"/>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -5675,7 +5646,7 @@
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>3</v>
@@ -5683,23 +5654,19 @@
       <c r="F123" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Common Conditions of Pet Birds; VCA Animal Hospitals: Psittacine Beak and Feather Disease in Pet Birds | lafeber.com listed 2 times: Lafeber Pet Birds: Pin Feathers; Lafeber Pet Birds: Moody Molting Cockatiel</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Common Conditions of Pet Birds; Psittacine Beak and Feather Disease in Pet Birds. Combine lafeber.com into one entry linking the site and naming the pages: Pin Feathers; Moody Molting Cockatiel.</t>
-        </is>
-      </c>
-      <c r="J123" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="5" t="n"/>
+      <c r="I123" s="5" t="n"/>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -5718,7 +5685,7 @@
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E124" s="5" t="n">
         <v>3</v>
@@ -5726,23 +5693,19 @@
       <c r="F124" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Beak and Nail Care in Birds; VCA Animal Hospitals: Blood or Pin Feathers in Birds | lafeber.com listed 2 times: LafeberVet: Grooming Companion Birds, A Review; LafeberVet: Psittacine Behavior, Handling, and Restraint</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr"/>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Beak and Nail Care in Birds; Blood or Pin Feathers in Birds. Combine lafeber.com into one entry linking the site and naming the pages: Grooming Companion Birds, A Review; Psittacine Behavior, Handling, and Restraint.</t>
-        </is>
-      </c>
-      <c r="J124" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="5" t="n"/>
+      <c r="I124" s="5" t="n"/>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -5761,7 +5724,7 @@
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>4</v>
@@ -5769,23 +5732,19 @@
       <c r="F125" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Household Hazards and Dangers to Birds; VCA Animal Hospitals: Zinc Poisoning in Pets | lafeber.com listed 2 times: Lafeber: Cat Bites to Pet Birds; Lafeber: Foods Toxic to Pet Birds</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Household Hazards and Dangers to Birds; Zinc Poisoning in Pets. Combine lafeber.com into one entry linking the site and naming the pages: Cat Bites to Pet Birds; Foods Toxic to Pet Birds. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J125" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="5" t="n"/>
+      <c r="I125" s="5" t="n"/>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -5804,7 +5763,7 @@
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5" t="n">
         <v>3</v>
@@ -5812,23 +5771,19 @@
       <c r="F126" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 3 times: VCA Animal Hospitals: Feeding Conures; VCA Animal Hospitals: Feeding Budgies; VCA Animal Hospitals: Cockatiels, Feeding</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Feeding Conures; Feeding Budgies; Cockatiels, Feeding.</t>
-        </is>
-      </c>
-      <c r="J126" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="5" t="n"/>
+      <c r="I126" s="5" t="n"/>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -5847,7 +5802,7 @@
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>4</v>
@@ -5855,23 +5810,19 @@
       <c r="F127" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Chronic Egg Laying in Birds; VCA Animal Hospitals: Sexual Behavior in Birds</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Chronic Egg Laying in Birds; Sexual Behavior in Birds.</t>
-        </is>
-      </c>
-      <c r="J127" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
+      <c r="I127" s="5" t="n"/>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -5890,7 +5841,7 @@
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>4</v>
@@ -5898,23 +5849,19 @@
       <c r="F128" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 3 times: VCA Animal Hospitals: Veterinary Care for Your New Bird; VCA Animal Hospitals: Psittacine Beak and Feather Disease in Pet Birds; VCA Animal Hospitals: Polyoma Virus Infection in Birds</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Veterinary Care for Your New Bird; Psittacine Beak and Feather Disease in Pet Birds; Polyoma Virus Infection in Birds. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J128" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="5" t="n"/>
+      <c r="I128" s="5" t="n"/>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -5933,7 +5880,7 @@
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5" t="n">
         <v>3</v>
@@ -5943,21 +5890,29 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 4 times: LafeberVet: Basic Information Sheet for the Cockatoo; LafeberVet: Basic Information Sheet for the Cockatiel; Lafeber Co.: Is Your Pet Bird a Healthy Weight?, Susan Orosz DVM; LafeberVet: Body Condition Scoring in Birds, Christal Pollock DVM</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
+          <t>lafeber.com listed 2 times: LafeberVet; Lafeber Co.: Is Your Pet Bird a Healthy Weight?, Susan Orosz DVM</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: LafeberVet (lafeber.com/vet, written for veterinarians) and Lafeber Co. pet owner pages are two different sites on one domain.</t>
+        </is>
+      </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Basic Information Sheet for the Cockatoo; Basic Information Sheet for the Cockatiel; Is Your Pet Bird a Healthy Weight?, Susan Orosz DVM; Body Condition Scoring in Birds, Christal Pollock DVM. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J129" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K129" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries. 2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -5976,7 +5931,7 @@
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E130" s="5" t="n">
         <v>3</v>
@@ -5984,23 +5939,19 @@
       <c r="F130" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Wing Clipping; VCA Animal Hospitals: Blood or Pin Feathers in Birds</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Wing Clipping; Blood or Pin Feathers in Birds.</t>
-        </is>
-      </c>
-      <c r="J130" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="5" t="n"/>
+      <c r="I130" s="5" t="n"/>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -6167,7 +6118,7 @@
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>4</v>
@@ -6175,23 +6126,19 @@
       <c r="F135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Blue Tongue Skink Parasites; ReptiFiles: Blue Tongue Skink Brumation; ReptiFiles: Blue Tongue Skink Obesity</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Blue Tongue Skink Parasites; Blue Tongue Skink Brumation; Blue Tongue Skink Obesity. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J135" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="5" t="n"/>
+      <c r="I135" s="5" t="n"/>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -6370,7 +6317,7 @@
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5" t="n">
         <v>4</v>
@@ -6378,23 +6325,19 @@
       <c r="F140" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: What Do Boa Constrictors Eat?; ReptiFiles: Boa Not Eating? Find Out Why</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: What Do Boa Constrictors Eat?; Boa Not Eating? Find Out Why.</t>
-        </is>
-      </c>
-      <c r="J140" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="5" t="n"/>
+      <c r="I140" s="5" t="n"/>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -6456,7 +6399,7 @@
         </is>
       </c>
       <c r="D142" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E142" s="5" t="n">
         <v>3</v>
@@ -6464,23 +6407,19 @@
       <c r="F142" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Boa Constrictor Scale Rot; ReptiFiles: Inclusion Body Disease in Boa Constrictors; ReptiFiles: Boa Constrictor Buyer's Guide | merckvetmanual.com listed 2 times: Merck Veterinary Manual: Viral Diseases of Reptiles; Merck Veterinary Manual: Parasitic Diseases of Reptiles</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr"/>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Boa Constrictor Scale Rot; Inclusion Body Disease in Boa Constrictors; Boa Constrictor Buyer's Guide. Combine merckvetmanual.com into one entry linking the site and naming the pages: Viral Diseases of Reptiles; Parasitic Diseases of Reptiles. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J142" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="5" t="n"/>
+      <c r="I142" s="5" t="n"/>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -6546,7 +6485,7 @@
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5" t="n">
         <v>1</v>
@@ -6556,13 +6495,13 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Boa Constrictor Enclosure Size; ReptiFiles: Boa Constrictor Temperatures; ReptiFiles: Boa Constrictor UVB and Lighting</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr"/>
+          <t>Only 1 source.</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Boa Constrictor Enclosure Size; Boa Constrictor Temperatures; Boa Constrictor UVB and Lighting.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
@@ -6570,7 +6509,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K144" s="5" t="inlineStr"/>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 1 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -6659,7 +6602,7 @@
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>6</v>
@@ -6669,13 +6612,13 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Feeding Box Turtles; VCA Animal Hospitals: Housing Box Turtles | zoomed.com listed 2 times: Zoo Med: ReptiSun 5.0 UVB T5 HO Linear Lamp; Zoo Med: ReptiSun T5 HO Terrarium Hood Instructions (PDF) | 8 sources, 6 after combining same-site entries.</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
+          <t>6 sources, 6 after combining same-site entries.</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Feeding Box Turtles; Housing Box Turtles. Combine zoomed.com into one entry linking the site and naming the pages: ReptiSun 5.0 UVB T5 HO Linear Lamp; ReptiSun T5 HO Terrarium Hood Instructions (PDF). Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
@@ -6683,7 +6626,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K147" s="5" t="inlineStr"/>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 8 to 6 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -6819,7 +6766,7 @@
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E151" s="5" t="n">
         <v>2</v>
@@ -6829,13 +6776,13 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Common Diseases of Box Turtles; VCA Animal Hospitals: Owning Box Turtles | merckvetmanual.com listed 2 times: Merck Veterinary Manual: Nutritional, Metabolic, and Endocrine Diseases of Reptiles; Merck Veterinary Manual: Bacterial Diseases of Reptiles</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Common Diseases of Box Turtles; Owning Box Turtles. Combine merckvetmanual.com into one entry linking the site and naming the pages: Nutritional, Metabolic, and Endocrine Diseases of Reptiles; Bacterial Diseases of Reptiles.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
@@ -6843,7 +6790,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K151" s="5" t="inlineStr"/>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -6909,7 +6860,7 @@
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E153" s="5" t="n">
         <v>3</v>
@@ -6917,23 +6868,19 @@
       <c r="F153" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Box Turtles, Housing; VCA Animal Hospitals: Box Turtles, Feeding</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Box Turtles, Housing; Box Turtles, Feeding.</t>
-        </is>
-      </c>
-      <c r="J153" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="5" t="n"/>
+      <c r="I153" s="5" t="n"/>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -7116,7 +7063,7 @@
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5" t="n">
         <v>4</v>
@@ -7124,23 +7071,19 @@
       <c r="F158" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>practicalfishkeeping.co.uk listed 2 times: Practical Fishkeeping: What you need to know about bagging fish; Practical Fishkeeping: Travels with your fish</t>
-        </is>
-      </c>
-      <c r="H158" s="5" t="inlineStr"/>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>Combine practicalfishkeeping.co.uk into one entry linking the site and naming the pages: What you need to know about bagging fish; Travels with your fish.</t>
-        </is>
-      </c>
-      <c r="J158" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K158" s="5" t="inlineStr"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
+      <c r="J158" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -7474,7 +7417,7 @@
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E168" s="5" t="n">
         <v>3</v>
@@ -7482,23 +7425,19 @@
       <c r="F168" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: How Long Do Parakeets Live?, PetMD; How Long Do Birds Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr"/>
-      <c r="I168" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: How Long Do Parakeets Live?, PetMD; How Long Do Birds Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J168" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K168" s="5" t="inlineStr"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="5" t="n"/>
+      <c r="I168" s="5" t="n"/>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -7599,7 +7538,7 @@
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>4</v>
@@ -7607,23 +7546,19 @@
       <c r="F171" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>reptilesmagazine.com listed 2 times: Reptiles Magazine: California Kingsnake Care Sheet; Reptiles Magazine: All Hail the California Kingsnake</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr"/>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptilesmagazine.com into one entry linking the site and naming the pages: California Kingsnake Care Sheet; All Hail the California Kingsnake.</t>
-        </is>
-      </c>
-      <c r="J171" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K171" s="5" t="inlineStr"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="5" t="n"/>
+      <c r="I171" s="5" t="n"/>
+      <c r="J171" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -7794,7 +7729,7 @@
         </is>
       </c>
       <c r="D176" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E176" s="5" t="n">
         <v>4</v>
@@ -7802,23 +7737,19 @@
       <c r="F176" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>reptilesmagazine.com listed 2 times: Reptiles Magazine: California Kingsnake Care Sheet (Robert Applegate); Reptiles Magazine: All Hail the California Kingsnake</t>
-        </is>
-      </c>
-      <c r="H176" s="5" t="inlineStr"/>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptilesmagazine.com into one entry linking the site and naming the pages: California Kingsnake Care Sheet (Robert Applegate); All Hail the California Kingsnake.</t>
-        </is>
-      </c>
-      <c r="J176" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K176" s="5" t="inlineStr"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="5" t="n"/>
+      <c r="I176" s="5" t="n"/>
+      <c r="J176" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -7942,7 +7873,7 @@
         </is>
       </c>
       <c r="D180" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E180" s="5" t="n">
         <v>3</v>
@@ -7950,23 +7881,19 @@
       <c r="F180" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>lafeber.com listed 2 times: LafeberVet: Basic Information Sheet, Canary; LafeberVet: Avian Emergency and Critical Care Summary Page</t>
-        </is>
-      </c>
-      <c r="H180" s="5" t="inlineStr"/>
-      <c r="I180" s="5" t="inlineStr">
-        <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Basic Information Sheet, Canary; Avian Emergency and Critical Care Summary Page.</t>
-        </is>
-      </c>
-      <c r="J180" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K180" s="5" t="inlineStr"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="5" t="n"/>
+      <c r="I180" s="5" t="n"/>
+      <c r="J180" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -7985,7 +7912,7 @@
         </is>
       </c>
       <c r="D181" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E181" s="5" t="n">
         <v>4</v>
@@ -7993,23 +7920,19 @@
       <c r="F181" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Parasitic Diseases of Pet Birds; Merck Veterinary Manual: Mites of Poultry (Dermanyssus gallinae, the red mite)</t>
-        </is>
-      </c>
-      <c r="H181" s="5" t="inlineStr"/>
-      <c r="I181" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Parasitic Diseases of Pet Birds; Mites of Poultry (Dermanyssus gallinae, the red mite).</t>
-        </is>
-      </c>
-      <c r="J181" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K181" s="5" t="inlineStr"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="5" t="n"/>
+      <c r="I181" s="5" t="n"/>
+      <c r="J181" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -8262,7 +8185,7 @@
         </is>
       </c>
       <c r="D188" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E188" s="5" t="n">
         <v>4</v>
@@ -8270,23 +8193,19 @@
       <c r="F188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>aquariumcoop.com listed 2 times: How to Treat Ich or White Spot Disease on Freshwater Fish - Aquarium Co-Op; 5 Quick and Easy Steps for Treating Fin Rot in Aquarium Fish - Aquarium Co-Op</t>
-        </is>
-      </c>
-      <c r="H188" s="5" t="inlineStr"/>
-      <c r="I188" s="5" t="inlineStr">
-        <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: How to Treat Ich or White Spot Disease on Freshwater Fish - Aquarium Co-Op; 5 Quick and Easy Steps for Treating Fin Rot in Aquarium Fish - Aquarium Co-Op.</t>
-        </is>
-      </c>
-      <c r="J188" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K188" s="5" t="inlineStr"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="5" t="n"/>
+      <c r="I188" s="5" t="n"/>
+      <c r="J188" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -8340,7 +8259,7 @@
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E190" s="5" t="n">
         <v>4</v>
@@ -8350,7 +8269,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 3 times: VCA Animal Hospitals: Cardiomyopathy in Cats; VCA Animal Hospitals: Aortic Thromboembolism in Cats; VCA Animal Hospitals: Dilated Cardiomyopathy (DCM) in Dogs | pmc.ncbi.nlm.nih.gov listed 2 times: Natural history of hypertrophic cardiomyopathy in cats from rehoming centers: The CatScan II study; Genetic Basis of Hypertrophic Cardiomyopathy in Cats</t>
+          <t>pmc.ncbi.nlm.nih.gov listed 2 times: Natural history of hypertrophic cardiomyopathy in cats from rehoming centers: The CatScan II study; Genetic Basis of Hypertrophic Cardiomyopathy in Cats</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -8360,7 +8279,7 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Cardiomyopathy in Cats; Aortic Thromboembolism in Cats; Dilated Cardiomyopathy (DCM) in Dogs. Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Combining brings it from 6 to 4, inside 3 to 5.</t>
+          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J190" s="6" t="inlineStr">
@@ -8368,7 +8287,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K190" s="5" t="inlineStr"/>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -8422,7 +8345,7 @@
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E192" s="5" t="n">
         <v>2</v>
@@ -8432,13 +8355,13 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>vet.cornell.edu listed 3 times: Cornell Feline Health Center: A Hairy Dilemma; Cornell Feline Health Center: Vomiting; Cornell Feline Health Center: Inflammatory Bowel Disease</t>
-        </is>
-      </c>
-      <c r="H192" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>Combine vet.cornell.edu into one entry linking the site and naming the pages: A Hairy Dilemma; Vomiting; Inflammatory Bowel Disease.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J192" s="6" t="inlineStr">
@@ -8446,7 +8369,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K192" s="5" t="inlineStr"/>
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -8735,7 +8662,7 @@
         </is>
       </c>
       <c r="D199" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E199" s="5" t="n">
         <v>5</v>
@@ -8743,27 +8670,19 @@
       <c r="F199" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>flipaquatics.com listed 2 times: Red Cherry Shrimp for Sale - Flip Aquatics; Painted Fire Red Shrimp - Flip Aquatics</t>
-        </is>
-      </c>
-      <c r="H199" s="5" t="inlineStr">
-        <is>
-          <t>flipaquatics.com: 2 of these pages are also linked in the body, so a reader lands on that exact page.</t>
-        </is>
-      </c>
-      <c r="I199" s="5" t="inlineStr">
-        <is>
-          <t>Combine flipaquatics.com into one entry linking the site and naming the pages: Red Cherry Shrimp for Sale - Flip Aquatics; Painted Fire Red Shrimp - Flip Aquatics. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J199" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K199" s="5" t="inlineStr"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="5" t="n"/>
+      <c r="I199" s="5" t="n"/>
+      <c r="J199" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -8817,7 +8736,7 @@
         </is>
       </c>
       <c r="D201" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E201" s="5" t="n">
         <v>3</v>
@@ -8825,23 +8744,19 @@
       <c r="F201" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>aquariumcoop.com listed 2 times: Care Guide for Cherry Shrimp, Aquarium Co-Op; Are Indian Almond Leaves Good for Aquarium Fish and How Are They Used?, Aquarium Co-Op | shrimpscience.com listed 2 times: Why Are My Freshwater Shrimp Dying?, Shrimp Science; Molting and Common Problems, Shrimp Science</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr"/>
-      <c r="I201" s="5" t="inlineStr">
-        <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: Care Guide for Cherry Shrimp, Aquarium Co-Op; Are Indian Almond Leaves Good for Aquarium Fish and How Are They Used?, Aquarium Co-Op. Combine shrimpscience.com into one entry linking the site and naming the pages: Why Are My Freshwater Shrimp Dying?, Shrimp Science; Molting and Common Problems, Shrimp Science.</t>
-        </is>
-      </c>
-      <c r="J201" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K201" s="5" t="inlineStr"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
+      <c r="J201" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -8895,7 +8810,7 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E203" s="5" t="n">
         <v>4</v>
@@ -8903,23 +8818,19 @@
       <c r="F203" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G203" s="5" t="inlineStr">
-        <is>
-          <t>shrimpscience.com listed 2 times: Molting and Common Problems, Shrimp Science; Why Are My Freshwater Shrimp Dying?, Shrimp Science</t>
-        </is>
-      </c>
-      <c r="H203" s="5" t="inlineStr"/>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>Combine shrimpscience.com into one entry linking the site and naming the pages: Molting and Common Problems, Shrimp Science; Why Are My Freshwater Shrimp Dying?, Shrimp Science.</t>
-        </is>
-      </c>
-      <c r="J203" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K203" s="5" t="inlineStr"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+      <c r="J203" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -9078,7 +8989,7 @@
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E208" s="5" t="n">
         <v>4</v>
@@ -9086,23 +8997,19 @@
       <c r="F208" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Chinchillas; Merck Veterinary Manual: Selecting a Chinchilla</t>
-        </is>
-      </c>
-      <c r="H208" s="5" t="inlineStr"/>
-      <c r="I208" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Chinchillas; Selecting a Chinchilla.</t>
-        </is>
-      </c>
-      <c r="J208" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K208" s="5" t="inlineStr"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
+      <c r="J208" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -9121,7 +9028,7 @@
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E209" s="5" t="n">
         <v>4</v>
@@ -9129,23 +9036,19 @@
       <c r="F209" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G209" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Routine Health Care for Chinchillas; Merck Veterinary Manual: Chinchillas (professional version)</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="inlineStr"/>
-      <c r="I209" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Routine Health Care for Chinchillas; Chinchillas (professional version).</t>
-        </is>
-      </c>
-      <c r="J209" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K209" s="5" t="inlineStr"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
+      <c r="J209" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -9211,7 +9114,7 @@
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E211" s="5" t="n">
         <v>4</v>
@@ -9219,17 +9122,9 @@
       <c r="F211" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G211" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Providing a Home for a Chinchilla; Merck Veterinary Manual: Chinchillas (professional version)</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="inlineStr"/>
-      <c r="I211" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Providing a Home for a Chinchilla; Chinchillas (professional version).</t>
-        </is>
-      </c>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
       <c r="J211" s="6" t="inlineStr">
         <is>
           <t>Review</t>
@@ -9237,7 +9132,7 @@
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>FIX_PLAN: the 50 to 68F comfort band; Merck (65 to 80F) and PetMD (55 to 70F) run warmer. Settle one band with sources. 2026-10-06: sources disagree. VCA (listed on the heat stress guide) 50 to 68F; PetMD 55 to 70F, never over 80; LafeberVet 59 to 70F; Merck 65 to 80F adapted range. The setup guide lists PetMD, LafeberVet and Merck but not VCA. Owner call. Settled 2026-10-06 (owner): 55 to 70F everywhere.</t>
+          <t>FIX_PLAN: the 50 to 68F comfort band; Merck (65 to 80F) and PetMD (55 to 70F) run warmer. Settle one band with sources. 2026-10-06: sources disagree. VCA (listed on the heat stress guide) 50 to 68F; PetMD 55 to 70F, never over 80; LafeberVet 59 to 70F; Merck 65 to 80F adapted range. The setup guide lists PetMD, LafeberVet and Merck but not VCA. Owner call. Settled 2026-10-06 (owner): 55 to 70F everywhere. 2026-10-06: same-site entries combined, 5 to 4 entries.</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9153,7 @@
         </is>
       </c>
       <c r="D212" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E212" s="5" t="n">
         <v>3</v>
@@ -9266,23 +9161,19 @@
       <c r="F212" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 3 times: Vitamin C Deficiency in Guinea Pigs, PetMD; How Long Do Chinchillas Live?, PetMD; How Long Do Guinea Pigs Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H212" s="5" t="inlineStr"/>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Vitamin C Deficiency in Guinea Pigs, PetMD; How Long Do Chinchillas Live?, PetMD; How Long Do Guinea Pigs Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J212" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K212" s="5" t="inlineStr"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
+      <c r="J212" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -9301,7 +9192,7 @@
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E213" s="5" t="n">
         <v>3</v>
@@ -9309,23 +9200,19 @@
       <c r="F213" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Chinchillas, Merck Veterinary Manual; Hamsters, Merck Veterinary Manual; Description and Physical Characteristics of Chinchillas, Merck Veterinary Manual | petmd.com listed 2 times: How Long Do Chinchillas Live?, PetMD; How Long Do Hamsters Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="inlineStr"/>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Chinchillas, Merck Veterinary Manual; Hamsters, Merck Veterinary Manual; Description and Physical Characteristics of Chinchillas, Merck Veterinary Manual. Combine petmd.com into one entry linking the site and naming the pages: How Long Do Chinchillas Live?, PetMD; How Long Do Hamsters Live?, PetMD. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J213" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K213" s="5" t="inlineStr"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
+      <c r="I213" s="5" t="n"/>
+      <c r="J213" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -9344,7 +9231,7 @@
         </is>
       </c>
       <c r="D214" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E214" s="5" t="n">
         <v>4</v>
@@ -9352,23 +9239,19 @@
       <c r="F214" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Cockatiels - General Information; VCA Animal Hospitals: Cockatoos - General Information</t>
-        </is>
-      </c>
-      <c r="H214" s="5" t="inlineStr"/>
-      <c r="I214" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Cockatiels - General Information; Cockatoos - General Information.</t>
-        </is>
-      </c>
-      <c r="J214" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K214" s="5" t="inlineStr"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
+      <c r="J214" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -9504,7 +9387,7 @@
         </is>
       </c>
       <c r="D218" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E218" s="5" t="n">
         <v>3</v>
@@ -9514,21 +9397,29 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 4 times: Lafeber: Cockatiel Questions; Lafeber: Cockatiel Hissing and Nipping; LafeberVet: Reading Bird Body Language; Lafeber: Add Another Cockatiel?</t>
-        </is>
-      </c>
-      <c r="H218" s="5" t="inlineStr"/>
+          <t>lafeber.com listed 2 times: Lafeber Pet Birds; LafeberVet: Reading Bird Body Language</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: LafeberVet (lafeber.com/vet, written for veterinarians) and Lafeber Co. pet owner pages are two different sites on one domain.</t>
+        </is>
+      </c>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Cockatiel Questions; Cockatiel Hissing and Nipping; Reading Bird Body Language; Add Another Cockatiel?. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J218" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K218" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J218" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries. 2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -9664,7 +9555,7 @@
         </is>
       </c>
       <c r="D222" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E222" s="5" t="n">
         <v>5</v>
@@ -9672,23 +9563,19 @@
       <c r="F222" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G222" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Cockatoos, General Information; VCA Animal Hospitals: Psittacine Beak and Feather Disease in Pet Birds</t>
-        </is>
-      </c>
-      <c r="H222" s="5" t="inlineStr"/>
-      <c r="I222" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Cockatoos, General Information; Psittacine Beak and Feather Disease in Pet Birds. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J222" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K222" s="5" t="inlineStr"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5" t="n"/>
+      <c r="I222" s="5" t="n"/>
+      <c r="J222" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -9820,7 +9707,7 @@
         </is>
       </c>
       <c r="D226" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E226" s="5" t="n">
         <v>3</v>
@@ -9828,23 +9715,19 @@
       <c r="F226" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G226" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Psittacine Beak and Feather Disease in Pet Birds; VCA Animal Hospitals: Common Conditions of Pet Birds | petmd.com listed 2 times: PetMD: Cockatoo Bird Species, Lifespan, and Care; PetMD: Vent Prolapse in Birds</t>
-        </is>
-      </c>
-      <c r="H226" s="5" t="inlineStr"/>
-      <c r="I226" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Psittacine Beak and Feather Disease in Pet Birds; Common Conditions of Pet Birds. Combine petmd.com into one entry linking the site and naming the pages: Cockatoo Bird Species, Lifespan, and Care; Vent Prolapse in Birds.</t>
-        </is>
-      </c>
-      <c r="J226" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K226" s="5" t="inlineStr"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="5" t="n"/>
+      <c r="I226" s="5" t="n"/>
+      <c r="J226" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -9933,7 +9816,7 @@
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E229" s="5" t="n">
         <v>3</v>
@@ -9941,23 +9824,19 @@
       <c r="F229" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Bathing Birds; VCA Animal Hospitals: Cockatoos, Feeding</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr"/>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Bathing Birds; Cockatoos, Feeding.</t>
-        </is>
-      </c>
-      <c r="J229" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K229" s="5" t="inlineStr"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
+      <c r="J229" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -10163,7 +10042,7 @@
         </is>
       </c>
       <c r="D235" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E235" s="5" t="n">
         <v>3</v>
@@ -10171,23 +10050,19 @@
       <c r="F235" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G235" s="5" t="inlineStr">
-        <is>
-          <t>lafeber.com listed 2 times: Lafeber: Green-Cheeked Conure; Lafeber: Male or Female? Your Bird's Gender Goes Beyond Naming | vcahospitals.com listed 2 times: VCA Animal Hospitals: Biting and Screaming in Birds; VCA Animal Hospitals: Introducing a New Pet Bird</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="inlineStr"/>
-      <c r="I235" s="5" t="inlineStr">
-        <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Green-Cheeked Conure; Male or Female? Your Bird's Gender Goes Beyond Naming. Combine vcahospitals.com into one entry linking the site and naming the pages: Biting and Screaming in Birds; Introducing a New Pet Bird.</t>
-        </is>
-      </c>
-      <c r="J235" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K235" s="5" t="inlineStr"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
+      <c r="J235" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -10444,7 +10319,7 @@
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E242" s="5" t="n">
         <v>4</v>
@@ -10452,23 +10327,19 @@
       <c r="F242" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G242" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Corn Snake Handling &amp; Body Language; ReptiFiles: Corn Snake Terrarium Size Requirements; ReptiFiles: How to Find a Lost Snake</t>
-        </is>
-      </c>
-      <c r="H242" s="5" t="inlineStr"/>
-      <c r="I242" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Corn Snake Handling &amp; Body Language; Corn Snake Terrarium Size Requirements; How to Find a Lost Snake. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J242" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K242" s="5" t="inlineStr"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
+      <c r="J242" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -10569,7 +10440,7 @@
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E245" s="5" t="n">
         <v>3</v>
@@ -10577,23 +10448,19 @@
       <c r="F245" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G245" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Corn Snake Substrate Options; ReptiFiles: Corn Snake Terrarium Size Requirements; ReptiFiles: Corn Snake Temperatures and Humidity Requirements</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="inlineStr"/>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Corn Snake Substrate Options; Corn Snake Terrarium Size Requirements; Corn Snake Temperatures and Humidity Requirements.</t>
-        </is>
-      </c>
-      <c r="J245" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K245" s="5" t="inlineStr"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="5" t="n"/>
+      <c r="I245" s="5" t="n"/>
+      <c r="J245" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
@@ -10612,7 +10479,7 @@
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E246" s="5" t="n">
         <v>4</v>
@@ -10620,23 +10487,19 @@
       <c r="F246" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G246" s="5" t="inlineStr">
-        <is>
-          <t>animaldiversity.org listed 3 times: Heterodon platirhinos (Eastern Hognose Snake), Animal Diversity Web (University of Michigan); Pantherophis guttatus (Corn Snake), Animal Diversity Web (University of Michigan); Animal Diversity Web: Heterodon nasicus</t>
-        </is>
-      </c>
-      <c r="H246" s="5" t="inlineStr"/>
-      <c r="I246" s="5" t="inlineStr">
-        <is>
-          <t>Combine animaldiversity.org into one entry linking the site and naming the pages: Heterodon platirhinos (Eastern Hognose Snake), Animal Diversity Web (University of Michigan); Pantherophis guttatus (Corn Snake), Animal Diversity Web (University of Michigan); Heterodon nasicus. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J246" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K246" s="5" t="inlineStr"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="5" t="n"/>
+      <c r="I246" s="5" t="n"/>
+      <c r="J246" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -10780,7 +10643,7 @@
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E250" s="5" t="n">
         <v>4</v>
@@ -10788,23 +10651,19 @@
       <c r="F250" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G250" s="5" t="inlineStr">
-        <is>
-          <t>seriouslyfish.com listed 2 times: SeriouslyFish: Corydoras pygmaeus; SeriouslyFish: Corydoras sterbai</t>
-        </is>
-      </c>
-      <c r="H250" s="5" t="inlineStr"/>
-      <c r="I250" s="5" t="inlineStr">
-        <is>
-          <t>Combine seriouslyfish.com into one entry linking the site and naming the pages: Corydoras pygmaeus; Corydoras sterbai.</t>
-        </is>
-      </c>
-      <c r="J250" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K250" s="5" t="inlineStr"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
+      <c r="J250" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -10858,7 +10717,7 @@
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E252" s="5" t="n">
         <v>2</v>
@@ -10868,13 +10727,13 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>aquariumcoop.com listed 2 times: Aquarium Co-Op: Care Guide for Cory Catfish; Aquarium Co-Op: How to Use a Gravel Vacuum or Aquarium Siphon to Clean Fish Tanks | seriouslyfish.com listed 2 times: SeriouslyFish: Corydoras sterbai; SeriouslyFish: Corydoras panda</t>
-        </is>
-      </c>
-      <c r="H252" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: Care Guide for Cory Catfish; How to Use a Gravel Vacuum or Aquarium Siphon to Clean Fish Tanks. Combine seriouslyfish.com into one entry linking the site and naming the pages: Corydoras sterbai; Corydoras panda.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J252" s="6" t="inlineStr">
@@ -10882,7 +10741,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K252" s="5" t="inlineStr"/>
+      <c r="K252" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -10901,7 +10764,7 @@
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E253" s="5" t="n">
         <v>4</v>
@@ -10909,23 +10772,19 @@
       <c r="F253" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G253" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Crested Gecko Starter Kit / Shopping List; ReptiFiles: Crested Gecko Enclosure Size and Cohabitation; ReptiFiles: Sexing Crested Geckos</t>
-        </is>
-      </c>
-      <c r="H253" s="5" t="inlineStr"/>
-      <c r="I253" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Crested Gecko Starter Kit / Shopping List; Crested Gecko Enclosure Size and Cohabitation; Sexing Crested Geckos. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J253" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K253" s="5" t="inlineStr"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
+      <c r="J253" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -11084,7 +10943,7 @@
         </is>
       </c>
       <c r="D258" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E258" s="5" t="n">
         <v>4</v>
@@ -11092,23 +10951,19 @@
       <c r="F258" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G258" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Management and Husbandry of Reptiles; Merck Veterinary Manual: Disorders and Diseases of Reptiles</t>
-        </is>
-      </c>
-      <c r="H258" s="5" t="inlineStr"/>
-      <c r="I258" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Management and Husbandry of Reptiles; Disorders and Diseases of Reptiles.</t>
-        </is>
-      </c>
-      <c r="J258" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K258" s="5" t="inlineStr"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
+      <c r="J258" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
@@ -11587,7 +11442,7 @@
         </is>
       </c>
       <c r="D271" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E271" s="5" t="n">
         <v>4</v>
@@ -11595,23 +11450,19 @@
       <c r="F271" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G271" s="5" t="inlineStr">
-        <is>
-          <t>rspca.org.uk listed 2 times: RSPCA: Degu Environment; RSPCA: Degu behaviour</t>
-        </is>
-      </c>
-      <c r="H271" s="5" t="inlineStr"/>
-      <c r="I271" s="5" t="inlineStr">
-        <is>
-          <t>Combine rspca.org.uk into one entry linking the site and naming the pages: Degu Environment; Degu behaviour.</t>
-        </is>
-      </c>
-      <c r="J271" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K271" s="5" t="inlineStr"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="5" t="n"/>
+      <c r="I271" s="5" t="n"/>
+      <c r="J271" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
@@ -11630,7 +11481,7 @@
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E272" s="5" t="n">
         <v>4</v>
@@ -11638,23 +11489,19 @@
       <c r="F272" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G272" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: Caring for a Degu: A Pet Parent's Guide, PetMD; How Long Do Chinchillas Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H272" s="5" t="inlineStr"/>
-      <c r="I272" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: A Pet Parent's Guide, PetMD; How Long Do Chinchillas Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J272" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K272" s="5" t="inlineStr"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+      <c r="J272" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
@@ -11790,7 +11637,7 @@
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E276" s="5" t="n">
         <v>4</v>
@@ -11798,23 +11645,19 @@
       <c r="F276" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G276" s="5" t="inlineStr">
-        <is>
-          <t>discus.com listed 2 times: Discus Fish Acclimation Instructions; How to Sex Discus Fish</t>
-        </is>
-      </c>
-      <c r="H276" s="5" t="inlineStr"/>
-      <c r="I276" s="5" t="inlineStr">
-        <is>
-          <t>Combine discus.com into one entry linking the site and naming the pages: Discus Fish Acclimation Instructions; How to Sex Discus Fish.</t>
-        </is>
-      </c>
-      <c r="J276" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K276" s="5" t="inlineStr"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="5" t="n"/>
+      <c r="I276" s="5" t="n"/>
+      <c r="J276" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
@@ -11833,7 +11676,7 @@
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E277" s="5" t="n">
         <v>4</v>
@@ -11841,23 +11684,19 @@
       <c r="F277" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G277" s="5" t="inlineStr">
-        <is>
-          <t>discus.com listed 3 times: Hole in the Head Disease: Head &amp; Lateral Line Erosion in Discus; Treatment and Causes of Discus Ich; Common Symptoms and Their Treatments</t>
-        </is>
-      </c>
-      <c r="H277" s="5" t="inlineStr"/>
-      <c r="I277" s="5" t="inlineStr">
-        <is>
-          <t>Combine discus.com into one entry linking the site and naming the pages: Head &amp; Lateral Line Erosion in Discus; Treatment and Causes of Discus Ich; Common Symptoms and Their Treatments. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J277" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K277" s="5" t="inlineStr"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
+      <c r="J277" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K277" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
@@ -11876,7 +11715,7 @@
         </is>
       </c>
       <c r="D278" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E278" s="5" t="n">
         <v>4</v>
@@ -11884,23 +11723,19 @@
       <c r="F278" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G278" s="5" t="inlineStr">
-        <is>
-          <t>discus.com listed 3 times: Filtration Basics; Discus Tank Substrates; The Natural Habitat of the Discus Fish</t>
-        </is>
-      </c>
-      <c r="H278" s="5" t="inlineStr"/>
-      <c r="I278" s="5" t="inlineStr">
-        <is>
-          <t>Combine discus.com into one entry linking the site and naming the pages: Filtration Basics; Discus Tank Substrates; The Natural Habitat of the Discus Fish. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J278" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K278" s="5" t="inlineStr"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
+      <c r="J278" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
@@ -12629,7 +12464,7 @@
         </is>
       </c>
       <c r="D297" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E297" s="5" t="n">
         <v>3</v>
@@ -12637,23 +12472,19 @@
       <c r="F297" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G297" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Management of Ferrets; Merck Veterinary Manual: Endocrine Disorders of Ferrets</t>
-        </is>
-      </c>
-      <c r="H297" s="5" t="inlineStr"/>
-      <c r="I297" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Management of Ferrets; Endocrine Disorders of Ferrets.</t>
-        </is>
-      </c>
-      <c r="J297" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K297" s="5" t="inlineStr"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="5" t="n"/>
+      <c r="I297" s="5" t="n"/>
+      <c r="J297" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K297" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
@@ -13264,7 +13095,7 @@
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E314" s="5" t="n">
         <v>4</v>
@@ -13272,23 +13103,19 @@
       <c r="F314" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G314" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Fire Skink Care Sheet; ReptiFiles: Leopard Gecko Tail Loss</t>
-        </is>
-      </c>
-      <c r="H314" s="5" t="inlineStr"/>
-      <c r="I314" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Fire Skink Care Sheet; Leopard Gecko Tail Loss.</t>
-        </is>
-      </c>
-      <c r="J314" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K314" s="5" t="inlineStr"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="5" t="n"/>
+      <c r="I314" s="5" t="n"/>
+      <c r="J314" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
@@ -13342,7 +13169,7 @@
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E316" s="5" t="n">
         <v>2</v>
@@ -13352,13 +13179,13 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Management of Aquarium Fish; Merck Veterinary Manual: Routine Health Care of Fish; Merck Veterinary Manual: Overview of Aquarium Fish</t>
-        </is>
-      </c>
-      <c r="H316" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H316" s="5" t="n"/>
       <c r="I316" s="5" t="inlineStr">
         <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Management of Aquarium Fish; Routine Health Care of Fish; Overview of Aquarium Fish.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J316" s="6" t="inlineStr">
@@ -13366,7 +13193,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K316" s="5" t="inlineStr"/>
+      <c r="K316" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
@@ -13385,7 +13216,7 @@
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E317" s="5" t="n">
         <v>3</v>
@@ -13393,23 +13224,19 @@
       <c r="F317" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G317" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Ball Python Terrarium Size and Lighting; ReptiFiles: Crested Gecko Temperatures and Humidity; ReptiFiles: Corn Snake Terrarium Size</t>
-        </is>
-      </c>
-      <c r="H317" s="5" t="inlineStr"/>
-      <c r="I317" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Ball Python Terrarium Size and Lighting; Crested Gecko Temperatures and Humidity; Corn Snake Terrarium Size.</t>
-        </is>
-      </c>
-      <c r="J317" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K317" s="5" t="inlineStr"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="5" t="n"/>
+      <c r="I317" s="5" t="n"/>
+      <c r="J317" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K317" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
@@ -13498,7 +13325,7 @@
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E320" s="5" t="n">
         <v>4</v>
@@ -13506,23 +13333,19 @@
       <c r="F320" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G320" s="5" t="inlineStr">
-        <is>
-          <t>squirrelrefuge.org listed 2 times: Metabolic Bone Disease in Squirrels, Squirrel Refuge; Flying Squirrel Diet, Squirrel Refuge</t>
-        </is>
-      </c>
-      <c r="H320" s="5" t="inlineStr"/>
-      <c r="I320" s="5" t="inlineStr">
-        <is>
-          <t>Combine squirrelrefuge.org into one entry linking the site and naming the pages: Metabolic Bone Disease in Squirrels, Squirrel Refuge; Flying Squirrel Diet, Squirrel Refuge.</t>
-        </is>
-      </c>
-      <c r="J320" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K320" s="5" t="inlineStr"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="5" t="n"/>
+      <c r="I320" s="5" t="n"/>
+      <c r="J320" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K320" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
@@ -13763,7 +13586,7 @@
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E327" s="5" t="n">
         <v>3</v>
@@ -13771,23 +13594,19 @@
       <c r="F327" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G327" s="5" t="inlineStr">
-        <is>
-          <t>dogster.com listed 2 times: Dogster: How Much Should a French Bulldog Eat; Dogster: Why Do French Bulldogs Fart So Much</t>
-        </is>
-      </c>
-      <c r="H327" s="5" t="inlineStr"/>
-      <c r="I327" s="5" t="inlineStr">
-        <is>
-          <t>Combine dogster.com into one entry linking the site and naming the pages: How Much Should a French Bulldog Eat; Why Do French Bulldogs Fart So Much.</t>
-        </is>
-      </c>
-      <c r="J327" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K327" s="5" t="inlineStr"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="5" t="n"/>
+      <c r="I327" s="5" t="n"/>
+      <c r="J327" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K327" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
@@ -13806,7 +13625,7 @@
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E328" s="5" t="n">
         <v>2</v>
@@ -13816,7 +13635,7 @@
       </c>
       <c r="G328" s="5" t="inlineStr">
         <is>
-          <t>usgs.gov listed 3 times: USGS Water Science School: pH and Water; USGS Water Science School: Hardness of Water; USGS Water Science School: Alkalinity and Water | merckvetmanual.com listed 2 times: Merck Veterinary Manual: Management of Aquarium Fish; Merck Veterinary Manual: Normal Reference Ranges for Routine Water Quality Analysis</t>
+          <t>usgs.gov listed 3 times: USGS Water Science School: pH and Water; USGS Water Science School: Hardness of Water; USGS Water Science School: Alkalinity and Water</t>
         </is>
       </c>
       <c r="H328" s="5" t="inlineStr">
@@ -13826,7 +13645,7 @@
       </c>
       <c r="I328" s="5" t="inlineStr">
         <is>
-          <t>Combine usgs.gov into one entry naming the pages unless each backs a distinct rule or listing. Combine merckvetmanual.com into one entry linking the site and naming the pages: Management of Aquarium Fish; Normal Reference Ranges for Routine Water Quality Analysis.</t>
+          <t>Combine usgs.gov into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr">
@@ -13834,7 +13653,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K328" s="5" t="inlineStr"/>
+      <c r="K328" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
@@ -13900,7 +13723,7 @@
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E330" s="5" t="n">
         <v>5</v>
@@ -13908,23 +13731,19 @@
       <c r="F330" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G330" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Gargoyle Gecko Care Guide; ReptiFiles: Gargoyle Gecko Substrate</t>
-        </is>
-      </c>
-      <c r="H330" s="5" t="inlineStr"/>
-      <c r="I330" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Gargoyle Gecko Care Guide; Gargoyle Gecko Substrate. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J330" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K330" s="5" t="inlineStr"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="5" t="n"/>
+      <c r="I330" s="5" t="n"/>
+      <c r="J330" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K330" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
@@ -13943,7 +13762,7 @@
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E331" s="5" t="n">
         <v>5</v>
@@ -13953,7 +13772,7 @@
       </c>
       <c r="G331" s="5" t="inlineStr">
         <is>
-          <t>sciencedirect.com listed 2 times: Bashaw MJ et al. (2016). Leopard geckos respond to five types of environmental enrichment. Applied Animal Behaviour Science; Burghardt GM (2013). Environmental enrichment and cognitive complexity in reptiles and amphibians | reptifiles.com listed 2 times: ReptiFiles: Decorating Your Gargoyle Gecko Terrarium; ReptiFiles: Floppy Tail Syndrome (FTS)</t>
+          <t>sciencedirect.com listed 2 times: Bashaw MJ et al. (2016). Leopard geckos respond to five types of environmental enrichment. Applied Animal Behaviour Science; Burghardt GM (2013). Environmental enrichment and cognitive complexity in reptiles and amphibians</t>
         </is>
       </c>
       <c r="H331" s="5" t="inlineStr">
@@ -13963,7 +13782,7 @@
       </c>
       <c r="I331" s="5" t="inlineStr">
         <is>
-          <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Combine reptifiles.com into one entry linking the site and naming the pages: Decorating Your Gargoyle Gecko Terrarium; Floppy Tail Syndrome (FTS). Combining brings it from 6 to 5, inside 3 to 5.</t>
+          <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J331" s="6" t="inlineStr">
@@ -13971,7 +13790,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K331" s="5" t="inlineStr"/>
+      <c r="K331" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
@@ -14025,7 +13848,7 @@
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E333" s="5" t="n">
         <v>5</v>
@@ -14033,23 +13856,19 @@
       <c r="F333" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G333" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Gargoyle Gecko Handling; ReptiFiles: Gargoyle Gecko Sexing</t>
-        </is>
-      </c>
-      <c r="H333" s="5" t="inlineStr"/>
-      <c r="I333" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Gargoyle Gecko Handling; Gargoyle Gecko Sexing. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J333" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K333" s="5" t="inlineStr"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="5" t="n"/>
+      <c r="I333" s="5" t="n"/>
+      <c r="J333" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K333" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
@@ -14068,7 +13887,7 @@
         </is>
       </c>
       <c r="D334" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E334" s="5" t="n">
         <v>2</v>
@@ -14078,13 +13897,13 @@
       </c>
       <c r="G334" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Metabolic Bone Disease (MBD); ReptiFiles: Floppy Tail Syndrome (FTS)</t>
-        </is>
-      </c>
-      <c r="H334" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H334" s="5" t="n"/>
       <c r="I334" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Metabolic Bone Disease (MBD); Floppy Tail Syndrome (FTS).</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J334" s="6" t="inlineStr">
@@ -14092,7 +13911,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K334" s="5" t="inlineStr"/>
+      <c r="K334" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
@@ -14146,7 +13969,7 @@
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E336" s="5" t="n">
         <v>3</v>
@@ -14154,23 +13977,19 @@
       <c r="F336" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G336" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Gargoyle Gecko Care Guide; ReptiFiles: Crested Gecko Care; ReptiFiles: Mourning Gecko Care</t>
-        </is>
-      </c>
-      <c r="H336" s="5" t="inlineStr"/>
-      <c r="I336" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Gargoyle Gecko Care Guide; Crested Gecko Care; Mourning Gecko Care.</t>
-        </is>
-      </c>
-      <c r="J336" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K336" s="5" t="inlineStr"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="5" t="n"/>
+      <c r="I336" s="5" t="n"/>
+      <c r="J336" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K336" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
@@ -14341,7 +14160,7 @@
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E341" s="5" t="n">
         <v>2</v>
@@ -14351,13 +14170,13 @@
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Nutritional, Metabolic, and Endocrine Diseases of Reptiles; Merck Veterinary Manual: Parasitic Diseases of Reptiles | petmd.com listed 2 times: PetMD: Snake Mouth Rot, Symptoms, Causes, and Treatment; PetMD: Garter Snake Care Sheet</t>
-        </is>
-      </c>
-      <c r="H341" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H341" s="5" t="n"/>
       <c r="I341" s="5" t="inlineStr">
         <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Nutritional, Metabolic, and Endocrine Diseases of Reptiles; Parasitic Diseases of Reptiles. Combine petmd.com into one entry linking the site and naming the pages: Snake Mouth Rot, Symptoms, Causes, and Treatment; Garter Snake Care Sheet.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J341" s="6" t="inlineStr">
@@ -14365,7 +14184,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K341" s="5" t="inlineStr"/>
+      <c r="K341" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
@@ -14571,7 +14394,7 @@
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E347" s="5" t="n">
         <v>3</v>
@@ -14579,23 +14402,19 @@
       <c r="F347" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G347" s="5" t="inlineStr">
-        <is>
-          <t>agsgerbils.org listed 4 times: American Gerbil Society: Taming (Gerbilpedia); American Gerbil Society: Split Cage Method (Gerbilpedia); American Gerbil Society: Declanning (Gerbilpedia); American Gerbil Society: Aggression (Gerbilpedia)</t>
-        </is>
-      </c>
-      <c r="H347" s="5" t="inlineStr"/>
-      <c r="I347" s="5" t="inlineStr">
-        <is>
-          <t>Combine agsgerbils.org into one entry linking the site and naming the pages: Taming (Gerbilpedia); Split Cage Method (Gerbilpedia); Declanning (Gerbilpedia); Aggression (Gerbilpedia). Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J347" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K347" s="5" t="inlineStr"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="5" t="n"/>
+      <c r="I347" s="5" t="n"/>
+      <c r="J347" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K347" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
@@ -14614,7 +14433,7 @@
         </is>
       </c>
       <c r="D348" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E348" s="5" t="n">
         <v>5</v>
@@ -14622,27 +14441,19 @@
       <c r="F348" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G348" s="5" t="inlineStr">
-        <is>
-          <t>cvm.missouri.edu listed 2 times: University of Missouri College of Veterinary Medicine: Squamous Cell Carcinoma (Gerbils); University of Missouri College of Veterinary Medicine: Malocclusion (Gerbils)</t>
-        </is>
-      </c>
-      <c r="H348" s="5" t="inlineStr">
-        <is>
-          <t>cvm.missouri.edu: 1 of these pages are also linked in the body, so a reader lands on that exact page.</t>
-        </is>
-      </c>
-      <c r="I348" s="5" t="inlineStr">
-        <is>
-          <t>Combine cvm.missouri.edu into one entry linking the site and naming the pages: University of Missouri College of Veterinary Medicine: Squamous Cell Carcinoma (Gerbils); University of Missouri College of Veterinary Medicine: Malocclusion (Gerbils). Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J348" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K348" s="5" t="inlineStr"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="5" t="n"/>
+      <c r="I348" s="5" t="n"/>
+      <c r="J348" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K348" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
@@ -14743,7 +14554,7 @@
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E351" s="5" t="n">
         <v>4</v>
@@ -14751,23 +14562,19 @@
       <c r="F351" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G351" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: Vitamin C Deficiency in Guinea Pigs, PetMD; How Long Do Guinea Pigs Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H351" s="5" t="inlineStr"/>
-      <c r="I351" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Vitamin C Deficiency in Guinea Pigs, PetMD; How Long Do Guinea Pigs Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J351" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K351" s="5" t="inlineStr"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="5" t="n"/>
+      <c r="I351" s="5" t="n"/>
+      <c r="J351" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K351" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
@@ -14786,7 +14593,7 @@
         </is>
       </c>
       <c r="D352" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E352" s="5" t="n">
         <v>3</v>
@@ -14794,23 +14601,19 @@
       <c r="F352" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G352" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Gerbils, Merck Veterinary Manual; Hamsters, Merck Veterinary Manual</t>
-        </is>
-      </c>
-      <c r="H352" s="5" t="inlineStr"/>
-      <c r="I352" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Gerbils, Merck Veterinary Manual; Hamsters, Merck Veterinary Manual.</t>
-        </is>
-      </c>
-      <c r="J352" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K352" s="5" t="inlineStr"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="5" t="n"/>
+      <c r="I352" s="5" t="n"/>
+      <c r="J352" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K352" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
@@ -14829,7 +14632,7 @@
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E353" s="5" t="n">
         <v>2</v>
@@ -14839,13 +14642,13 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 3 times: VCA Hospitals: German Shepherd Dog; VCA Hospitals: Exocrine Pancreatic Insufficiency in Dogs; VCA Hospitals: Anorexia in Dogs</t>
-        </is>
-      </c>
-      <c r="H353" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H353" s="5" t="n"/>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: German Shepherd Dog; Exocrine Pancreatic Insufficiency in Dogs; Anorexia in Dogs.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J353" s="6" t="inlineStr">
@@ -14853,7 +14656,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K353" s="5" t="inlineStr"/>
+      <c r="K353" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
@@ -15250,7 +15057,7 @@
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E364" s="5" t="n">
         <v>4</v>
@@ -15258,23 +15065,19 @@
       <c r="F364" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G364" s="5" t="inlineStr">
-        <is>
-          <t>bugsincyberspace.com listed 2 times: Bugs in Cyberspace: Live Pet Millipede Care Sheet; Bugs in Cyberspace: Pet Cage Pest Control, Flies, Mites, Beetles, Fungus and More</t>
-        </is>
-      </c>
-      <c r="H364" s="5" t="inlineStr"/>
-      <c r="I364" s="5" t="inlineStr">
-        <is>
-          <t>Combine bugsincyberspace.com into one entry linking the site and naming the pages: Live Pet Millipede Care Sheet; Pet Cage Pest Control, Flies, Mites, Beetles, Fungus and More.</t>
-        </is>
-      </c>
-      <c r="J364" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K364" s="5" t="inlineStr"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="5" t="n"/>
+      <c r="I364" s="5" t="n"/>
+      <c r="J364" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K364" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
@@ -15390,12 +15193,12 @@
       </c>
       <c r="H367" s="5" t="inlineStr">
         <is>
-          <t>pmc.ncbi.nlm.nih.gov: separate studies, each with its own authors and year; one combined entry could not credit them. pubmed.ncbi.nlm.nih.gov: separate studies, each with its own authors and year; one combined entry could not credit them.</t>
+          <t>Kept separate: separate studies, each with its own authors and year.</t>
         </is>
       </c>
       <c r="I367" s="5" t="inlineStr">
         <is>
-          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Keep pubmed.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Combine iucn.org into one entry linking the site and naming the pages: Four giraffe species officially recognised in major conservation reclassification (IUCN press release, August 2025); An Evaluation of the Taxonomic Status of Giraffe (Giraffa spp.), IUCN SSC Giraffe and Okapi Specialist Group Taxonomic Task Force, August 2025. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J367" s="6" t="inlineStr">
@@ -15403,7 +15206,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K367" s="5" t="inlineStr"/>
+      <c r="K367" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="5" t="inlineStr">
@@ -15457,7 +15264,7 @@
         </is>
       </c>
       <c r="D369" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E369" s="5" t="n">
         <v>3</v>
@@ -15465,23 +15272,19 @@
       <c r="F369" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G369" s="5" t="inlineStr">
-        <is>
-          <t>akc.org listed 2 times: Golden Retriever Dog Breed Information, American Kennel Club; German Shepherd Dog Breed Information, American Kennel Club</t>
-        </is>
-      </c>
-      <c r="H369" s="5" t="inlineStr"/>
-      <c r="I369" s="5" t="inlineStr">
-        <is>
-          <t>Combine akc.org into one entry linking the site and naming the pages: Golden Retriever Dog Breed Information, American Kennel Club; German Shepherd Dog Breed Information, American Kennel Club.</t>
-        </is>
-      </c>
-      <c r="J369" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K369" s="5" t="inlineStr"/>
+      <c r="G369" s="5" t="n"/>
+      <c r="H369" s="5" t="n"/>
+      <c r="I369" s="5" t="n"/>
+      <c r="J369" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K369" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="5" t="inlineStr">
@@ -15570,7 +15373,7 @@
         </is>
       </c>
       <c r="D372" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E372" s="5" t="n">
         <v>3</v>
@@ -15578,23 +15381,19 @@
       <c r="F372" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G372" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: PetMD: Goldfish Care Sheet (Melissa Witherell, DVM); PetMD: Swim Bladder Disorders in Fish (Dr. Jessie Sanders, DVM, DABVP Fish Practice) | ask.ifas.ufl.edu listed 2 times: University of Florida IFAS Extension: Fish Nutrition; University of Florida IFAS Extension: Preparing Your Own Fish Feeds</t>
-        </is>
-      </c>
-      <c r="H372" s="5" t="inlineStr"/>
-      <c r="I372" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Goldfish Care Sheet (Melissa Witherell, DVM); Swim Bladder Disorders in Fish (Dr. Jessie Sanders, DVM, DABVP Fish Practice). Combine ask.ifas.ufl.edu into one entry linking the site and naming the pages: Fish Nutrition; Preparing Your Own Fish Feeds.</t>
-        </is>
-      </c>
-      <c r="J372" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K372" s="5" t="inlineStr"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="5" t="n"/>
+      <c r="I372" s="5" t="n"/>
+      <c r="J372" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K372" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
@@ -15660,7 +15459,7 @@
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E374" s="5" t="n">
         <v>4</v>
@@ -15668,23 +15467,19 @@
       <c r="F374" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G374" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Parasitic Diseases of Fish; Merck Veterinary Manual: Bacterial Diseases of Fish | cafishvet.com listed 2 times: Aquatic Veterinary Services (Dr. Jessie Sanders, DVM, DABVP): Fish Popeye; Aquatic Veterinary Services (Dr. Jessie Sanders, DVM, DABVP): Fin Rot in Pet Fish</t>
-        </is>
-      </c>
-      <c r="H374" s="5" t="inlineStr"/>
-      <c r="I374" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Parasitic Diseases of Fish; Bacterial Diseases of Fish. Combine cafishvet.com into one entry linking the site and naming the pages: Aquatic Veterinary Services (Dr. Jessie Sanders, DVM, DABVP): Fish Popeye; Aquatic Veterinary Services (Dr. Jessie Sanders, DVM, DABVP): Fin Rot in Pet Fish. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J374" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K374" s="5" t="inlineStr"/>
+      <c r="G374" s="5" t="n"/>
+      <c r="H374" s="5" t="n"/>
+      <c r="I374" s="5" t="n"/>
+      <c r="J374" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K374" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
@@ -16218,7 +16013,7 @@
         </is>
       </c>
       <c r="D388" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E388" s="5" t="n">
         <v>2</v>
@@ -16228,13 +16023,13 @@
       </c>
       <c r="G388" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Iguanas, Diseases; VCA Animal Hospitals: Reptiles, Dystocia | lafeber.com listed 3 times: LafeberVet: Metabolic Bone Disease in Reptiles and Amphibians, client handout by Christal Pollock DVM; LafeberVet: Presenting Problem, Burns in Snakes and Lizards; LafeberVet: Basic Information Sheet for Green or Common Iguana</t>
-        </is>
-      </c>
-      <c r="H388" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H388" s="5" t="n"/>
       <c r="I388" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Iguanas, Diseases; Reptiles, Dystocia. Combine lafeber.com into one entry linking the site and naming the pages: Metabolic Bone Disease in Reptiles and Amphibians, client handout by Christal Pollock DVM; Presenting Problem, Burns in Snakes and Lizards; Basic Information Sheet for Green or Common Iguana.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J388" s="6" t="inlineStr">
@@ -16242,7 +16037,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K388" s="5" t="inlineStr"/>
+      <c r="K388" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
@@ -16858,7 +16657,7 @@
         </is>
       </c>
       <c r="D404" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E404" s="5" t="n">
         <v>4</v>
@@ -16866,23 +16665,19 @@
       <c r="F404" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G404" s="5" t="inlineStr">
-        <is>
-          <t>practicalfishkeeping.co.uk listed 2 times: Practical Fishkeeping: How to breed livebearing fish; Practical Fishkeeping: The Guppy, first loves never die</t>
-        </is>
-      </c>
-      <c r="H404" s="5" t="inlineStr"/>
-      <c r="I404" s="5" t="inlineStr">
-        <is>
-          <t>Combine practicalfishkeeping.co.uk into one entry linking the site and naming the pages: How to breed livebearing fish; The Guppy, first loves never die.</t>
-        </is>
-      </c>
-      <c r="J404" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K404" s="5" t="inlineStr"/>
+      <c r="G404" s="5" t="n"/>
+      <c r="H404" s="5" t="n"/>
+      <c r="I404" s="5" t="n"/>
+      <c r="J404" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="5" t="inlineStr">
@@ -17369,7 +17164,7 @@
         </is>
       </c>
       <c r="D417" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E417" s="5" t="n">
         <v>3</v>
@@ -17377,23 +17172,19 @@
       <c r="F417" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G417" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: How Long Do Hamsters Live?, PetMD; How Long Do Guinea Pigs Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H417" s="5" t="inlineStr"/>
-      <c r="I417" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: How Long Do Hamsters Live?, PetMD; How Long Do Guinea Pigs Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J417" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K417" s="5" t="inlineStr"/>
+      <c r="G417" s="5" t="n"/>
+      <c r="H417" s="5" t="n"/>
+      <c r="I417" s="5" t="n"/>
+      <c r="J417" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K417" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="5" t="inlineStr">
@@ -17525,7 +17316,7 @@
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E421" s="5" t="n">
         <v>4</v>
@@ -17533,23 +17324,19 @@
       <c r="F421" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G421" s="5" t="inlineStr">
-        <is>
-          <t>birdexoticsvet.com listed 2 times: Long Island Bird and Exotics Veterinary Clinic: Male or Female? How to Identify the Sex of Popular Exotic Pets; Long Island Bird and Exotics Veterinary Clinic: Hedgehog Grooming and Skin Care</t>
-        </is>
-      </c>
-      <c r="H421" s="5" t="inlineStr"/>
-      <c r="I421" s="5" t="inlineStr">
-        <is>
-          <t>Combine birdexoticsvet.com into one entry linking the site and naming the pages: Long Island Bird and Exotics Veterinary Clinic: Male or Female? How to Identify the Sex of Popular Exotic Pets; Long Island Bird and Exotics Veterinary Clinic: Hedgehog Grooming and Skin Care.</t>
-        </is>
-      </c>
-      <c r="J421" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K421" s="5" t="inlineStr"/>
+      <c r="G421" s="5" t="n"/>
+      <c r="H421" s="5" t="n"/>
+      <c r="I421" s="5" t="n"/>
+      <c r="J421" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K421" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="5" t="inlineStr">
@@ -17681,7 +17468,7 @@
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E425" s="5" t="n">
         <v>3</v>
@@ -17689,23 +17476,19 @@
       <c r="F425" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G425" s="5" t="inlineStr">
-        <is>
-          <t>hedgehogstreet.org listed 2 times: Hedgehog Street (People's Trust for Endangered Species and British Hedgehog Preservation Society). What should we be feeding hedgehogs?; Hedgehog Street. Hedgehog biology | wildlifeonline.me.uk listed 2 times: Wildlife Online. European hedgehog: interaction with humans, supplemental feeding; Wildlife Online. European hedgehog behaviour: self-anointing</t>
-        </is>
-      </c>
-      <c r="H425" s="5" t="inlineStr"/>
-      <c r="I425" s="5" t="inlineStr">
-        <is>
-          <t>Combine hedgehogstreet.org into one entry linking the site and naming the pages: Hedgehog Street (People's Trust for Endangered Species and British Hedgehog Preservation Society). What should we be feeding hedgehogs?; Hedgehog Street. Hedgehog biology. Combine wildlifeonline.me.uk into one entry linking the site and naming the pages: interaction with humans, supplemental feeding; Wildlife Online. European hedgehog behaviour: self-anointing.</t>
-        </is>
-      </c>
-      <c r="J425" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K425" s="5" t="inlineStr"/>
+      <c r="G425" s="5" t="n"/>
+      <c r="H425" s="5" t="n"/>
+      <c r="I425" s="5" t="n"/>
+      <c r="J425" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K425" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="5" t="inlineStr">
@@ -17864,7 +17647,7 @@
         </is>
       </c>
       <c r="D430" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E430" s="5" t="n">
         <v>4</v>
@@ -17872,23 +17655,19 @@
       <c r="F430" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G430" s="5" t="inlineStr">
-        <is>
-          <t>crabstreetjournal.org listed 2 times: Crab Street Journal: Anatomy of Land Hermit Crabs, a Guide to the Coenobita Body; Crab Street Journal: Choosing a Pet Hermit Crab</t>
-        </is>
-      </c>
-      <c r="H430" s="5" t="inlineStr"/>
-      <c r="I430" s="5" t="inlineStr">
-        <is>
-          <t>Combine crabstreetjournal.org into one entry linking the site and naming the pages: Anatomy of Land Hermit Crabs, a Guide to the Coenobita Body; Choosing a Pet Hermit Crab.</t>
-        </is>
-      </c>
-      <c r="J430" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K430" s="5" t="inlineStr"/>
+      <c r="G430" s="5" t="n"/>
+      <c r="H430" s="5" t="n"/>
+      <c r="I430" s="5" t="n"/>
+      <c r="J430" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K430" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="5" t="inlineStr">
@@ -17907,7 +17686,7 @@
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E431" s="5" t="n">
         <v>2</v>
@@ -17917,13 +17696,13 @@
       </c>
       <c r="G431" s="5" t="inlineStr">
         <is>
-          <t>crabstreetjournal.org listed 4 times: Crab Street Journal: Caring for Hermit Crabs with Limb Loss; Crab Street Journal: Post Purchase Death Reduction Method; Crab Street Journal: Hermit Crab Molting Explained, the Biology Behind the Process; Crab Street Journal: Hermit Crab Out of Shell, What to Do Right Now</t>
-        </is>
-      </c>
-      <c r="H431" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H431" s="5" t="n"/>
       <c r="I431" s="5" t="inlineStr">
         <is>
-          <t>Combine crabstreetjournal.org into one entry linking the site and naming the pages: Caring for Hermit Crabs with Limb Loss; Post Purchase Death Reduction Method; Hermit Crab Molting Explained, the Biology Behind the Process; Hermit Crab Out of Shell, What to Do Right Now.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J431" s="6" t="inlineStr">
@@ -17931,7 +17710,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K431" s="5" t="inlineStr"/>
+      <c r="K431" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="5" t="inlineStr">
@@ -17985,7 +17768,7 @@
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E433" s="5" t="n">
         <v>5</v>
@@ -17995,7 +17778,7 @@
       </c>
       <c r="G433" s="5" t="inlineStr">
         <is>
-          <t>ofa.org listed 2 times: OFA: Hip Dysplasia; OFA: Elbow Dysplasia | pmc.ncbi.nlm.nih.gov listed 2 times: Feline hip dysplasia in the OFA registry, 2,708 Maine Coons; Swedish hip dysplasia screening programme, 5,038 Maine Coons</t>
+          <t>pmc.ncbi.nlm.nih.gov listed 2 times: Feline hip dysplasia in the OFA registry, 2,708 Maine Coons; Swedish hip dysplasia screening programme, 5,038 Maine Coons</t>
         </is>
       </c>
       <c r="H433" s="5" t="inlineStr">
@@ -18005,7 +17788,7 @@
       </c>
       <c r="I433" s="5" t="inlineStr">
         <is>
-          <t>Combine ofa.org into one entry linking the site and naming the pages: Hip Dysplasia; Elbow Dysplasia. Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Combining brings it from 6 to 5, inside 3 to 5.</t>
+          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J433" s="6" t="inlineStr">
@@ -18013,7 +17796,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K433" s="5" t="inlineStr"/>
+      <c r="K433" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="5" t="inlineStr">
@@ -18184,7 +17971,7 @@
         </is>
       </c>
       <c r="D438" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E438" s="5" t="n">
         <v>3</v>
@@ -18192,23 +17979,19 @@
       <c r="F438" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G438" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 4 times: ReptiFiles: Western Hognose Snake Care; ReptiFiles: Hognose Snake Diseases and General Health; ReptiFiles: Regurgitation in Snakes; ReptiFiles: Hognose Snake Shedding</t>
-        </is>
-      </c>
-      <c r="H438" s="5" t="inlineStr"/>
-      <c r="I438" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Western Hognose Snake Care; Hognose Snake Diseases and General Health; Regurgitation in Snakes; Hognose Snake Shedding. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J438" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K438" s="5" t="inlineStr"/>
+      <c r="G438" s="5" t="n"/>
+      <c r="H438" s="5" t="n"/>
+      <c r="I438" s="5" t="n"/>
+      <c r="J438" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K438" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="5" t="inlineStr">
@@ -18274,7 +18057,7 @@
         </is>
       </c>
       <c r="D440" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E440" s="5" t="n">
         <v>2</v>
@@ -18284,13 +18067,13 @@
       </c>
       <c r="G440" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 4 times: ReptiFiles: Western Hognose Snake Care; ReptiFiles: Hognose Snake Temperatures, Humidity and Lighting; ReptiFiles: Hognose Snake Enclosure Size; ReptiFiles: Hognose Substrate Options</t>
-        </is>
-      </c>
-      <c r="H440" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H440" s="5" t="n"/>
       <c r="I440" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Western Hognose Snake Care; Hognose Snake Temperatures, Humidity and Lighting; Hognose Snake Enclosure Size; Hognose Substrate Options.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J440" s="6" t="inlineStr">
@@ -18298,7 +18081,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K440" s="5" t="inlineStr"/>
+      <c r="K440" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="5" t="inlineStr">
@@ -18330,18 +18117,26 @@
           <t>honeybadger.com listed 2 times: Begg, C.M., Begg, K.S., Du Toit, J.T. &amp; Mills, M.G.L. 2003. Sexual and seasonal variation in the diet and foraging behaviour of a sexually dimorphic carnivore, the honey badger (Mellivora capensis). Journal of Zoology 260:301-316; Begg, C.M., Begg, K.S., Du Toit, J.T. &amp; Mills, M.G.L. 2005. Life-history variables of an atypical mustelid, the honey badger Mellivora capensis. Journal of Zoology 265:17-22</t>
         </is>
       </c>
-      <c r="H441" s="5" t="inlineStr"/>
+      <c r="H441" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: separate Begg et al. papers (2003, 2005).</t>
+        </is>
+      </c>
       <c r="I441" s="5" t="inlineStr">
         <is>
-          <t>Combine honeybadger.com into one entry linking the site and naming the pages: Begg, C.M., Begg, K.S., Du Toit, J.T. &amp; Mills, M.G.L. 2003. Sexual and seasonal variation in the diet and foraging behaviour of a sexually dimorphic carnivore, the honey badger (Mellivora capensis). Journal of Zoology 260:301-316; Begg, C.M., Begg, K.S., Du Toit, J.T. &amp; Mills, M.G.L. 2005. Life-history variables of an atypical mustelid, the honey badger Mellivora capensis. Journal of Zoology 265:17-22. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J441" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K441" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J441" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K441" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="5" t="inlineStr">
@@ -18407,7 +18202,7 @@
         </is>
       </c>
       <c r="D443" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E443" s="5" t="n">
         <v>4</v>
@@ -18415,23 +18210,19 @@
       <c r="F443" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G443" s="5" t="inlineStr">
-        <is>
-          <t>floridamuseum.ufl.edu listed 2 times: International Shark Attack File: Global shark bites return to average in 2025 (Florida Museum of Natural History); International Shark Attack File, Florida Museum of Natural History</t>
-        </is>
-      </c>
-      <c r="H443" s="5" t="inlineStr"/>
-      <c r="I443" s="5" t="inlineStr">
-        <is>
-          <t>Combine floridamuseum.ufl.edu into one entry linking the site and naming the pages: Global shark bites return to average in 2025 (Florida Museum of Natural History); International Shark Attack File, Florida Museum of Natural History.</t>
-        </is>
-      </c>
-      <c r="J443" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K443" s="5" t="inlineStr"/>
+      <c r="G443" s="5" t="n"/>
+      <c r="H443" s="5" t="n"/>
+      <c r="I443" s="5" t="n"/>
+      <c r="J443" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K443" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="5" t="inlineStr">
@@ -18506,18 +18297,26 @@
           <t>lafeber.com listed 2 times: LafeberVet: Basic Information Sheet, Green or Common Iguana; Lafeber: Quaker Parakeet</t>
         </is>
       </c>
-      <c r="H445" s="5" t="inlineStr"/>
+      <c r="H445" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: LafeberVet (lafeber.com/vet, written for veterinarians) and Lafeber Co. pet owner pages are two different sites on one domain.</t>
+        </is>
+      </c>
       <c r="I445" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Basic Information Sheet, Green or Common Iguana; Quaker Parakeet.</t>
-        </is>
-      </c>
-      <c r="J445" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K445" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J445" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K445" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="5" t="inlineStr">
@@ -18583,7 +18382,7 @@
         </is>
       </c>
       <c r="D447" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E447" s="5" t="n">
         <v>4</v>
@@ -18593,21 +18392,21 @@
       </c>
       <c r="G447" s="5" t="inlineStr">
         <is>
-          <t>ofa.org listed 2 times: OFA: Companion Animal Eye Registry certification; OFA: crd4 progressive retinal atrophy and the RPGRIP1 caveat | merckvetmanual.com listed 2 times: Merck Veterinary Manual: The Ocular Fundus in Animals; Merck Veterinary Manual: The Cornea in Animals | Also consulted list of 20 unlinked entries (fine print by design).</t>
-        </is>
-      </c>
-      <c r="H447" s="5" t="inlineStr"/>
-      <c r="I447" s="5" t="inlineStr">
-        <is>
-          <t>Combine ofa.org into one entry linking the site and naming the pages: Companion Animal Eye Registry certification; crd4 progressive retinal atrophy and the RPGRIP1 caveat. Combine merckvetmanual.com into one entry linking the site and naming the pages: The Ocular Fundus in Animals; The Cornea in Animals. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J447" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K447" s="5" t="inlineStr"/>
+          <t>Also consulted list of 20 unlinked entries (fine print by design).</t>
+        </is>
+      </c>
+      <c r="H447" s="5" t="n"/>
+      <c r="I447" s="5" t="n"/>
+      <c r="J447" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K447" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="5" t="inlineStr">
@@ -18696,7 +18495,7 @@
         </is>
       </c>
       <c r="D450" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E450" s="5" t="n">
         <v>5</v>
@@ -18704,23 +18503,19 @@
       <c r="F450" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G450" s="5" t="inlineStr">
-        <is>
-          <t>pe.usps.com listed 2 times: USPS Postal Explorer, Publication 52: 525 Nonmailable Live Animals; USPS Postal Explorer, Publication 52: 526 Mailable Live Animals</t>
-        </is>
-      </c>
-      <c r="H450" s="5" t="inlineStr"/>
-      <c r="I450" s="5" t="inlineStr">
-        <is>
-          <t>Combine pe.usps.com into one entry linking the site and naming the pages: 525 Nonmailable Live Animals; 526 Mailable Live Animals. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J450" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K450" s="5" t="inlineStr"/>
+      <c r="G450" s="5" t="n"/>
+      <c r="H450" s="5" t="n"/>
+      <c r="I450" s="5" t="n"/>
+      <c r="J450" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K450" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="5" t="inlineStr">
@@ -18782,7 +18577,7 @@
         </is>
       </c>
       <c r="D452" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E452" s="5" t="n">
         <v>3</v>
@@ -18790,23 +18585,19 @@
       <c r="F452" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G452" s="5" t="inlineStr">
-        <is>
-          <t>npic.orst.edu listed 3 times: National Pesticide Information Center: Pyrethrins General Fact Sheet; National Pesticide Information Center: Fipronil Fact Sheet; National Pesticide Information Center: Imidacloprid General Fact Sheet</t>
-        </is>
-      </c>
-      <c r="H452" s="5" t="inlineStr"/>
-      <c r="I452" s="5" t="inlineStr">
-        <is>
-          <t>Combine npic.orst.edu into one entry linking the site and naming the pages: Pyrethrins General Fact Sheet; Fipronil Fact Sheet; Imidacloprid General Fact Sheet.</t>
-        </is>
-      </c>
-      <c r="J452" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K452" s="5" t="inlineStr"/>
+      <c r="G452" s="5" t="n"/>
+      <c r="H452" s="5" t="n"/>
+      <c r="I452" s="5" t="n"/>
+      <c r="J452" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K452" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="5" t="inlineStr">
@@ -18962,7 +18753,7 @@
         </is>
       </c>
       <c r="D456" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E456" s="5" t="n">
         <v>3</v>
@@ -18970,23 +18761,19 @@
       <c r="F456" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G456" s="5" t="inlineStr">
-        <is>
-          <t>chameleonacademy.com listed 2 times: Chameleon Academy: Jackson's Chameleon Care; Chameleon Academy: Trioceros jacksonii, Breeding Jackson's Chameleons</t>
-        </is>
-      </c>
-      <c r="H456" s="5" t="inlineStr"/>
-      <c r="I456" s="5" t="inlineStr">
-        <is>
-          <t>Combine chameleonacademy.com into one entry linking the site and naming the pages: Jackson's Chameleon Care; Trioceros jacksonii, Breeding Jackson's Chameleons.</t>
-        </is>
-      </c>
-      <c r="J456" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K456" s="5" t="inlineStr"/>
+      <c r="G456" s="5" t="n"/>
+      <c r="H456" s="5" t="n"/>
+      <c r="I456" s="5" t="n"/>
+      <c r="J456" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K456" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="5" t="inlineStr">
@@ -19122,7 +18909,7 @@
         </is>
       </c>
       <c r="D460" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E460" s="5" t="n">
         <v>3</v>
@@ -19130,23 +18917,19 @@
       <c r="F460" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G460" s="5" t="inlineStr">
-        <is>
-          <t>chameleonacademy.com listed 3 times: Chameleon Academy: Chameleon Medical, Respiratory Infection; Chameleon Academy: Trioceros jacksonii, Breeding Jackson's Chameleons; Chameleon Academy: What to Feed Hatchling Chameleons</t>
-        </is>
-      </c>
-      <c r="H460" s="5" t="inlineStr"/>
-      <c r="I460" s="5" t="inlineStr">
-        <is>
-          <t>Combine chameleonacademy.com into one entry linking the site and naming the pages: Chameleon Medical, Respiratory Infection; Trioceros jacksonii, Breeding Jackson's Chameleons; What to Feed Hatchling Chameleons.</t>
-        </is>
-      </c>
-      <c r="J460" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K460" s="5" t="inlineStr"/>
+      <c r="G460" s="5" t="n"/>
+      <c r="H460" s="5" t="n"/>
+      <c r="I460" s="5" t="n"/>
+      <c r="J460" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K460" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="5" t="inlineStr">
@@ -19450,7 +19233,7 @@
         </is>
       </c>
       <c r="D468" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E468" s="5" t="n">
         <v>4</v>
@@ -19458,23 +19241,19 @@
       <c r="F468" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G468" s="5" t="inlineStr">
-        <is>
-          <t>poramorart.ca listed 2 times: Por Amor Art: Pet Jumping Spider Care, Comprehensive Guide; Por Amor Art: Jumping Spider Enclosure Setup Guide</t>
-        </is>
-      </c>
-      <c r="H468" s="5" t="inlineStr"/>
-      <c r="I468" s="5" t="inlineStr">
-        <is>
-          <t>Combine poramorart.ca into one entry linking the site and naming the pages: Pet Jumping Spider Care, Comprehensive Guide; Jumping Spider Enclosure Setup Guide.</t>
-        </is>
-      </c>
-      <c r="J468" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K468" s="5" t="inlineStr"/>
+      <c r="G468" s="5" t="n"/>
+      <c r="H468" s="5" t="n"/>
+      <c r="I468" s="5" t="n"/>
+      <c r="J468" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K468" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="5" t="inlineStr">
@@ -19493,7 +19272,7 @@
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E469" s="5" t="n">
         <v>2</v>
@@ -19503,13 +19282,13 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>poramorart.ca listed 2 times: Por Amor Art: Jumping Spider Enclosure Setup Guide; Por Amor Art: Pet Jumping Spider Care, Comprehensive Guide</t>
-        </is>
-      </c>
-      <c r="H469" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H469" s="5" t="n"/>
       <c r="I469" s="5" t="inlineStr">
         <is>
-          <t>Combine poramorart.ca into one entry linking the site and naming the pages: Jumping Spider Enclosure Setup Guide; Pet Jumping Spider Care, Comprehensive Guide.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J469" s="6" t="inlineStr">
@@ -19517,7 +19296,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K469" s="5" t="inlineStr"/>
+      <c r="K469" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="5" t="inlineStr">
@@ -19606,7 +19389,7 @@
         </is>
       </c>
       <c r="D472" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E472" s="5" t="n">
         <v>3</v>
@@ -19614,23 +19397,19 @@
       <c r="F472" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G472" s="5" t="inlineStr">
-        <is>
-          <t>kodamakoifarm.com listed 2 times: Kodama Koi Farm: How Much Do Koi Fish Cost?; Kodama Koi Farm: How Long Do Koi Fish Live?</t>
-        </is>
-      </c>
-      <c r="H472" s="5" t="inlineStr"/>
-      <c r="I472" s="5" t="inlineStr">
-        <is>
-          <t>Combine kodamakoifarm.com into one entry linking the site and naming the pages: How Much Do Koi Fish Cost?; How Long Do Koi Fish Live?.</t>
-        </is>
-      </c>
-      <c r="J472" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K472" s="5" t="inlineStr"/>
+      <c r="G472" s="5" t="n"/>
+      <c r="H472" s="5" t="n"/>
+      <c r="I472" s="5" t="n"/>
+      <c r="J472" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K472" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="5" t="inlineStr">
@@ -19692,7 +19471,7 @@
         </is>
       </c>
       <c r="D474" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E474" s="5" t="n">
         <v>4</v>
@@ -19700,23 +19479,19 @@
       <c r="F474" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G474" s="5" t="inlineStr">
-        <is>
-          <t>pondinformer.com listed 2 times: Pond Informer: What Can Koi Eat; Pond Informer: Why Is My Koi Not Eating</t>
-        </is>
-      </c>
-      <c r="H474" s="5" t="inlineStr"/>
-      <c r="I474" s="5" t="inlineStr">
-        <is>
-          <t>Combine pondinformer.com into one entry linking the site and naming the pages: What Can Koi Eat; Why Is My Koi Not Eating.</t>
-        </is>
-      </c>
-      <c r="J474" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K474" s="5" t="inlineStr"/>
+      <c r="G474" s="5" t="n"/>
+      <c r="H474" s="5" t="n"/>
+      <c r="I474" s="5" t="n"/>
+      <c r="J474" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K474" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="5" t="inlineStr">
@@ -19840,7 +19615,7 @@
         </is>
       </c>
       <c r="D478" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E478" s="5" t="n">
         <v>4</v>
@@ -19848,23 +19623,19 @@
       <c r="F478" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G478" s="5" t="inlineStr">
-        <is>
-          <t>ask.ifas.ufl.edu listed 2 times: Freshwater Ornamental Fish Commonly Cultured in Florida, University of Florida IFAS Extension; Petty, Hartman, Yanong, Pouder, Francis-Floyd and Waltzek, UF/IFAS Extension VM-149: Koi Herpesvirus Disease (KHVD) | petmd.com listed 2 times: 6 Koi Fish Facts You Should Know, PetMD; Goldfish Care Sheet, PetMD</t>
-        </is>
-      </c>
-      <c r="H478" s="5" t="inlineStr"/>
-      <c r="I478" s="5" t="inlineStr">
-        <is>
-          <t>Combine ask.ifas.ufl.edu into one entry linking the site and naming the pages: Freshwater Ornamental Fish Commonly Cultured in Florida, University of Florida IFAS Extension; Petty, Hartman, Yanong, Pouder, Francis-Floyd and Waltzek, UF/IFAS Extension VM-149: Koi Herpesvirus Disease (KHVD). Combine petmd.com into one entry linking the site and naming the pages: 6 Koi Fish Facts You Should Know, PetMD; Goldfish Care Sheet, PetMD. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J478" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K478" s="5" t="inlineStr"/>
+      <c r="G478" s="5" t="n"/>
+      <c r="H478" s="5" t="n"/>
+      <c r="I478" s="5" t="n"/>
+      <c r="J478" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K478" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="5" t="inlineStr">
@@ -20000,7 +19771,7 @@
         </is>
       </c>
       <c r="D482" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E482" s="5" t="n">
         <v>5</v>
@@ -20008,23 +19779,19 @@
       <c r="F482" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G482" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: What Do Leaf-Tailed Geckos Eat?; ReptiFiles: Leaf-Tailed Gecko Temperatures</t>
-        </is>
-      </c>
-      <c r="H482" s="5" t="inlineStr"/>
-      <c r="I482" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: What Do Leaf-Tailed Geckos Eat?; Leaf-Tailed Gecko Temperatures. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J482" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K482" s="5" t="inlineStr"/>
+      <c r="G482" s="5" t="n"/>
+      <c r="H482" s="5" t="n"/>
+      <c r="I482" s="5" t="n"/>
+      <c r="J482" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K482" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="5" t="inlineStr">
@@ -20043,7 +19810,7 @@
         </is>
       </c>
       <c r="D483" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E483" s="5" t="n">
         <v>2</v>
@@ -20053,13 +19820,13 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Satanic Leaf-Tailed Gecko Care Sheet; ReptiFiles: Leaf-Tailed Gecko Body Language and Handling Notes</t>
-        </is>
-      </c>
-      <c r="H483" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H483" s="5" t="n"/>
       <c r="I483" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Satanic Leaf-Tailed Gecko Care Sheet; Leaf-Tailed Gecko Body Language and Handling Notes.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J483" s="6" t="inlineStr">
@@ -20067,7 +19834,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K483" s="5" t="inlineStr"/>
+      <c r="K483" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="5" t="inlineStr">
@@ -20086,7 +19857,7 @@
         </is>
       </c>
       <c r="D484" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E484" s="5" t="n">
         <v>2</v>
@@ -20096,13 +19867,13 @@
       </c>
       <c r="G484" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Satanic Leaf-Tailed Gecko Care Sheet; ReptiFiles: Leaf-Tailed Gecko Shedding; ReptiFiles: Leaf-Tailed Gecko Mites</t>
-        </is>
-      </c>
-      <c r="H484" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H484" s="5" t="n"/>
       <c r="I484" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Satanic Leaf-Tailed Gecko Care Sheet; Leaf-Tailed Gecko Shedding; Leaf-Tailed Gecko Mites.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J484" s="6" t="inlineStr">
@@ -20110,7 +19881,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K484" s="5" t="inlineStr"/>
+      <c r="K484" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
@@ -20129,7 +19904,7 @@
         </is>
       </c>
       <c r="D485" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E485" s="5" t="n">
         <v>2</v>
@@ -20139,13 +19914,13 @@
       </c>
       <c r="G485" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 5 times: ReptiFiles: Leaf-Tailed Gecko Terrarium Size by Species; ReptiFiles: Leaf-Tailed Gecko Humidity Requirements; ReptiFiles: Leaf-Tailed Gecko Lighting and UVB; ReptiFiles: Leaf-Tailed Gecko Substrate; ReptiFiles: What Do Leaf-Tailed Geckos Eat?</t>
-        </is>
-      </c>
-      <c r="H485" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H485" s="5" t="n"/>
       <c r="I485" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Leaf-Tailed Gecko Terrarium Size by Species; Leaf-Tailed Gecko Humidity Requirements; Leaf-Tailed Gecko Lighting and UVB; Leaf-Tailed Gecko Substrate; What Do Leaf-Tailed Geckos Eat?. Combining brings it from 6 to 2, inside 3 to 5.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J485" s="6" t="inlineStr">
@@ -20153,7 +19928,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K485" s="5" t="inlineStr"/>
+      <c r="K485" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="5" t="inlineStr">
@@ -20508,7 +20287,7 @@
         </is>
       </c>
       <c r="D494" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E494" s="5" t="n">
         <v>3</v>
@@ -20516,23 +20295,19 @@
       <c r="F494" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G494" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Management and Husbandry of Reptiles; Merck Veterinary Manual: Disorders and Diseases of Reptiles | zenhabitats.com listed 3 times: Zen Habitats: Leopard Gecko Complete Lighting and Heating Guide; Zen Habitats: Overhead Heating vs. Under Tank Heating for Leopard Geckos; Zen Habitats: Signs Your Reptile Is Overheating</t>
-        </is>
-      </c>
-      <c r="H494" s="5" t="inlineStr"/>
-      <c r="I494" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Management and Husbandry of Reptiles; Disorders and Diseases of Reptiles. Combine zenhabitats.com into one entry linking the site and naming the pages: Leopard Gecko Complete Lighting and Heating Guide; Overhead Heating vs. Under Tank Heating for Leopard Geckos; Signs Your Reptile Is Overheating. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J494" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K494" s="5" t="inlineStr"/>
+      <c r="G494" s="5" t="n"/>
+      <c r="H494" s="5" t="n"/>
+      <c r="I494" s="5" t="n"/>
+      <c r="J494" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K494" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="5" t="inlineStr">
@@ -20633,7 +20408,7 @@
         </is>
       </c>
       <c r="D497" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E497" s="5" t="n">
         <v>4</v>
@@ -20643,7 +20418,7 @@
       </c>
       <c r="G497" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Cockatoos - General Information; VCA Animal Hospitals: Owning a Tortoise | animallaw.info listed 3 times: Michigan State University College of Law, Animal Legal &amp; Historical Center: Wills and Trusts (Introduction); Michigan State University College of Law, Animal Legal &amp; Historical Center: Detailed Discussion of Pet Trusts; Michigan State University College of Law, Animal Legal &amp; Historical Center: Map of States with Companion Animal (Pet) Trust Laws</t>
+          <t>animallaw.info listed 3 times: Michigan State University College of Law, Animal Legal &amp; Historical Center: Wills and Trusts (Introduction); Michigan State University College of Law, Animal Legal &amp; Historical Center: Detailed Discussion of Pet Trusts; Michigan State University College of Law, Animal Legal &amp; Historical Center: Map of States with Companion Animal (Pet) Trust Laws</t>
         </is>
       </c>
       <c r="H497" s="5" t="inlineStr">
@@ -20653,7 +20428,7 @@
       </c>
       <c r="I497" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Cockatoos - General Information; Owning a Tortoise. Keep animallaw.info entries separate, reason stated.</t>
+          <t>Keep animallaw.info entries separate, reason stated.</t>
         </is>
       </c>
       <c r="J497" s="6" t="inlineStr">
@@ -20661,7 +20436,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K497" s="5" t="inlineStr"/>
+      <c r="K497" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="5" t="inlineStr">
@@ -20785,7 +20564,7 @@
         </is>
       </c>
       <c r="D501" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E501" s="5" t="n">
         <v>5</v>
@@ -20793,23 +20572,19 @@
       <c r="F501" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G501" s="5" t="inlineStr">
-        <is>
-          <t>lafeber.com listed 2 times: Lafeber: Lovebird Questions; Lafeber: Lovebird or Parrotlet?</t>
-        </is>
-      </c>
-      <c r="H501" s="5" t="inlineStr"/>
-      <c r="I501" s="5" t="inlineStr">
-        <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Lovebird Questions; Lovebird or Parrotlet?. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J501" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K501" s="5" t="inlineStr"/>
+      <c r="G501" s="5" t="n"/>
+      <c r="H501" s="5" t="n"/>
+      <c r="I501" s="5" t="n"/>
+      <c r="J501" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K501" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="5" t="inlineStr">
@@ -21292,7 +21067,7 @@
         </is>
       </c>
       <c r="D514" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E514" s="5" t="n">
         <v>3</v>
@@ -21300,23 +21075,19 @@
       <c r="F514" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G514" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: PetMD: Milksnake; PetMD: Milk Snake Care Sheet (Maria Zayas, DVM)</t>
-        </is>
-      </c>
-      <c r="H514" s="5" t="inlineStr"/>
-      <c r="I514" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Milksnake; Milk Snake Care Sheet (Maria Zayas, DVM).</t>
-        </is>
-      </c>
-      <c r="J514" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K514" s="5" t="inlineStr"/>
+      <c r="G514" s="5" t="n"/>
+      <c r="H514" s="5" t="n"/>
+      <c r="I514" s="5" t="n"/>
+      <c r="J514" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K514" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="5" t="inlineStr">
@@ -21417,7 +21188,7 @@
         </is>
       </c>
       <c r="D517" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E517" s="5" t="n">
         <v>5</v>
@@ -21425,23 +21196,19 @@
       <c r="F517" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G517" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: PetMD: Milksnake; PetMD: Milk Snake Care Sheet (Maria Zayas, DVM)</t>
-        </is>
-      </c>
-      <c r="H517" s="5" t="inlineStr"/>
-      <c r="I517" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Milksnake; Milk Snake Care Sheet (Maria Zayas, DVM). Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J517" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K517" s="5" t="inlineStr"/>
+      <c r="G517" s="5" t="n"/>
+      <c r="H517" s="5" t="n"/>
+      <c r="I517" s="5" t="n"/>
+      <c r="J517" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K517" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="5" t="inlineStr">
@@ -21585,7 +21352,7 @@
         </is>
       </c>
       <c r="D521" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E521" s="5" t="n">
         <v>3</v>
@@ -21593,23 +21360,19 @@
       <c r="F521" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G521" s="5" t="inlineStr">
-        <is>
-          <t>animaldiversity.org listed 2 times: Lampropeltis triangulum (Milk Snake), Animal Diversity Web (University of Michigan); Pantherophis guttatus (Corn Snake), Animal Diversity Web (University of Michigan) | nationalzoo.si.edu listed 2 times: Sinaloan Milksnake, Smithsonian's National Zoo &amp; Conservation Biology Institute; Corn Snake, Smithsonian's National Zoo &amp; Conservation Biology Institute</t>
-        </is>
-      </c>
-      <c r="H521" s="5" t="inlineStr"/>
-      <c r="I521" s="5" t="inlineStr">
-        <is>
-          <t>Combine animaldiversity.org into one entry linking the site and naming the pages: Lampropeltis triangulum (Milk Snake), Animal Diversity Web (University of Michigan); Pantherophis guttatus (Corn Snake), Animal Diversity Web (University of Michigan). Combine nationalzoo.si.edu into one entry linking the site and naming the pages: Sinaloan Milksnake, Smithsonian's National Zoo &amp; Conservation Biology Institute; Corn Snake, Smithsonian's National Zoo &amp; Conservation Biology Institute.</t>
-        </is>
-      </c>
-      <c r="J521" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K521" s="5" t="inlineStr"/>
+      <c r="G521" s="5" t="n"/>
+      <c r="H521" s="5" t="n"/>
+      <c r="I521" s="5" t="n"/>
+      <c r="J521" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K521" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="5" t="inlineStr">
@@ -21975,7 +21738,7 @@
         </is>
       </c>
       <c r="D531" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E531" s="5" t="n">
         <v>2</v>
@@ -21985,13 +21748,13 @@
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Mourning Gecko Handling and Body Language Tips; ReptiFiles: Mourning Gecko Care Guide</t>
-        </is>
-      </c>
-      <c r="H531" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H531" s="5" t="n"/>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Mourning Gecko Handling and Body Language Tips; Mourning Gecko Care Guide.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J531" s="6" t="inlineStr">
@@ -21999,7 +21762,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K531" s="5" t="inlineStr"/>
+      <c r="K531" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="5" t="inlineStr">
@@ -22018,7 +21785,7 @@
         </is>
       </c>
       <c r="D532" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E532" s="5" t="n">
         <v>4</v>
@@ -22026,23 +21793,19 @@
       <c r="F532" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G532" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Mourning Gecko Metabolic Bone Disease; ReptiFiles: What to Do When Your Mourning Geckos Lay Eggs</t>
-        </is>
-      </c>
-      <c r="H532" s="5" t="inlineStr"/>
-      <c r="I532" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Mourning Gecko Metabolic Bone Disease; What to Do When Your Mourning Geckos Lay Eggs.</t>
-        </is>
-      </c>
-      <c r="J532" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K532" s="5" t="inlineStr"/>
+      <c r="G532" s="5" t="n"/>
+      <c r="H532" s="5" t="n"/>
+      <c r="I532" s="5" t="n"/>
+      <c r="J532" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K532" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="5" t="inlineStr">
@@ -22061,7 +21824,7 @@
         </is>
       </c>
       <c r="D533" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E533" s="5" t="n">
         <v>3</v>
@@ -22069,23 +21832,19 @@
       <c r="F533" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G533" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 4 times: ReptiFiles: Mourning Gecko Vivarium Size; ReptiFiles: Mourning Gecko Temperatures and Humidity; ReptiFiles: What to Do When Your Mourning Geckos Lay Eggs; ReptiFiles: Establishing a Bioactive Clean Up Crew</t>
-        </is>
-      </c>
-      <c r="H533" s="5" t="inlineStr"/>
-      <c r="I533" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Mourning Gecko Vivarium Size; Mourning Gecko Temperatures and Humidity; What to Do When Your Mourning Geckos Lay Eggs; Establishing a Bioactive Clean Up Crew. Combining brings it from 6 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J533" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K533" s="5" t="inlineStr"/>
+      <c r="G533" s="5" t="n"/>
+      <c r="H533" s="5" t="n"/>
+      <c r="I533" s="5" t="n"/>
+      <c r="J533" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K533" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="5" t="inlineStr">
@@ -22233,7 +21992,7 @@
         </is>
       </c>
       <c r="D537" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E537" s="5" t="n">
         <v>3</v>
@@ -22241,23 +22000,19 @@
       <c r="F537" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G537" s="5" t="inlineStr">
-        <is>
-          <t>rspca.org.uk listed 3 times: RSPCA: Mouse Health &amp; Welfare Tips; RSPCA: Creating a Good Home For Mice; RSPCA: Keeping Mice Together</t>
-        </is>
-      </c>
-      <c r="H537" s="5" t="inlineStr"/>
-      <c r="I537" s="5" t="inlineStr">
-        <is>
-          <t>Combine rspca.org.uk into one entry linking the site and naming the pages: Mouse Health &amp; Welfare Tips; Creating a Good Home For Mice; Keeping Mice Together.</t>
-        </is>
-      </c>
-      <c r="J537" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K537" s="5" t="inlineStr"/>
+      <c r="G537" s="5" t="n"/>
+      <c r="H537" s="5" t="n"/>
+      <c r="I537" s="5" t="n"/>
+      <c r="J537" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K537" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="5" t="inlineStr">
@@ -22276,7 +22031,7 @@
         </is>
       </c>
       <c r="D538" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E538" s="5" t="n">
         <v>5</v>
@@ -22284,23 +22039,19 @@
       <c r="F538" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G538" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Routine Health Care of Mice; Merck Veterinary Manual: Mice and Rats as Pets</t>
-        </is>
-      </c>
-      <c r="H538" s="5" t="inlineStr"/>
-      <c r="I538" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Routine Health Care of Mice; Mice and Rats as Pets. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J538" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K538" s="5" t="inlineStr"/>
+      <c r="G538" s="5" t="n"/>
+      <c r="H538" s="5" t="n"/>
+      <c r="I538" s="5" t="n"/>
+      <c r="J538" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K538" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="5" t="inlineStr">
@@ -22319,7 +22070,7 @@
         </is>
       </c>
       <c r="D539" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E539" s="5" t="n">
         <v>3</v>
@@ -22327,23 +22078,19 @@
       <c r="F539" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G539" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Providing a Home for Mice; Merck Veterinary Manual: Mice and Rats as Pets</t>
-        </is>
-      </c>
-      <c r="H539" s="5" t="inlineStr"/>
-      <c r="I539" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Providing a Home for Mice; Mice and Rats as Pets.</t>
-        </is>
-      </c>
-      <c r="J539" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K539" s="5" t="inlineStr"/>
+      <c r="G539" s="5" t="n"/>
+      <c r="H539" s="5" t="n"/>
+      <c r="I539" s="5" t="n"/>
+      <c r="J539" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K539" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="5" t="inlineStr">
@@ -22377,12 +22124,12 @@
       </c>
       <c r="H540" s="5" t="inlineStr">
         <is>
-          <t>science.org: separate studies, each with its own authors and year; one combined entry could not credit them. pubmed.ncbi.nlm.nih.gov: separate studies, each with its own authors and year; one combined entry could not credit them. nature.com: separate studies, each with its own authors and year; one combined entry could not credit them.</t>
+          <t>Kept separate: separate Science papers (1981 and 2021).</t>
         </is>
       </c>
       <c r="I540" s="5" t="inlineStr">
         <is>
-          <t>Keep science.org studies separate, reason stated; drop any study whose claim another listed source already covers. Keep pubmed.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Keep nature.com studies separate, reason stated; drop any study whose claim another listed source already covers. Combine elifesciences.org into one entry linking the site and naming the pages: Naked mole-rat mortality rates defy Gompertzian laws by not increasing with age, eLife 7:e31157 (Ruby, Smith and Buffenstein, 2018); Comment on 'Naked mole-rat mortality rates defy Gompertzian laws by not increasing with age', eLife 8:e45415 (2019); Response to comment on 'Naked mole-rat mortality rates defy Gompertzian laws by not increasing with age', eLife 8:e47047 (2019). Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J540" s="6" t="inlineStr">
@@ -22390,7 +22137,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K540" s="5" t="inlineStr"/>
+      <c r="K540" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="5" t="inlineStr">
@@ -22803,7 +22554,7 @@
         </is>
       </c>
       <c r="D551" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E551" s="5" t="n">
         <v>4</v>
@@ -22811,23 +22562,19 @@
       <c r="F551" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G551" s="5" t="inlineStr">
-        <is>
-          <t>aquariumcoop.com listed 2 times: Aquarium Co-Op: Care Guide for Oscar Fish; Aquarium Co-Op: How to Treat Hole-in-the-Head Disease in Freshwater Aquarium Fish</t>
-        </is>
-      </c>
-      <c r="H551" s="5" t="inlineStr"/>
-      <c r="I551" s="5" t="inlineStr">
-        <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: Care Guide for Oscar Fish; How to Treat Hole-in-the-Head Disease in Freshwater Aquarium Fish.</t>
-        </is>
-      </c>
-      <c r="J551" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K551" s="5" t="inlineStr"/>
+      <c r="G551" s="5" t="n"/>
+      <c r="H551" s="5" t="n"/>
+      <c r="I551" s="5" t="n"/>
+      <c r="J551" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K551" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="5" t="inlineStr">
@@ -22846,7 +22593,7 @@
         </is>
       </c>
       <c r="D552" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E552" s="5" t="n">
         <v>3</v>
@@ -22854,23 +22601,19 @@
       <c r="F552" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G552" s="5" t="inlineStr">
-        <is>
-          <t>aquariumcoop.com listed 2 times: Aquarium Co-Op: Care Guide for Oscar Fish; Aquarium Co-Op: How to Catch Aquarium Fish Like a Professional</t>
-        </is>
-      </c>
-      <c r="H552" s="5" t="inlineStr"/>
-      <c r="I552" s="5" t="inlineStr">
-        <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: Care Guide for Oscar Fish; How to Catch Aquarium Fish Like a Professional.</t>
-        </is>
-      </c>
-      <c r="J552" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K552" s="5" t="inlineStr"/>
+      <c r="G552" s="5" t="n"/>
+      <c r="H552" s="5" t="n"/>
+      <c r="I552" s="5" t="n"/>
+      <c r="J552" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K552" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="5" t="inlineStr">
@@ -22959,7 +22702,7 @@
         </is>
       </c>
       <c r="D555" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E555" s="5" t="n">
         <v>5</v>
@@ -22967,23 +22710,19 @@
       <c r="F555" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G555" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Owning a Tortoise; VCA Animal Hospitals: Housing Box Turtles</t>
-        </is>
-      </c>
-      <c r="H555" s="5" t="inlineStr"/>
-      <c r="I555" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Owning a Tortoise; Housing Box Turtles. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J555" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K555" s="5" t="inlineStr"/>
+      <c r="G555" s="5" t="n"/>
+      <c r="H555" s="5" t="n"/>
+      <c r="I555" s="5" t="n"/>
+      <c r="J555" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K555" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="5" t="inlineStr">
@@ -23232,7 +22971,7 @@
         </is>
       </c>
       <c r="D562" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E562" s="5" t="n">
         <v>10</v>
@@ -23242,7 +22981,7 @@
       </c>
       <c r="G562" s="5" t="inlineStr">
         <is>
-          <t>pangolinsg.org listed 2 times: Pangolins (IUCN SSC Pangolin Specialist Group); Conservation (IUCN SSC Pangolin Specialist Group) | nationalzoo.si.edu listed 2 times: Smithsonian Scientists Aid in Decoding a Mammalian Mystery: The Genetics of the Pangolin (Smithsonian's National Zoo and Conservation Biology Institute); Latest Pangolin Family Tree Provides Key To Tracking World's Most Trafficked Mammal (Smithsonian's National Zoo and Conservation Biology Institute) | fws.gov listed 2 times: U.S. Fish and Wildlife Service proposes Endangered Species Act protections for pangolins (USFWS, 16 June 2025); Endangered and Threatened Wildlife and Plants; Endangered Species Status for Seven Species of Pangolin (USFWS proposed rule) | ifaw.org listed 2 times: Pangolins are the world's most trafficked wild mammal (IFAW); Pangolins: ecosystem gardeners worth conserving (IFAW) | 14 sources, 10 after combining same-site entries.</t>
+          <t>fws.gov listed 2 times: U.S. Fish and Wildlife Service proposes Endangered Species Act protections for pangolins (USFWS, 16 June 2025); Endangered and Threatened Wildlife and Plants; Endangered Species Status for Seven Species of Pangolin (USFWS proposed rule) | 11 sources, 10 after combining same-site entries.</t>
         </is>
       </c>
       <c r="H562" s="5" t="inlineStr">
@@ -23252,7 +22991,7 @@
       </c>
       <c r="I562" s="5" t="inlineStr">
         <is>
-          <t>Combine pangolinsg.org into one entry linking the site and naming the pages: Pangolins (IUCN SSC Pangolin Specialist Group); Conservation (IUCN SSC Pangolin Specialist Group). Combine nationalzoo.si.edu into one entry linking the site and naming the pages: Smithsonian Scientists Aid in Decoding a Mammalian Mystery: The Genetics of the Pangolin (Smithsonian's National Zoo and Conservation Biology Institute); Latest Pangolin Family Tree Provides Key To Tracking World's Most Trafficked Mammal (Smithsonian's National Zoo and Conservation Biology Institute). Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing. Combine ifaw.org into one entry linking the site and naming the pages: Pangolins are the world's most trafficked wild mammal (IFAW); ecosystem gardeners worth conserving (IFAW). Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J562" s="6" t="inlineStr">
@@ -23260,7 +22999,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K562" s="5" t="inlineStr"/>
+      <c r="K562" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 14 to 11 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="5" t="inlineStr">
@@ -23279,7 +23022,7 @@
         </is>
       </c>
       <c r="D563" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E563" s="5" t="n">
         <v>3</v>
@@ -23287,23 +23030,19 @@
       <c r="F563" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G563" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Taming, Training, Talking to Birds; VCA Animal Hospitals: Behavior Modification, Clicker and Target Training</t>
-        </is>
-      </c>
-      <c r="H563" s="5" t="inlineStr"/>
-      <c r="I563" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Taming, Training, Talking to Birds; Behavior Modification, Clicker and Target Training.</t>
-        </is>
-      </c>
-      <c r="J563" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K563" s="5" t="inlineStr"/>
+      <c r="G563" s="5" t="n"/>
+      <c r="H563" s="5" t="n"/>
+      <c r="I563" s="5" t="n"/>
+      <c r="J563" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K563" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="5" t="inlineStr">
@@ -23400,7 +23139,7 @@
         </is>
       </c>
       <c r="D566" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E566" s="5" t="n">
         <v>4</v>
@@ -23408,23 +23147,19 @@
       <c r="F566" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G566" s="5" t="inlineStr">
-        <is>
-          <t>lafeber.com listed 2 times: Lafeber: Pacific Parrotlet, Personality, Food &amp; Care; Lafeber: Parrotlet, Personality, Food &amp; Care</t>
-        </is>
-      </c>
-      <c r="H566" s="5" t="inlineStr"/>
-      <c r="I566" s="5" t="inlineStr">
-        <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Pacific Parrotlet, Personality, Food &amp; Care; Parrotlet, Personality, Food &amp; Care.</t>
-        </is>
-      </c>
-      <c r="J566" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K566" s="5" t="inlineStr"/>
+      <c r="G566" s="5" t="n"/>
+      <c r="H566" s="5" t="n"/>
+      <c r="I566" s="5" t="n"/>
+      <c r="J566" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K566" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="5" t="inlineStr">
@@ -23443,7 +23178,7 @@
         </is>
       </c>
       <c r="D567" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E567" s="5" t="n">
         <v>2</v>
@@ -23453,13 +23188,13 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 2 times: Lafeber: Pacific Parrotlet, Personality, Food &amp; Care; Lafeber: Lovebird or Parrotlet?</t>
-        </is>
-      </c>
-      <c r="H567" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H567" s="5" t="n"/>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Pacific Parrotlet, Personality, Food &amp; Care; Lovebird or Parrotlet?.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J567" s="6" t="inlineStr">
@@ -23467,7 +23202,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K567" s="5" t="inlineStr"/>
+      <c r="K567" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="5" t="inlineStr">
@@ -23486,7 +23225,7 @@
         </is>
       </c>
       <c r="D568" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E568" s="5" t="n">
         <v>2</v>
@@ -23496,13 +23235,13 @@
       </c>
       <c r="G568" s="5" t="inlineStr">
         <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Reproductive Diseases of Pet Birds; Merck Veterinary Manual: Nutritional Diseases of Pet Birds | vcahospitals.com listed 2 times: VCA Animal Hospitals: Common Conditions of Pet Birds; VCA Animal Hospitals: Psittacine Beak and Feather Disease in Pet Birds</t>
-        </is>
-      </c>
-      <c r="H568" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H568" s="5" t="n"/>
       <c r="I568" s="5" t="inlineStr">
         <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Reproductive Diseases of Pet Birds; Nutritional Diseases of Pet Birds. Combine vcahospitals.com into one entry linking the site and naming the pages: Common Conditions of Pet Birds; Psittacine Beak and Feather Disease in Pet Birds.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J568" s="6" t="inlineStr">
@@ -23510,7 +23249,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K568" s="5" t="inlineStr"/>
+      <c r="K568" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="5" t="inlineStr">
@@ -23529,7 +23272,7 @@
         </is>
       </c>
       <c r="D569" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E569" s="5" t="n">
         <v>2</v>
@@ -23539,13 +23282,13 @@
       </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 2 times: Lafeber: Parrotlet, Personality, Food &amp; Care; Lafeber: Lovebird or Parrotlet?</t>
-        </is>
-      </c>
-      <c r="H569" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H569" s="5" t="n"/>
       <c r="I569" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Parrotlet, Personality, Food &amp; Care; Lovebird or Parrotlet?.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J569" s="6" t="inlineStr">
@@ -23553,7 +23296,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K569" s="5" t="inlineStr"/>
+      <c r="K569" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="5" t="inlineStr">
@@ -23619,7 +23366,7 @@
         </is>
       </c>
       <c r="D571" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E571" s="5" t="n">
         <v>5</v>
@@ -23629,7 +23376,7 @@
       </c>
       <c r="G571" s="5" t="inlineStr">
         <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Periodontal Disease in Small Animals; Merck Veterinary Manual: Tooth Resorption in Small Animals | pmc.ncbi.nlm.nih.gov listed 2 times: Periodontal disease in dogs under primary veterinary care in the UK; Periodontal disease in cats under primary veterinary care in the UK | Also consulted list of 13 unlinked entries (fine print by design).</t>
+          <t>pmc.ncbi.nlm.nih.gov listed 2 times: Periodontal disease in dogs under primary veterinary care in the UK; Periodontal disease in cats under primary veterinary care in the UK | Also consulted list of 13 unlinked entries (fine print by design).</t>
         </is>
       </c>
       <c r="H571" s="5" t="inlineStr">
@@ -23639,7 +23386,7 @@
       </c>
       <c r="I571" s="5" t="inlineStr">
         <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Periodontal Disease in Small Animals; Tooth Resorption in Small Animals. Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Combining brings it from 6 to 5, inside 3 to 5.</t>
+          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J571" s="6" t="inlineStr">
@@ -23647,7 +23394,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K571" s="5" t="inlineStr"/>
+      <c r="K571" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="5" t="inlineStr">
@@ -23679,18 +23430,26 @@
           <t>catvets.com listed 2 times: 2013 AAFP/ISFM Environmental Needs Guidelines. American Association of Feline Practitioners; 2021 General principles of feline well-being. American Association of Feline Practitioners</t>
         </is>
       </c>
-      <c r="H572" s="5" t="inlineStr"/>
+      <c r="H572" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: two separate AAFP guideline documents (2013 and 2021).</t>
+        </is>
+      </c>
       <c r="I572" s="5" t="inlineStr">
         <is>
-          <t>Combine catvets.com into one entry linking the site and naming the pages: 2013 AAFP/ISFM Environmental Needs Guidelines. American Association of Feline Practitioners; 2021 General principles of feline well-being. American Association of Feline Practitioners.</t>
-        </is>
-      </c>
-      <c r="J572" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K572" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J572" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K572" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="5" t="inlineStr">
@@ -23756,7 +23515,7 @@
         </is>
       </c>
       <c r="D574" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E574" s="5" t="n">
         <v>5</v>
@@ -23766,7 +23525,7 @@
       </c>
       <c r="G574" s="5" t="inlineStr">
         <is>
-          <t>pmc.ncbi.nlm.nih.gov listed 2 times: Life span and overweight status in 50,787 dogs; A Deletion in the Canine POMC Gene in Labrador Retrievers | wsava.org listed 2 times: WSAVA Body Condition Score chart: Dogs (PDF); WSAVA Body Condition Score chart: Cats (PDF) | Also consulted list of 12 unlinked entries (fine print by design).</t>
+          <t>pmc.ncbi.nlm.nih.gov listed 2 times: Life span and overweight status in 50,787 dogs; A Deletion in the Canine POMC Gene in Labrador Retrievers | Also consulted list of 12 unlinked entries (fine print by design).</t>
         </is>
       </c>
       <c r="H574" s="5" t="inlineStr">
@@ -23776,7 +23535,7 @@
       </c>
       <c r="I574" s="5" t="inlineStr">
         <is>
-          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Combine wsava.org into one entry linking the site and naming the pages: Dogs (PDF); Cats (PDF). Combining brings it from 6 to 5, inside 3 to 5.</t>
+          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J574" s="6" t="inlineStr">
@@ -23784,7 +23543,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K574" s="5" t="inlineStr"/>
+      <c r="K574" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="5" t="inlineStr">
@@ -23908,7 +23671,7 @@
         </is>
       </c>
       <c r="D578" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E578" s="5" t="n">
         <v>5</v>
@@ -23916,23 +23679,19 @@
       <c r="F578" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G578" s="5" t="inlineStr">
-        <is>
-          <t>aquariumcoop.com listed 2 times: Aquarium Co-Op: Care Guide for Platy Fish; Aquarium Co-Op: How to Breed Livebearers for Profit</t>
-        </is>
-      </c>
-      <c r="H578" s="5" t="inlineStr"/>
-      <c r="I578" s="5" t="inlineStr">
-        <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: Care Guide for Platy Fish; How to Breed Livebearers for Profit. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J578" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K578" s="5" t="inlineStr"/>
+      <c r="G578" s="5" t="n"/>
+      <c r="H578" s="5" t="n"/>
+      <c r="I578" s="5" t="n"/>
+      <c r="J578" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K578" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
@@ -24029,7 +23788,7 @@
         </is>
       </c>
       <c r="D581" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E581" s="5" t="n">
         <v>4</v>
@@ -24037,23 +23796,19 @@
       <c r="F581" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G581" s="5" t="inlineStr">
-        <is>
-          <t>seriouslyfish.com listed 2 times: Seriously Fish: Xiphophorus maculatus; Seriously Fish: Xiphophorus variatus</t>
-        </is>
-      </c>
-      <c r="H581" s="5" t="inlineStr"/>
-      <c r="I581" s="5" t="inlineStr">
-        <is>
-          <t>Combine seriouslyfish.com into one entry linking the site and naming the pages: Xiphophorus maculatus; Xiphophorus variatus.</t>
-        </is>
-      </c>
-      <c r="J581" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K581" s="5" t="inlineStr"/>
+      <c r="G581" s="5" t="n"/>
+      <c r="H581" s="5" t="n"/>
+      <c r="I581" s="5" t="n"/>
+      <c r="J581" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K581" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="5" t="inlineStr">
@@ -24329,7 +24084,7 @@
         </is>
       </c>
       <c r="D589" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E589" s="5" t="n">
         <v>3</v>
@@ -24337,23 +24092,19 @@
       <c r="F589" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G589" s="5" t="inlineStr">
-        <is>
-          <t>keepinginsects.com listed 2 times: Keeping Insects: Taking care of your pet praying mantis; Keeping Insects: African Mantis (Sphodromantis lineola)</t>
-        </is>
-      </c>
-      <c r="H589" s="5" t="inlineStr"/>
-      <c r="I589" s="5" t="inlineStr">
-        <is>
-          <t>Combine keepinginsects.com into one entry linking the site and naming the pages: Taking care of your pet praying mantis; African Mantis (Sphodromantis lineola).</t>
-        </is>
-      </c>
-      <c r="J589" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K589" s="5" t="inlineStr"/>
+      <c r="G589" s="5" t="n"/>
+      <c r="H589" s="5" t="n"/>
+      <c r="I589" s="5" t="n"/>
+      <c r="J589" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K589" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="5" t="inlineStr">
@@ -24442,7 +24193,7 @@
         </is>
       </c>
       <c r="D592" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E592" s="5" t="n">
         <v>2</v>
@@ -24452,13 +24203,13 @@
       </c>
       <c r="G592" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Quaker or Monk Parakeets, Feeding; VCA Animal Hospitals: Liver Disorders in Birds</t>
-        </is>
-      </c>
-      <c r="H592" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H592" s="5" t="n"/>
       <c r="I592" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Quaker or Monk Parakeets, Feeding; Liver Disorders in Birds.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J592" s="6" t="inlineStr">
@@ -24466,7 +24217,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K592" s="5" t="inlineStr"/>
+      <c r="K592" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
@@ -24485,7 +24240,7 @@
         </is>
       </c>
       <c r="D593" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E593" s="5" t="n">
         <v>4</v>
@@ -24493,23 +24248,19 @@
       <c r="F593" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G593" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Biting and Screaming in Birds; VCA Animal Hospitals: Introducing a New Pet Bird</t>
-        </is>
-      </c>
-      <c r="H593" s="5" t="inlineStr"/>
-      <c r="I593" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Biting and Screaming in Birds; Introducing a New Pet Bird.</t>
-        </is>
-      </c>
-      <c r="J593" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K593" s="5" t="inlineStr"/>
+      <c r="G593" s="5" t="n"/>
+      <c r="H593" s="5" t="n"/>
+      <c r="I593" s="5" t="n"/>
+      <c r="J593" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K593" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="5" t="inlineStr">
@@ -24528,7 +24279,7 @@
         </is>
       </c>
       <c r="D594" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E594" s="5" t="n">
         <v>5</v>
@@ -24536,23 +24287,19 @@
       <c r="F594" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G594" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Liver Disorders in Birds; VCA Animal Hospitals: Lead Poisoning in Birds</t>
-        </is>
-      </c>
-      <c r="H594" s="5" t="inlineStr"/>
-      <c r="I594" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Liver Disorders in Birds; Lead Poisoning in Birds. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J594" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K594" s="5" t="inlineStr"/>
+      <c r="G594" s="5" t="n"/>
+      <c r="H594" s="5" t="n"/>
+      <c r="I594" s="5" t="n"/>
+      <c r="J594" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K594" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
@@ -24618,7 +24365,7 @@
         </is>
       </c>
       <c r="D596" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E596" s="5" t="n">
         <v>3</v>
@@ -24626,23 +24373,19 @@
       <c r="F596" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G596" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Quaker or Monk Parakeets, General; VCA Animal Hospitals: Feeding Quaker or Monk Parakeets</t>
-        </is>
-      </c>
-      <c r="H596" s="5" t="inlineStr"/>
-      <c r="I596" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Quaker or Monk Parakeets, General; Feeding Quaker or Monk Parakeets.</t>
-        </is>
-      </c>
-      <c r="J596" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K596" s="5" t="inlineStr"/>
+      <c r="G596" s="5" t="n"/>
+      <c r="H596" s="5" t="n"/>
+      <c r="I596" s="5" t="n"/>
+      <c r="J596" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K596" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
@@ -24661,7 +24404,7 @@
         </is>
       </c>
       <c r="D597" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E597" s="5" t="n">
         <v>5</v>
@@ -24669,23 +24412,19 @@
       <c r="F597" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G597" s="5" t="inlineStr">
-        <is>
-          <t>rabbit.org listed 2 times: rabbit.org: Food and Diet; rabbit.org: GI Stasis</t>
-        </is>
-      </c>
-      <c r="H597" s="5" t="inlineStr"/>
-      <c r="I597" s="5" t="inlineStr">
-        <is>
-          <t>Combine rabbit.org into one entry linking the site and naming the pages: Food and Diet; GI Stasis. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J597" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K597" s="5" t="inlineStr"/>
+      <c r="G597" s="5" t="n"/>
+      <c r="H597" s="5" t="n"/>
+      <c r="I597" s="5" t="n"/>
+      <c r="J597" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K597" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="5" t="inlineStr">
@@ -25012,7 +24751,7 @@
         </is>
       </c>
       <c r="D606" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E606" s="5" t="n">
         <v>4</v>
@@ -25020,23 +24759,19 @@
       <c r="F606" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G606" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Mice and Rats as Pets; Merck Veterinary Manual: Disorders and Diseases of Rats</t>
-        </is>
-      </c>
-      <c r="H606" s="5" t="inlineStr"/>
-      <c r="I606" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Mice and Rats as Pets; Disorders and Diseases of Rats.</t>
-        </is>
-      </c>
-      <c r="J606" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K606" s="5" t="inlineStr"/>
+      <c r="G606" s="5" t="n"/>
+      <c r="H606" s="5" t="n"/>
+      <c r="I606" s="5" t="n"/>
+      <c r="J606" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K606" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
@@ -25090,7 +24825,7 @@
         </is>
       </c>
       <c r="D608" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E608" s="5" t="n">
         <v>4</v>
@@ -25098,23 +24833,19 @@
       <c r="F608" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G608" s="5" t="inlineStr">
-        <is>
-          <t>oxbowanimalhealth.com listed 2 times: Oxbow Animal Health: Essentials Adult Rat Food; Oxbow Animal Health: Garden Select Hamster &amp; Gerbil Food</t>
-        </is>
-      </c>
-      <c r="H608" s="5" t="inlineStr"/>
-      <c r="I608" s="5" t="inlineStr">
-        <is>
-          <t>Combine oxbowanimalhealth.com into one entry linking the site and naming the pages: Essentials Adult Rat Food; Garden Select Hamster &amp; Gerbil Food.</t>
-        </is>
-      </c>
-      <c r="J608" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K608" s="5" t="inlineStr"/>
+      <c r="G608" s="5" t="n"/>
+      <c r="H608" s="5" t="n"/>
+      <c r="I608" s="5" t="n"/>
+      <c r="J608" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K608" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
@@ -25133,7 +24864,7 @@
         </is>
       </c>
       <c r="D609" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E609" s="5" t="n">
         <v>4</v>
@@ -25141,23 +24872,19 @@
       <c r="F609" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G609" s="5" t="inlineStr">
-        <is>
-          <t>rspca.org.uk listed 2 times: RSPCA: Pet Rats in the UK; RSPCA: Rat Company | petmd.com listed 2 times: PetMD: Sexing Rats, How to Identify Male vs. Female Rats; PetMD: Upper Respiratory Infection in Rats</t>
-        </is>
-      </c>
-      <c r="H609" s="5" t="inlineStr"/>
-      <c r="I609" s="5" t="inlineStr">
-        <is>
-          <t>Combine rspca.org.uk into one entry linking the site and naming the pages: Pet Rats in the UK; Rat Company. Combine petmd.com into one entry linking the site and naming the pages: Sexing Rats, How to Identify Male vs. Female Rats; Upper Respiratory Infection in Rats. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J609" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K609" s="5" t="inlineStr"/>
+      <c r="G609" s="5" t="n"/>
+      <c r="H609" s="5" t="n"/>
+      <c r="I609" s="5" t="n"/>
+      <c r="J609" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K609" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
@@ -25176,7 +24903,7 @@
         </is>
       </c>
       <c r="D610" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E610" s="5" t="n">
         <v>3</v>
@@ -25184,23 +24911,19 @@
       <c r="F610" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G610" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Mice and Rats as Pets; Merck Veterinary Manual: Disorders and Diseases of Rats</t>
-        </is>
-      </c>
-      <c r="H610" s="5" t="inlineStr"/>
-      <c r="I610" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Mice and Rats as Pets; Disorders and Diseases of Rats.</t>
-        </is>
-      </c>
-      <c r="J610" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K610" s="5" t="inlineStr"/>
+      <c r="G610" s="5" t="n"/>
+      <c r="H610" s="5" t="n"/>
+      <c r="I610" s="5" t="n"/>
+      <c r="J610" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K610" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="5" t="inlineStr">
@@ -25422,7 +25145,7 @@
         </is>
       </c>
       <c r="D616" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E616" s="5" t="n">
         <v>1</v>
@@ -25432,13 +25155,13 @@
       </c>
       <c r="G616" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Red-Eared Slider Care; ReptiFiles: Red-Eared Slider Handling and Behavior Notes | Only 2 sources.</t>
-        </is>
-      </c>
-      <c r="H616" s="5" t="inlineStr"/>
+          <t>Only 1 source.</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="n"/>
       <c r="I616" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Red-Eared Slider Care; Red-Eared Slider Handling and Behavior Notes. Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J616" s="6" t="inlineStr">
@@ -25446,7 +25169,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K616" s="5" t="inlineStr"/>
+      <c r="K616" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 2 to 1 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="5" t="inlineStr">
@@ -25465,7 +25192,7 @@
         </is>
       </c>
       <c r="D617" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E617" s="5" t="n">
         <v>4</v>
@@ -25473,23 +25200,19 @@
       <c r="F617" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G617" s="5" t="inlineStr">
-        <is>
-          <t>treeoflifeexotics.vet listed 2 times: Tree of Life Exotic Pet Medical Center: Red-Eared Slider Care; Tree of Life Exotic Pet Medical Center: Pyramiding in Tortoises | vcahospitals.com listed 2 times: VCA Animal Hospitals: Common Diseases of Aquatic Turtles; VCA Animal Hospitals: Common Problems in Aquatic Turtles</t>
-        </is>
-      </c>
-      <c r="H617" s="5" t="inlineStr"/>
-      <c r="I617" s="5" t="inlineStr">
-        <is>
-          <t>Combine treeoflifeexotics.vet into one entry linking the site and naming the pages: Red-Eared Slider Care; Pyramiding in Tortoises. Combine vcahospitals.com into one entry linking the site and naming the pages: Common Diseases of Aquatic Turtles; Common Problems in Aquatic Turtles. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J617" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K617" s="5" t="inlineStr"/>
+      <c r="G617" s="5" t="n"/>
+      <c r="H617" s="5" t="n"/>
+      <c r="I617" s="5" t="n"/>
+      <c r="J617" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K617" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="5" t="inlineStr">
@@ -25894,7 +25617,7 @@
         </is>
       </c>
       <c r="D628" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E628" s="5" t="n">
         <v>3</v>
@@ -25902,23 +25625,19 @@
       <c r="F628" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G628" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Amazon Parrots, General; VCA Animal Hospitals: Veterinary Care, New Bird Visit</t>
-        </is>
-      </c>
-      <c r="H628" s="5" t="inlineStr"/>
-      <c r="I628" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Amazon Parrots, General; Veterinary Care, New Bird Visit.</t>
-        </is>
-      </c>
-      <c r="J628" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K628" s="5" t="inlineStr"/>
+      <c r="G628" s="5" t="n"/>
+      <c r="H628" s="5" t="n"/>
+      <c r="I628" s="5" t="n"/>
+      <c r="J628" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K628" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="5" t="inlineStr">
@@ -25972,7 +25691,7 @@
         </is>
       </c>
       <c r="D630" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E630" s="5" t="n">
         <v>4</v>
@@ -25980,23 +25699,19 @@
       <c r="F630" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G630" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Clinical Procedures for Reptiles; Merck Veterinary Manual: Important Husbandry Requirements for Selected Reptiles | vcahospitals.com listed 2 times: VCA Animal Hospitals: Aquatic Turtles, Housing; VCA Animal Hospitals: Box Turtles, Housing</t>
-        </is>
-      </c>
-      <c r="H630" s="5" t="inlineStr"/>
-      <c r="I630" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Clinical Procedures for Reptiles; Important Husbandry Requirements for Selected Reptiles. Combine vcahospitals.com into one entry linking the site and naming the pages: Aquatic Turtles, Housing; Box Turtles, Housing. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J630" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K630" s="5" t="inlineStr"/>
+      <c r="G630" s="5" t="n"/>
+      <c r="H630" s="5" t="n"/>
+      <c r="I630" s="5" t="n"/>
+      <c r="J630" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K630" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="5" t="inlineStr">
@@ -26015,7 +25730,7 @@
         </is>
       </c>
       <c r="D631" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E631" s="5" t="n">
         <v>4</v>
@@ -26023,23 +25738,19 @@
       <c r="F631" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G631" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Management and Husbandry of Reptiles; Merck Veterinary Manual: Overview of Reptiles; Merck Veterinary Manual: Bacterial Diseases of Reptiles | vcahospitals.com listed 2 times: VCA Animal Hospitals: Snakes, Housing; VCA Animal Hospitals: Bearded Dragons, Housing</t>
-        </is>
-      </c>
-      <c r="H631" s="5" t="inlineStr"/>
-      <c r="I631" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Management and Husbandry of Reptiles; Overview of Reptiles; Bacterial Diseases of Reptiles. Combine vcahospitals.com into one entry linking the site and naming the pages: Snakes, Housing; Bearded Dragons, Housing. Combining brings it from 7 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J631" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K631" s="5" t="inlineStr"/>
+      <c r="G631" s="5" t="n"/>
+      <c r="H631" s="5" t="n"/>
+      <c r="I631" s="5" t="n"/>
+      <c r="J631" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K631" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 7 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="5" t="inlineStr">
@@ -26058,7 +25769,7 @@
         </is>
       </c>
       <c r="D632" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E632" s="5" t="n">
         <v>3</v>
@@ -26066,23 +25777,19 @@
       <c r="F632" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G632" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 4 times: Merck Veterinary Manual: Parasitic Diseases of Reptiles; Merck Veterinary Manual: Viral Diseases of Reptiles; Merck Veterinary Manual: Management and Husbandry of Reptiles; Merck Veterinary Manual: Selecting a Reptile | vcahospitals.com listed 2 times: VCA Animal Hospitals: Veterinary Care, New Reptile Visit; VCA Animal Hospitals: Choosing a Pet Reptile</t>
-        </is>
-      </c>
-      <c r="H632" s="5" t="inlineStr"/>
-      <c r="I632" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Parasitic Diseases of Reptiles; Viral Diseases of Reptiles; Management and Husbandry of Reptiles; Selecting a Reptile. Combine vcahospitals.com into one entry linking the site and naming the pages: Veterinary Care, New Reptile Visit; Choosing a Pet Reptile. Combining brings it from 7 to 3, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J632" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K632" s="5" t="inlineStr"/>
+      <c r="G632" s="5" t="n"/>
+      <c r="H632" s="5" t="n"/>
+      <c r="I632" s="5" t="n"/>
+      <c r="J632" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K632" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 7 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="5" t="inlineStr">
@@ -26183,7 +25890,7 @@
         </is>
       </c>
       <c r="D635" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E635" s="5" t="n">
         <v>3</v>
@@ -26191,23 +25898,19 @@
       <c r="F635" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G635" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Routine Health Care of Reptiles; Merck Veterinary Manual: Disorders and Diseases of Reptiles | vcahospitals.com listed 2 times: VCA Animal Hospitals: Reptiles, Gout; VCA Animal Hospitals: Common Diseases of Tortoises</t>
-        </is>
-      </c>
-      <c r="H635" s="5" t="inlineStr"/>
-      <c r="I635" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Routine Health Care of Reptiles; Disorders and Diseases of Reptiles. Combine vcahospitals.com into one entry linking the site and naming the pages: Reptiles, Gout; Common Diseases of Tortoises.</t>
-        </is>
-      </c>
-      <c r="J635" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K635" s="5" t="inlineStr"/>
+      <c r="G635" s="5" t="n"/>
+      <c r="H635" s="5" t="n"/>
+      <c r="I635" s="5" t="n"/>
+      <c r="J635" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K635" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="5" t="inlineStr">
@@ -27021,7 +26724,7 @@
         </is>
       </c>
       <c r="D657" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E657" s="5" t="n">
         <v>6</v>
@@ -27031,13 +26734,13 @@
       </c>
       <c r="G657" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 2 times: LafeberVet: Basic Information Sheet, Savannah Monitor; LafeberVet: Basic Information Sheet, Russian Tortoise | 7 sources, 6 after combining same-site entries.</t>
-        </is>
-      </c>
-      <c r="H657" s="5" t="inlineStr"/>
+          <t>6 sources, 6 after combining same-site entries.</t>
+        </is>
+      </c>
+      <c r="H657" s="5" t="n"/>
       <c r="I657" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Basic Information Sheet, Savannah Monitor; Basic Information Sheet, Russian Tortoise. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J657" s="6" t="inlineStr">
@@ -27045,7 +26748,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K657" s="5" t="inlineStr"/>
+      <c r="K657" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 7 to 6 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="5" t="inlineStr">
@@ -27263,7 +26970,7 @@
         </is>
       </c>
       <c r="D663" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E663" s="5" t="n">
         <v>3</v>
@@ -27271,23 +26978,19 @@
       <c r="F663" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G663" s="5" t="inlineStr">
-        <is>
-          <t>shrimpscience.com listed 2 times: Shrimp Science: Molting and Common Problems; Shrimp Science: Amano Shrimp</t>
-        </is>
-      </c>
-      <c r="H663" s="5" t="inlineStr"/>
-      <c r="I663" s="5" t="inlineStr">
-        <is>
-          <t>Combine shrimpscience.com into one entry linking the site and naming the pages: Molting and Common Problems; Amano Shrimp.</t>
-        </is>
-      </c>
-      <c r="J663" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K663" s="5" t="inlineStr"/>
+      <c r="G663" s="5" t="n"/>
+      <c r="H663" s="5" t="n"/>
+      <c r="I663" s="5" t="n"/>
+      <c r="J663" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K663" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="5" t="inlineStr">
@@ -27388,7 +27091,7 @@
         </is>
       </c>
       <c r="D666" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E666" s="5" t="n">
         <v>3</v>
@@ -27396,23 +27099,19 @@
       <c r="F666" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G666" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Lincosamides Use in Animals; Merck Veterinary Manual: Bacterial and Mycotic Diseases of Rabbits; Merck Veterinary Manual: Hamsters</t>
-        </is>
-      </c>
-      <c r="H666" s="5" t="inlineStr"/>
-      <c r="I666" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Lincosamides Use in Animals; Bacterial and Mycotic Diseases of Rabbits; Hamsters.</t>
-        </is>
-      </c>
-      <c r="J666" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K666" s="5" t="inlineStr"/>
+      <c r="G666" s="5" t="n"/>
+      <c r="H666" s="5" t="n"/>
+      <c r="I666" s="5" t="n"/>
+      <c r="J666" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K666" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="5" t="inlineStr">
@@ -27431,7 +27130,7 @@
         </is>
       </c>
       <c r="D667" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E667" s="5" t="n">
         <v>4</v>
@@ -27441,13 +27140,13 @@
       </c>
       <c r="G667" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 2 times: Lafeber Co.: Tips for Grooming Your Rabbit; Lafeber Co.: Tips for Grooming Your Guinea Pig | merckvetmanual.com listed 4 times: Merck Veterinary Manual: Chinchillas (Exotic and Laboratory Animals); Merck Veterinary Manual: Management of Hedgehogs; Merck Veterinary Manual: Gerbils; Merck Veterinary Manual: Mice and Rats as Pets</t>
-        </is>
-      </c>
-      <c r="H667" s="5" t="inlineStr"/>
+          <t>lafeber.com listed 2 times: Lafeber Co.: Tips for Grooming Your Rabbit; Lafeber Co.: Tips for Grooming Your Guinea Pig</t>
+        </is>
+      </c>
+      <c r="H667" s="5" t="n"/>
       <c r="I667" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Tips for Grooming Your Rabbit; Tips for Grooming Your Guinea Pig. Combine merckvetmanual.com into one entry linking the site and naming the pages: Chinchillas (Exotic and Laboratory Animals); Management of Hedgehogs; Gerbils; Mice and Rats as Pets. Combining brings it from 8 to 4, inside 3 to 5.</t>
+          <t>Combine lafeber.com into one entry linking the site and naming the pages: Tips for Grooming Your Rabbit; Tips for Grooming Your Guinea Pig.</t>
         </is>
       </c>
       <c r="J667" s="6" t="inlineStr">
@@ -27455,7 +27154,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K667" s="5" t="inlineStr"/>
+      <c r="K667" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 8 to 5 entries. 2026-10-06: the two Lafeber Co. grooming pages combined into one entry.</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="5" t="inlineStr">
@@ -27474,33 +27177,25 @@
         </is>
       </c>
       <c r="D668" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E668" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F668" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G668" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 5 times: Merck Veterinary Manual: Housing and Nutrition of Guinea Pigs; Merck Veterinary Manual: Chinchillas; Merck Veterinary Manual: Housing of Rabbits; Merck Veterinary Manual: Hamsters; Merck Veterinary Manual: Gerbils | vcahospitals.com listed 3 times: VCA Animal Hospitals: Health Problems in Rabbits; VCA Animal Hospitals: Chinchillas, Health Conditions; VCA Animal Hospitals: Health Problems in Rodents</t>
-        </is>
-      </c>
-      <c r="H668" s="5" t="inlineStr"/>
-      <c r="I668" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Housing and Nutrition of Guinea Pigs; Chinchillas; Housing of Rabbits; Hamsters; Gerbils. Combine vcahospitals.com into one entry linking the site and naming the pages: Health Problems in Rabbits; Chinchillas, Health Conditions; Health Problems in Rodents. Combining brings it from 10 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J668" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="G668" s="5" t="n"/>
+      <c r="H668" s="5" t="n"/>
+      <c r="I668" s="5" t="n"/>
+      <c r="J668" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K668" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: PetMD chinchilla care sheet added for the settled 55 to 70F band (11 sources; trim in step 5).</t>
+          <t>2026-10-06: PetMD chinchilla care sheet added for the settled 55 to 70F band (11 sources; trim in step 5). 2026-10-06: same-site entries combined, 10 to 5 entries.</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27216,7 @@
         </is>
       </c>
       <c r="D669" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E669" s="5" t="n">
         <v>4</v>
@@ -27529,23 +27224,19 @@
       <c r="F669" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G669" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 4 times: Merck Veterinary Manual: Management of Rabbits; Merck Veterinary Manual: Management of Hedgehogs; Merck Veterinary Manual: Emergencies of Ferrets; Merck Veterinary Manual: Noninfectious Diseases of Guinea Pigs</t>
-        </is>
-      </c>
-      <c r="H669" s="5" t="inlineStr"/>
-      <c r="I669" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Management of Rabbits; Management of Hedgehogs; Emergencies of Ferrets; Noninfectious Diseases of Guinea Pigs. Combining brings it from 7 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J669" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K669" s="5" t="inlineStr"/>
+      <c r="G669" s="5" t="n"/>
+      <c r="H669" s="5" t="n"/>
+      <c r="I669" s="5" t="n"/>
+      <c r="J669" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K669" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 7 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="5" t="inlineStr">
@@ -27741,18 +27432,26 @@
           <t>catvets.com listed 2 times: 2013 AAFP/ISFM Environmental Needs Guidelines. American Association of Feline Practitioners; 2021 General principles of feline well-being. American Association of Feline Practitioners</t>
         </is>
       </c>
-      <c r="H674" s="5" t="inlineStr"/>
+      <c r="H674" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: two separate AAFP guideline documents (2013 and 2021).</t>
+        </is>
+      </c>
       <c r="I674" s="5" t="inlineStr">
         <is>
-          <t>Combine catvets.com into one entry linking the site and naming the pages: 2013 AAFP/ISFM Environmental Needs Guidelines. American Association of Feline Practitioners; 2021 General principles of feline well-being. American Association of Feline Practitioners.</t>
-        </is>
-      </c>
-      <c r="J674" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K674" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J674" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K674" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="5" t="inlineStr">
@@ -27771,7 +27470,7 @@
         </is>
       </c>
       <c r="D675" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E675" s="5" t="n">
         <v>4</v>
@@ -27779,23 +27478,19 @@
       <c r="F675" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G675" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Disorders and Diseases of Fish; Merck Veterinary Manual: Environmental Diseases of Aquatic Animals in Aquatic Systems; Merck Veterinary Manual: Parasitic Diseases of Fish</t>
-        </is>
-      </c>
-      <c r="H675" s="5" t="inlineStr"/>
-      <c r="I675" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Disorders and Diseases of Fish; Environmental Diseases of Aquatic Animals in Aquatic Systems; Parasitic Diseases of Fish. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J675" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K675" s="5" t="inlineStr"/>
+      <c r="G675" s="5" t="n"/>
+      <c r="H675" s="5" t="n"/>
+      <c r="I675" s="5" t="n"/>
+      <c r="J675" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K675" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="5" t="inlineStr">
@@ -28036,7 +27731,7 @@
         </is>
       </c>
       <c r="D682" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E682" s="5" t="n">
         <v>4</v>
@@ -28044,23 +27739,19 @@
       <c r="F682" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G682" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: PetMD: How Long Do Sugar Gliders Live?; PetMD: Sugar Gliders, A Pet Parent's Guide to Habitats, Food, and Care</t>
-        </is>
-      </c>
-      <c r="H682" s="5" t="inlineStr"/>
-      <c r="I682" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: How Long Do Sugar Gliders Live?; Sugar Gliders, A Pet Parent's Guide to Habitats, Food, and Care.</t>
-        </is>
-      </c>
-      <c r="J682" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K682" s="5" t="inlineStr"/>
+      <c r="G682" s="5" t="n"/>
+      <c r="H682" s="5" t="n"/>
+      <c r="I682" s="5" t="n"/>
+      <c r="J682" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K682" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="5" t="inlineStr">
@@ -28114,7 +27805,7 @@
         </is>
       </c>
       <c r="D684" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E684" s="5" t="n">
         <v>4</v>
@@ -28122,23 +27813,19 @@
       <c r="F684" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G684" s="5" t="inlineStr">
-        <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Sugar Gliders, Feeding; VCA Animal Hospitals: Sugar Gliders, Owning</t>
-        </is>
-      </c>
-      <c r="H684" s="5" t="inlineStr"/>
-      <c r="I684" s="5" t="inlineStr">
-        <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Sugar Gliders, Feeding; Sugar Gliders, Owning.</t>
-        </is>
-      </c>
-      <c r="J684" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K684" s="5" t="inlineStr"/>
+      <c r="G684" s="5" t="n"/>
+      <c r="H684" s="5" t="n"/>
+      <c r="I684" s="5" t="n"/>
+      <c r="J684" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K684" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="5" t="inlineStr">
@@ -28192,7 +27879,7 @@
         </is>
       </c>
       <c r="D686" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E686" s="5" t="n">
         <v>3</v>
@@ -28200,23 +27887,19 @@
       <c r="F686" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G686" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Disorders and Diseases of Sugar Gliders; Merck Veterinary Manual: Overview of Sugar Gliders (professional version); Merck Veterinary Manual: Providing a Home for a Sugar Glider</t>
-        </is>
-      </c>
-      <c r="H686" s="5" t="inlineStr"/>
-      <c r="I686" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Disorders and Diseases of Sugar Gliders; Overview of Sugar Gliders (professional version); Providing a Home for a Sugar Glider.</t>
-        </is>
-      </c>
-      <c r="J686" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K686" s="5" t="inlineStr"/>
+      <c r="G686" s="5" t="n"/>
+      <c r="H686" s="5" t="n"/>
+      <c r="I686" s="5" t="n"/>
+      <c r="J686" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K686" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="5" t="inlineStr">
@@ -28270,7 +27953,7 @@
         </is>
       </c>
       <c r="D688" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E688" s="5" t="n">
         <v>4</v>
@@ -28278,23 +27961,19 @@
       <c r="F688" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G688" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual: Providing a Home for a Sugar Glider; Merck Veterinary Manual: Overview of Sugar Gliders (professional version)</t>
-        </is>
-      </c>
-      <c r="H688" s="5" t="inlineStr"/>
-      <c r="I688" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Providing a Home for a Sugar Glider; Overview of Sugar Gliders (professional version).</t>
-        </is>
-      </c>
-      <c r="J688" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K688" s="5" t="inlineStr"/>
+      <c r="G688" s="5" t="n"/>
+      <c r="H688" s="5" t="n"/>
+      <c r="I688" s="5" t="n"/>
+      <c r="J688" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K688" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="5" t="inlineStr">
@@ -28819,7 +28498,7 @@
         </is>
       </c>
       <c r="D703" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E703" s="5" t="n">
         <v>3</v>
@@ -28827,23 +28506,19 @@
       <c r="F703" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G703" s="5" t="inlineStr">
-        <is>
-          <t>tropica.com listed 3 times: Tropica: Vallisneria spiralis 'Tiger'; Tropica: Ceratophyllum demersum; Tropica: Anubias barteri var. nana</t>
-        </is>
-      </c>
-      <c r="H703" s="5" t="inlineStr"/>
-      <c r="I703" s="5" t="inlineStr">
-        <is>
-          <t>Combine tropica.com into one entry linking the site and naming the pages: Vallisneria spiralis 'Tiger'; Ceratophyllum demersum; Anubias barteri var. nana.</t>
-        </is>
-      </c>
-      <c r="J703" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K703" s="5" t="inlineStr"/>
+      <c r="G703" s="5" t="n"/>
+      <c r="H703" s="5" t="n"/>
+      <c r="I703" s="5" t="n"/>
+      <c r="J703" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K703" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="5" t="inlineStr">
@@ -28995,7 +28670,7 @@
         </is>
       </c>
       <c r="D707" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E707" s="5" t="n">
         <v>3</v>
@@ -29003,23 +28678,19 @@
       <c r="F707" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G707" s="5" t="inlineStr">
-        <is>
-          <t>tomsbigspiders.com listed 2 times: Tom's Big Spiders: Tarantula Feeding, How Much to Feed; Tom's Big Spiders: How Do I Know if My Tarantula Is in Premolt?</t>
-        </is>
-      </c>
-      <c r="H707" s="5" t="inlineStr"/>
-      <c r="I707" s="5" t="inlineStr">
-        <is>
-          <t>Combine tomsbigspiders.com into one entry linking the site and naming the pages: Tarantula Feeding, How Much to Feed; How Do I Know if My Tarantula Is in Premolt?.</t>
-        </is>
-      </c>
-      <c r="J707" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K707" s="5" t="inlineStr"/>
+      <c r="G707" s="5" t="n"/>
+      <c r="H707" s="5" t="n"/>
+      <c r="I707" s="5" t="n"/>
+      <c r="J707" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K707" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="5" t="inlineStr">
@@ -29186,7 +28857,7 @@
         </is>
       </c>
       <c r="D712" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E712" s="5" t="n">
         <v>4</v>
@@ -29194,23 +28865,19 @@
       <c r="F712" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G712" s="5" t="inlineStr">
-        <is>
-          <t>animaldiversity.org listed 2 times: Pandinus imperator (Emperor Scorpion), Animal Diversity Web (University of Michigan); Brachypelma smithi (Mexican Red-knee Tarantula), Animal Diversity Web (University of Michigan)</t>
-        </is>
-      </c>
-      <c r="H712" s="5" t="inlineStr"/>
-      <c r="I712" s="5" t="inlineStr">
-        <is>
-          <t>Combine animaldiversity.org into one entry linking the site and naming the pages: Pandinus imperator (Emperor Scorpion), Animal Diversity Web (University of Michigan); Brachypelma smithi (Mexican Red-knee Tarantula), Animal Diversity Web (University of Michigan).</t>
-        </is>
-      </c>
-      <c r="J712" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K712" s="5" t="inlineStr"/>
+      <c r="G712" s="5" t="n"/>
+      <c r="H712" s="5" t="n"/>
+      <c r="I712" s="5" t="n"/>
+      <c r="J712" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K712" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="5" t="inlineStr">
@@ -29775,7 +29442,7 @@
         </is>
       </c>
       <c r="D727" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E727" s="5" t="n">
         <v>5</v>
@@ -29785,7 +29452,7 @@
       </c>
       <c r="G727" s="5" t="inlineStr">
         <is>
-          <t>sciencedirect.com listed 2 times: Changes in enclosure use and basking behaviour associated with pair housing in tokay geckos. Applied Animal Behaviour Science (2024); Bashaw MJ et al. (2016). Does enrichment improve reptile welfare? Leopard geckos respond to five types of environmental enrichment. Applied Animal Behaviour Science | reptilesmagazine.com listed 2 times: Kevin McCurley, Reptiles Magazine: Tokay Gecko Care; Michael Billewicz, Reptiles Magazine: Tokay Gecko Reproduction, Breeding and Genetics</t>
+          <t>sciencedirect.com listed 2 times: Changes in enclosure use and basking behaviour associated with pair housing in tokay geckos. Applied Animal Behaviour Science (2024); Bashaw MJ et al. (2016). Does enrichment improve reptile welfare? Leopard geckos respond to five types of environmental enrichment. Applied Animal Behaviour Science</t>
         </is>
       </c>
       <c r="H727" s="5" t="inlineStr">
@@ -29795,7 +29462,7 @@
       </c>
       <c r="I727" s="5" t="inlineStr">
         <is>
-          <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Combine reptilesmagazine.com into one entry linking the site and naming the pages: Tokay Gecko Care; Tokay Gecko Reproduction, Breeding and Genetics. Combining brings it from 6 to 5, inside 3 to 5.</t>
+          <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J727" s="6" t="inlineStr">
@@ -29803,7 +29470,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K727" s="5" t="inlineStr"/>
+      <c r="K727" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="5" t="inlineStr">
@@ -29857,7 +29528,7 @@
         </is>
       </c>
       <c r="D729" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E729" s="5" t="n">
         <v>4</v>
@@ -29865,23 +29536,19 @@
       <c r="F729" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G729" s="5" t="inlineStr">
-        <is>
-          <t>reptilesmagazine.com listed 2 times: Reptiles Magazine: Tokay Gecko Care; Reptiles Magazine: Tokay Gecko Information (Robert Baldwin)</t>
-        </is>
-      </c>
-      <c r="H729" s="5" t="inlineStr"/>
-      <c r="I729" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptilesmagazine.com into one entry linking the site and naming the pages: Tokay Gecko Care; Tokay Gecko Information (Robert Baldwin).</t>
-        </is>
-      </c>
-      <c r="J729" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K729" s="5" t="inlineStr"/>
+      <c r="G729" s="5" t="n"/>
+      <c r="H729" s="5" t="n"/>
+      <c r="I729" s="5" t="n"/>
+      <c r="J729" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K729" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="5" t="inlineStr">
@@ -29900,7 +29567,7 @@
         </is>
       </c>
       <c r="D730" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E730" s="5" t="n">
         <v>4</v>
@@ -29908,23 +29575,19 @@
       <c r="F730" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G730" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Disorders and Diseases of Reptiles; Merck Veterinary Manual: Management and Husbandry of Reptiles; Merck Veterinary Manual: Parasitic Diseases of Reptiles</t>
-        </is>
-      </c>
-      <c r="H730" s="5" t="inlineStr"/>
-      <c r="I730" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Disorders and Diseases of Reptiles; Management and Husbandry of Reptiles; Parasitic Diseases of Reptiles. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J730" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K730" s="5" t="inlineStr"/>
+      <c r="G730" s="5" t="n"/>
+      <c r="H730" s="5" t="n"/>
+      <c r="I730" s="5" t="n"/>
+      <c r="J730" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K730" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="5" t="inlineStr">
@@ -30056,7 +29719,7 @@
         </is>
       </c>
       <c r="D734" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E734" s="5" t="n">
         <v>4</v>
@@ -30066,7 +29729,7 @@
       </c>
       <c r="G734" s="5" t="inlineStr">
         <is>
-          <t>vcahospitals.com listed 2 times: VCA Animal Hospitals: Reptiles, Dystocia; VCA Animal Hospitals: Box Turtles, Problems | pmc.ncbi.nlm.nih.gov listed 2 times: Lubian et al., "Disorders of the Female Reproductive Tract in Chelonians: A Review," Animals, 2025, 15(9):1275, DOI: 10.3390/ani15091275; Morel et al., "Biochemical and Hepatic Determinants of Reproductive Failure in Reptiles: A Review of Dystocia Pathophysiology and Management," Veterinary Sciences, 2025, 13(1):30, DOI: 10.3390/vetsci13010030</t>
+          <t>pmc.ncbi.nlm.nih.gov listed 2 times: Lubian et al., "Disorders of the Female Reproductive Tract in Chelonians: A Review," Animals, 2025, 15(9):1275, DOI: 10.3390/ani15091275; Morel et al., "Biochemical and Hepatic Determinants of Reproductive Failure in Reptiles: A Review of Dystocia Pathophysiology and Management," Veterinary Sciences, 2025, 13(1):30, DOI: 10.3390/vetsci13010030</t>
         </is>
       </c>
       <c r="H734" s="5" t="inlineStr">
@@ -30076,7 +29739,7 @@
       </c>
       <c r="I734" s="5" t="inlineStr">
         <is>
-          <t>Combine vcahospitals.com into one entry linking the site and naming the pages: Reptiles, Dystocia; Box Turtles, Problems. Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
+          <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
       <c r="J734" s="6" t="inlineStr">
@@ -30084,7 +29747,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K734" s="5" t="inlineStr"/>
+      <c r="K734" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="5" t="inlineStr">
@@ -30103,7 +29770,7 @@
         </is>
       </c>
       <c r="D735" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E735" s="5" t="n">
         <v>4</v>
@@ -30111,23 +29778,19 @@
       <c r="F735" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G735" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 3 times: ReptiFiles: Sulcata Tortoise Care Sheet; ReptiFiles: Russian Tortoise Care Sheet; ReptiFiles: Eastern Box Turtle Care Sheet</t>
-        </is>
-      </c>
-      <c r="H735" s="5" t="inlineStr"/>
-      <c r="I735" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Sulcata Tortoise Care Sheet; Russian Tortoise Care Sheet; Eastern Box Turtle Care Sheet. Combining brings it from 6 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J735" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K735" s="5" t="inlineStr"/>
+      <c r="G735" s="5" t="n"/>
+      <c r="H735" s="5" t="n"/>
+      <c r="I735" s="5" t="n"/>
+      <c r="J735" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K735" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="5" t="inlineStr">
@@ -30283,7 +29946,7 @@
         </is>
       </c>
       <c r="D739" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E739" s="5" t="n">
         <v>4</v>
@@ -30291,23 +29954,19 @@
       <c r="F739" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G739" s="5" t="inlineStr">
-        <is>
-          <t>lizards101.com listed 2 times: Lizards101: Complete Guide to Uromastyx Diet, Food List &amp; Supplements; Lizards101: Why Is My Uromastyx Not Eating</t>
-        </is>
-      </c>
-      <c r="H739" s="5" t="inlineStr"/>
-      <c r="I739" s="5" t="inlineStr">
-        <is>
-          <t>Combine lizards101.com into one entry linking the site and naming the pages: Complete Guide to Uromastyx Diet, Food List &amp; Supplements; Why Is My Uromastyx Not Eating.</t>
-        </is>
-      </c>
-      <c r="J739" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K739" s="5" t="inlineStr"/>
+      <c r="G739" s="5" t="n"/>
+      <c r="H739" s="5" t="n"/>
+      <c r="I739" s="5" t="n"/>
+      <c r="J739" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K739" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="5" t="inlineStr">
@@ -30447,7 +30106,7 @@
         </is>
       </c>
       <c r="D743" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E743" s="5" t="n">
         <v>3</v>
@@ -30455,23 +30114,19 @@
       <c r="F743" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G743" s="5" t="inlineStr">
-        <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Uromastyx Care Sheet; ReptiFiles: Tokay Gecko Care Sheet</t>
-        </is>
-      </c>
-      <c r="H743" s="5" t="inlineStr"/>
-      <c r="I743" s="5" t="inlineStr">
-        <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Uromastyx Care Sheet; Tokay Gecko Care Sheet.</t>
-        </is>
-      </c>
-      <c r="J743" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K743" s="5" t="inlineStr"/>
+      <c r="G743" s="5" t="n"/>
+      <c r="H743" s="5" t="n"/>
+      <c r="I743" s="5" t="n"/>
+      <c r="J743" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K743" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 4 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="5" t="inlineStr">
@@ -30490,7 +30145,7 @@
         </is>
       </c>
       <c r="D744" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E744" s="5" t="n">
         <v>4</v>
@@ -30498,23 +30153,19 @@
       <c r="F744" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G744" s="5" t="inlineStr">
-        <is>
-          <t>petmd.com listed 2 times: Bearded Dragon Care Sheet, PetMD; How Long Do Bearded Dragons Live?, PetMD</t>
-        </is>
-      </c>
-      <c r="H744" s="5" t="inlineStr"/>
-      <c r="I744" s="5" t="inlineStr">
-        <is>
-          <t>Combine petmd.com into one entry linking the site and naming the pages: Bearded Dragon Care Sheet, PetMD; How Long Do Bearded Dragons Live?, PetMD.</t>
-        </is>
-      </c>
-      <c r="J744" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K744" s="5" t="inlineStr"/>
+      <c r="G744" s="5" t="n"/>
+      <c r="H744" s="5" t="n"/>
+      <c r="I744" s="5" t="n"/>
+      <c r="J744" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K744" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="5" t="inlineStr">
@@ -30533,7 +30184,7 @@
         </is>
       </c>
       <c r="D745" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E745" s="5" t="n">
         <v>4</v>
@@ -30541,23 +30192,19 @@
       <c r="F745" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G745" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 4 times: Merck Veterinary Manual: Nutritional, Metabolic and Endocrine Diseases of Reptiles; Merck Veterinary Manual: Nutritional Diseases of Pet Birds; Merck Veterinary Manual: Environment and Husbandry for Amphibians; Merck Veterinary Manual: Noninfectious Disorders of Amphibians</t>
-        </is>
-      </c>
-      <c r="H745" s="5" t="inlineStr"/>
-      <c r="I745" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Nutritional, Metabolic and Endocrine Diseases of Reptiles; Nutritional Diseases of Pet Birds; Environment and Husbandry for Amphibians; Noninfectious Disorders of Amphibians. Combining brings it from 7 to 4, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J745" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K745" s="5" t="inlineStr"/>
+      <c r="G745" s="5" t="n"/>
+      <c r="H745" s="5" t="n"/>
+      <c r="I745" s="5" t="n"/>
+      <c r="J745" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K745" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 7 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="5" t="inlineStr">
@@ -30693,7 +30340,7 @@
         </is>
       </c>
       <c r="D749" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E749" s="5" t="n">
         <v>2</v>
@@ -30703,13 +30350,13 @@
       </c>
       <c r="G749" s="5" t="inlineStr">
         <is>
-          <t>reptifiles.com listed 2 times: ReptiFiles: Veiled Chameleon Care Sheet; ReptiFiles: Hognose Snake Care Guide</t>
-        </is>
-      </c>
-      <c r="H749" s="5" t="inlineStr"/>
+          <t>Only 2 sources.</t>
+        </is>
+      </c>
+      <c r="H749" s="5" t="n"/>
       <c r="I749" s="5" t="inlineStr">
         <is>
-          <t>Combine reptifiles.com into one entry linking the site and naming the pages: Veiled Chameleon Care Sheet; Hognose Snake Care Guide.</t>
+          <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
       <c r="J749" s="6" t="inlineStr">
@@ -30717,7 +30364,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K749" s="5" t="inlineStr"/>
+      <c r="K749" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="5" t="inlineStr">
@@ -30889,10 +30540,14 @@
           <t>sciencedaily.com listed 2 times: ScienceDaily. Giant squids' giant eyes: the better to see hungry whales with (on Nilsson DE, Warrant EJ, Johnsen S, Hanlon R, Shashar N. 2012. A unique advantage for giant eyes in giant squid. Current Biology); ScienceDaily. First video of 'Dumbo' octopod hatchling shows that they look like mini-adults (on Shea EK, et al. 2018. Dumbo octopod hatchling provides insight into early cirrate life cycle. Current Biology) | 9 sources, 8 after combining same-site entries.</t>
         </is>
       </c>
-      <c r="H754" s="5" t="inlineStr"/>
+      <c r="H754" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: ScienceDaily write-ups of separate papers, each naming its study.</t>
+        </is>
+      </c>
       <c r="I754" s="5" t="inlineStr">
         <is>
-          <t>Combine sciencedaily.com into one entry linking the site and naming the pages: the better to see hungry whales with (on Nilsson DE, Warrant EJ, Johnsen S, Hanlon R, Shashar N. 2012. A unique advantage for giant eyes in giant squid. Current Biology); ScienceDaily. First video of 'Dumbo' octopod hatchling shows that they look like mini-adults (on Shea EK, et al. 2018. Dumbo octopod hatchling provides insight into early cirrate life cycle. Current Biology). Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
+          <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
       <c r="J754" s="6" t="inlineStr">
@@ -30900,7 +30555,11 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="K754" s="5" t="inlineStr"/>
+      <c r="K754" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="5" t="inlineStr">
@@ -31395,7 +31054,7 @@
         </is>
       </c>
       <c r="D767" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E767" s="5" t="n">
         <v>5</v>
@@ -31403,23 +31062,19 @@
       <c r="F767" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G767" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 2 times: Merck Veterinary Manual (Bird Owners). Skin and Feather Disorders of Pet Birds; Merck Veterinary Manual (Bird Owners). Behavior of Pet Birds</t>
-        </is>
-      </c>
-      <c r="H767" s="5" t="inlineStr"/>
-      <c r="I767" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Merck Veterinary Manual (Bird Owners). Skin and Feather Disorders of Pet Birds; Merck Veterinary Manual (Bird Owners). Behavior of Pet Birds. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J767" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K767" s="5" t="inlineStr"/>
+      <c r="G767" s="5" t="n"/>
+      <c r="H767" s="5" t="n"/>
+      <c r="I767" s="5" t="n"/>
+      <c r="J767" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K767" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="5" t="inlineStr">
@@ -31867,7 +31522,7 @@
         </is>
       </c>
       <c r="D779" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E779" s="5" t="n">
         <v>4</v>
@@ -31875,23 +31530,19 @@
       <c r="F779" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G779" s="5" t="inlineStr">
-        <is>
-          <t>aquariumcoop.com listed 2 times: Care Guide for Zebra and Leopard Danios, Aquarium Co-Op; How to Catch Aquarium Fish Like a Professional, Aquarium Co-Op</t>
-        </is>
-      </c>
-      <c r="H779" s="5" t="inlineStr"/>
-      <c r="I779" s="5" t="inlineStr">
-        <is>
-          <t>Combine aquariumcoop.com into one entry linking the site and naming the pages: Care Guide for Zebra and Leopard Danios, Aquarium Co-Op; How to Catch Aquarium Fish Like a Professional, Aquarium Co-Op.</t>
-        </is>
-      </c>
-      <c r="J779" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K779" s="5" t="inlineStr"/>
+      <c r="G779" s="5" t="n"/>
+      <c r="H779" s="5" t="n"/>
+      <c r="I779" s="5" t="n"/>
+      <c r="J779" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K779" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="5" t="inlineStr">
@@ -32128,7 +31779,7 @@
         </is>
       </c>
       <c r="D786" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E786" s="5" t="n">
         <v>3</v>
@@ -32136,23 +31787,19 @@
       <c r="F786" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G786" s="5" t="inlineStr">
-        <is>
-          <t>merckvetmanual.com listed 3 times: Merck Veterinary Manual: Nutritional Diseases of Pet Birds; Merck Veterinary Manual: Reproductive Disorders of Pet Birds; Merck Veterinary Manual: Parasitic Diseases of Pet Birds</t>
-        </is>
-      </c>
-      <c r="H786" s="5" t="inlineStr"/>
-      <c r="I786" s="5" t="inlineStr">
-        <is>
-          <t>Combine merckvetmanual.com into one entry linking the site and naming the pages: Nutritional Diseases of Pet Birds; Reproductive Disorders of Pet Birds; Parasitic Diseases of Pet Birds.</t>
-        </is>
-      </c>
-      <c r="J786" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K786" s="5" t="inlineStr"/>
+      <c r="G786" s="5" t="n"/>
+      <c r="H786" s="5" t="n"/>
+      <c r="I786" s="5" t="n"/>
+      <c r="J786" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K786" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 3 entries.</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="5" t="inlineStr">
@@ -32171,7 +31818,7 @@
         </is>
       </c>
       <c r="D787" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E787" s="5" t="n">
         <v>3</v>
@@ -32181,21 +31828,29 @@
       </c>
       <c r="G787" s="5" t="inlineStr">
         <is>
-          <t>lafeber.com listed 2 times: LafeberVet: Basic Information Sheet, Finch; Lafeber: Pacific Parrotlet, Personality, Food &amp; Care | petmd.com listed 2 times: PetMD: Finch Care Sheet; PetMD: Parrotlets, a Large Personality Packed in a Mini Body</t>
-        </is>
-      </c>
-      <c r="H787" s="5" t="inlineStr"/>
+          <t>lafeber.com listed 2 times: LafeberVet: Basic Information Sheet, Finch; Lafeber: Pacific Parrotlet, Personality, Food &amp; Care</t>
+        </is>
+      </c>
+      <c r="H787" s="5" t="inlineStr">
+        <is>
+          <t>Kept separate: LafeberVet (lafeber.com/vet, written for veterinarians) and Lafeber Co. pet owner pages are two different sites on one domain.</t>
+        </is>
+      </c>
       <c r="I787" s="5" t="inlineStr">
         <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Basic Information Sheet, Finch; Pacific Parrotlet, Personality, Food &amp; Care. Combine petmd.com into one entry linking the site and naming the pages: Finch Care Sheet; Parrotlets, a Large Personality Packed in a Mini Body.</t>
-        </is>
-      </c>
-      <c r="J787" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K787" s="5" t="inlineStr"/>
+          <t>Keep, reason stated.</t>
+        </is>
+      </c>
+      <c r="J787" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K787" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: same-site entries combined, 5 to 4 entries. 2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="5" t="inlineStr">

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22"/>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>5</v>
@@ -4682,27 +4682,19 @@
       <c r="F99" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>cdc.gov listed 2 times: CDC: Salmonella Outbreak Linked to Bearded Dragons (2025); CDC: Reptiles and Amphibians, Healthy Pets</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>cdc.gov: separate pages from one agency; worth keeping apart only if each backs a different claim the article makes.</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Combine cdc.gov into one entry naming the pages unless each backs a distinct rule or listing. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J99" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="5" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: the two CDC pages combined into one entry, 6 to 5.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -9122,12 +9114,12 @@
       <c r="F211" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G211" s="5" t="n"/>
+      <c r="G211" s="5" t="inlineStr"/>
       <c r="H211" s="5" t="n"/>
-      <c r="I211" s="5" t="n"/>
-      <c r="J211" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="I211" s="5" t="inlineStr"/>
+      <c r="J211" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
@@ -25808,7 +25800,7 @@
         </is>
       </c>
       <c r="D633" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E633" s="5" t="n">
         <v>5</v>
@@ -25816,27 +25808,19 @@
       <c r="F633" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G633" s="5" t="inlineStr">
-        <is>
-          <t>cdc.gov listed 2 times: CDC: Healthy Pets, Healthy People, Reptiles and Amphibians; CDC: Salmonella Outbreak Linked to Pet Geckos, Muenchen</t>
-        </is>
-      </c>
-      <c r="H633" s="5" t="inlineStr">
-        <is>
-          <t>cdc.gov: separate pages from one agency; worth keeping apart only if each backs a different claim the article makes.</t>
-        </is>
-      </c>
-      <c r="I633" s="5" t="inlineStr">
-        <is>
-          <t>Combine cdc.gov into one entry naming the pages unless each backs a distinct rule or listing. Combining brings it from 6 to 5, inside 3 to 5.</t>
-        </is>
-      </c>
-      <c r="J633" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K633" s="5" t="inlineStr"/>
+      <c r="G633" s="5" t="inlineStr"/>
+      <c r="H633" s="5" t="inlineStr"/>
+      <c r="I633" s="5" t="inlineStr"/>
+      <c r="J633" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K633" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: the two CDC pages combined into one entry, 6 to 5.</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="5" t="inlineStr">
@@ -27138,20 +27122,12 @@
       <c r="F667" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G667" s="5" t="inlineStr">
-        <is>
-          <t>lafeber.com listed 2 times: Lafeber Co.: Tips for Grooming Your Rabbit; Lafeber Co.: Tips for Grooming Your Guinea Pig</t>
-        </is>
-      </c>
+      <c r="G667" s="5" t="inlineStr"/>
       <c r="H667" s="5" t="n"/>
-      <c r="I667" s="5" t="inlineStr">
-        <is>
-          <t>Combine lafeber.com into one entry linking the site and naming the pages: Tips for Grooming Your Rabbit; Tips for Grooming Your Guinea Pig.</t>
-        </is>
-      </c>
-      <c r="J667" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="I667" s="5" t="inlineStr"/>
+      <c r="J667" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K667" s="5" t="inlineStr">

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sites" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Articles'!$A$1:$K$788</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Articles'!$A$1:$M$788</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -676,7 +676,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -705,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K788"/>
+  <dimension ref="A1:M788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -719,6 +718,8 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="90" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -777,6 +778,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Step 4 check</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Step 4 detail</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -863,6 +874,16 @@
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -988,6 +1009,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1031,6 +1062,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block; these figures have nothing behind them: Adult boas range from about 5 to 13 feet long, and it's almost always the females occupying the top end of that range. | A healthy wild boa constrictor can survive 20 to 30 years, hunting rodents, birds, bats, lizards, and other small mammals along the way.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1226,6 +1267,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: They can live 20 to 30 years or more in the wild.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1421,6 +1472,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1511,6 +1572,16 @@
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1589,6 +1660,16 @@
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>No figures; the Cell paper covers the chemotactile claim only.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1706,6 +1787,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: The purchase price is the smallest number on this page, and the seller decides more about the next 15 to 20 years than the price does. | 15 to 20 years with proper housing and care.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1858,6 +1949,16 @@
           <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1940,6 +2041,16 @@
           <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: caption="Bigger, hotter, and deeper than most reptile setups, an ackie monitor enclosure runs 130-170°F on the basking surface and needs 12-24 inches of diggabl | ## Temperature: 130 to 170°F on the Basking Surface | Ackies bask at surface temperatures roughly 130 to 170°F, measured directly on the basking stone or stack with an infrared thermometer, not air temperature. | A basking surface reading below about 130°F is too cool for this species to properly synthesize vitamin D.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2385,6 +2496,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2971,6 +3092,16 @@
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Only the 55 gallon tank figure is outside the two listed studies.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3088,6 +3219,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Move affected fish into a bare 10 to 20 gallon [hospital tank] where possible, and give any new angelfish 30 to 60 days there before it joins the display.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3408,6 +3549,16 @@
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block; these figures have nothing behind them: A proper adult enclosure alone, custom built at 8 feet by 4 feet by 4 feet minimum, routinely runs into the thousands once you add powerful basking and radiant heat, a real thermostat, high output UVB, and 12 to 18 inche | Worth being upfront about the first enclosure line above: it's a ready made 8ft PVC modular unit, 8x2x2ft, a partial match on length only, well short of the full 8x4x4ft footprint an adult tegu needs. | The substrate line is similarly a starting point, not a total, reaching 12 to 18 inches of depth across an 8 by 4 foot floor takes considerably more than one or two packs.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -3568,6 +3719,16 @@
           <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3656,6 +3817,16 @@
       <c r="K72" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Basking area 100 to 110F, which overlaps the published 95 to 100F and 100 to 115F ranges, warm ambient in the 90s, cool side around 80F, with nighttime allowed  | For an enclosure this large, a 46 inch T5 HO bulb in the 12 to 14% range, spanning a quarter to half the enclosure's length on the warm side, targeting a baskin</t>
         </is>
       </c>
     </row>
@@ -4465,6 +4636,16 @@
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr"/>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: - **Offer a shallow, lukewarm soak.** About 15 minutes, chest-deep at most, never unsupervised. | - **Shorten the light cycle.** Drop to 8 to 10 hours of light on a timer, or leave lights off entirely if the dragon is fully asleep in its hide and not coming  | - **Keep the room from dropping below 65°F (18°C).** Brumation is a slowdown, not a cold-tolerance test. | Through November and December you weigh weekly, offer a soak and fresh greens every few days, keep the light cycle at 9 hours, and watch the room thermometer to</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -4543,6 +4724,16 @@
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr"/>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: **Substrate depth:** 6 to 12 in (15 to 30 cm) of a 50/50 mix of organic topsoil and washed play sand, the same fill as a [dig box], only deeper. | - Digging and straining for more than 24 to 48 hours with no eggs produced, or a partial clutch followed by the dragon stopping and looking exhausted. | But by day three she's still digging and straining with nothing produced, and by the start of day two past that (about 48 hours of unproductive digging) she loo | When in doubt, especially past that 24 to 48 hour digging window, call a reptile vet rather than waiting it out.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -4859,6 +5050,16 @@
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr"/>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: A home that stays above 65°F at night needs no night heat at all.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5339,6 +5540,16 @@
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr"/>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block; these figures have nothing behind them: ["Temperature", "78-80°F", "Bettas are tropical fish; cold water suppresses immune function and digestion"], | ["Ammonia", "0 ppm", "Even 0.25 ppm causes gill damage; any detectable reading is an emergency"], | ["Nitrate", "Under 20 ppm", "Byproduct of a healthy cycle; controlled with regular water changes"],</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -5384,6 +5595,16 @@
       <c r="K116" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: The dragon still needs strong UVB (Arcadia 12 percent or similar), a basking surface of 95 to 110°F for an adult, checked with an infrared thermometer, and a co</t>
         </is>
       </c>
     </row>
@@ -6244,6 +6465,16 @@
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: An adult boa eats every 10 to 14 days, stretching to every 2 to 4 weeks once mature, so it goes through one to three frozen rats a month. | Most boas won't reach that extreme, but 20 to 30 years is genuinely typical, part of why this species is such a serious long-term commitment. | 20 to 30 years is typical, and boas can exceed 40 with excellent care.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -6506,6 +6737,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 1 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Basking area 88 to 92°F, occasionally up to 95°F, ambient warm side 80 to 85°F, cool side 75 to 80°F, nighttime 70 to 80°F. | 60 to 70%, higher during shedding cycles.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -6787,6 +7028,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: A box turtle [brumates on its own numbers], warmer than a tortoise: a 10 to 14 day fast first, 45 to 50°F through the cold, weighed every two weeks, and woken f</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -8366,6 +8617,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M192" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -8409,6 +8670,16 @@
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr"/>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M193" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -8499,6 +8770,16 @@
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr"/>
+      <c r="L195" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M195" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -8636,6 +8917,16 @@
         </is>
       </c>
       <c r="K198" s="5" t="inlineStr"/>
+      <c r="L198" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -10098,6 +10389,16 @@
         </is>
       </c>
       <c r="K236" s="5" t="inlineStr"/>
+      <c r="L236" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M236" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -10141,6 +10442,16 @@
         </is>
       </c>
       <c r="K237" s="5" t="inlineStr"/>
+      <c r="L237" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M237" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Bigger is always better, aim for 30 to 36 inches or more in multiple dimensions, or a genuine flight cage if you can manage it.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
@@ -10535,6 +10846,16 @@
         </is>
       </c>
       <c r="K247" s="5" t="inlineStr"/>
+      <c r="L247" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M247" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block; these figures have nothing behind them: Most live 5 to 10 years, and occasional reports have individuals reaching up to 15 years under genuinely ideal conditions, an unusually long lifespan for a fish this small and unassuming at the bottom of the tank. | 5 to 10 years is typical, with some individuals living well past that, occasional reports reach up to 15 years under genuinely ideal conditions.</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -10738,6 +11059,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L252" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M252" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: 72 to 78°F suits most commonly kept species, and the exceptions sit at both ends of it. | A tank held at 80°F suits a sterbai school and is too warm for pandas.</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -11081,6 +11412,16 @@
         </is>
       </c>
       <c r="K261" s="5" t="inlineStr"/>
+      <c r="L261" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M261" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
@@ -11818,6 +12159,16 @@
         </is>
       </c>
       <c r="K280" s="5" t="inlineStr"/>
+      <c r="L280" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M280" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
@@ -12707,6 +13058,16 @@
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr"/>
+      <c r="L303" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M303" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: For a pair, aim for at least 30 inches long by 24 inches wide by 48 inches tall, adding roughly 4 additional square feet of floor space for each ferret beyond t | Keep the room in the 50 to 75°F range, and treat anything above about 80 to 85°F as a real heatstroke risk.</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
@@ -13190,6 +13551,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L316" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M316" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
@@ -13908,6 +14279,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L334" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M334" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
@@ -14181,6 +14562,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L341" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M341" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
@@ -14653,6 +15044,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L353" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M353" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Because this is a large breed, adult males run roughly 66 to 88 lbs and females 49 to 71 lbs, growth extends well past what smaller breeds need, some large-bree | For puppies, a large-breed growth formula that slows growth rate without capping final size has been shown to reduce the incidence or severity of hip dysplasia  | That window shrinks sharply the moment other symptoms appear, contact a vet within 8 to 12 hours if refusal comes with vomiting or diarrhea.</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
@@ -15819,6 +16220,16 @@
         </is>
       </c>
       <c r="K383" s="5" t="inlineStr"/>
+      <c r="L383" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M383" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
@@ -16034,6 +16445,16 @@
           <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L388" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M388" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: An estimated 70% of captive green iguanas die within their first year of life, and inadequate diet, lighting, and housing (the exact same three factors behind m</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
@@ -16124,6 +16545,16 @@
         </is>
       </c>
       <c r="K390" s="5" t="inlineStr"/>
+      <c r="L390" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M390" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
@@ -16167,6 +16598,16 @@
         </is>
       </c>
       <c r="K391" s="5" t="inlineStr"/>
+      <c r="L391" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M391" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="5" t="inlineStr">
@@ -16561,6 +17002,16 @@
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr"/>
+      <c r="L401" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
@@ -16787,6 +17238,16 @@
         </is>
       </c>
       <c r="K407" s="5" t="inlineStr"/>
+      <c r="L407" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M407" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block; these figures have nothing behind them: Work by Klasing and colleagues showed that mealworms fed a diet containing around 8 percent calcium for 48 hours had their whole-body calcium content raised substantially, enough to shift the calcium to phosphorus ratio  | Twenty four to seventy two hours before feeding, with 48 hours the most commonly cited figure.</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="5" t="inlineStr">
@@ -17255,6 +17716,16 @@
         </is>
       </c>
       <c r="K419" s="5" t="inlineStr"/>
+      <c r="L419" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="M419" s="5" t="inlineStr">
+        <is>
+          <t>The 84, 68 and 17 percent figures come from the listed 2024 owner survey, so they are covered.</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="5" t="inlineStr">
@@ -17442,6 +17913,16 @@
         </is>
       </c>
       <c r="K424" s="5" t="inlineStr"/>
+      <c r="L424" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M424" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: A large, solid-surface exercise wheel, 10.5 to 12 inches in diameter, like an axle-free running wheel, is essential, not optional.</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="5" t="inlineStr">
@@ -17707,6 +18188,16 @@
           <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L431" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M431" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="5" t="inlineStr">
@@ -18078,6 +18569,16 @@
           <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L440" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M440" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="5" t="inlineStr">
@@ -18258,6 +18759,16 @@
         </is>
       </c>
       <c r="K444" s="5" t="inlineStr"/>
+      <c r="L444" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M444" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="5" t="inlineStr">
@@ -18551,6 +19062,16 @@
         </is>
       </c>
       <c r="K451" s="5" t="inlineStr"/>
+      <c r="L451" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M451" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Resume feeding only after the new exoskeleton has visibly hardened - typically 7 to 14 days after a tarantula molt, a shorter window for smaller species like ju</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="5" t="inlineStr">
@@ -19047,6 +19568,16 @@
         </is>
       </c>
       <c r="K463" s="5" t="inlineStr"/>
+      <c r="L463" s="5" t="inlineStr">
+        <is>
+          <t>Probably none</t>
+        </is>
+      </c>
+      <c r="M463" s="5" t="inlineStr">
+        <is>
+          <t>Overview page with no Sources block. Its figures summarize the species guides, which carry their own sources, and a fact already on the site can stand unsourced. Add a source only for a figure no guide carries.</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="5" t="inlineStr">
@@ -19090,6 +19621,16 @@
         </is>
       </c>
       <c r="K464" s="5" t="inlineStr"/>
+      <c r="L464" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M464" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="5" t="inlineStr">
@@ -19293,6 +19834,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L469" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M469" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="5" t="inlineStr">
@@ -19445,6 +19996,16 @@
         </is>
       </c>
       <c r="K473" s="5" t="inlineStr"/>
+      <c r="L473" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="M473" s="5" t="inlineStr">
+        <is>
+          <t>Koi feeding stopping below about 48 to 50F has no listed source; the Saxby group size study backs the welfare points.</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="5" t="inlineStr">
@@ -19831,6 +20392,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L483" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M483" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="5" t="inlineStr">
@@ -19878,6 +20449,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L484" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M484" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
@@ -19925,6 +20506,16 @@
           <t>2026-10-06: same-site entries combined, 6 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L485" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M485" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Genus-level care sheets give a basking area of 80 to 84F for Uroplatus as a whole; that figure is for the lowland species and does not apply to this montane one</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="5" t="inlineStr">
@@ -19968,6 +20559,16 @@
         </is>
       </c>
       <c r="K486" s="5" t="inlineStr"/>
+      <c r="L486" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M486" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="5" t="inlineStr">
@@ -21326,6 +21927,16 @@
         </is>
       </c>
       <c r="K520" s="5" t="inlineStr"/>
+      <c r="L520" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M520" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="5" t="inlineStr">
@@ -21759,6 +22370,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L531" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M531" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="5" t="inlineStr">
@@ -22364,6 +22985,16 @@
         </is>
       </c>
       <c r="K546" s="5" t="inlineStr"/>
+      <c r="L546" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M546" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Prevention is the only tool available: [quarantine new fish] for at least 30 days before adding them to an established tank, buy from sources with healthy stock | Raise the temperature a couple of degrees a day, but only to about 81°F, the top of a neon's workable range. | The 86°F that kills ich on its own is [past what this fish tolerates], so a standard commercial ich medication, or aquarium salt at about a tablespoon per 5 gal</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="5" t="inlineStr">
@@ -22758,6 +23389,16 @@
         </is>
       </c>
       <c r="K556" s="5" t="inlineStr"/>
+      <c r="L556" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M556" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="5" t="inlineStr">
@@ -23199,6 +23840,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L567" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M567" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: Short sessions, 5 to 10 minutes, two or three times a day, work better than one long forced session.</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="5" t="inlineStr">
@@ -23246,6 +23897,16 @@
           <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L568" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M568" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figures not found in any listed source: A new parrotlet spends 30 to 45 days in a separate room while it is screened for chlamydia, polyomavirus and PBFD, with the resident birds cared for first each </t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="5" t="inlineStr">
@@ -23291,6 +23952,16 @@
       <c r="K569" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+        </is>
+      </c>
+      <c r="L569" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M569" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figures not found in any listed source: Minimum 18x18x24 inches for a single bird. | That's meaningfully narrower than the 3/8 to 5/8 inch range that's fine for a lovebird, and it comes down to size: a parrotlet's head is smaller, so spacing tha | Normal household range, roughly 65 to 80°F, works well. | A consistent day and night cycle also matters: roughly 10 to 12 hours of genuine, covered darkness supports both healthy sleep and a more stable hormonal cycle </t>
         </is>
       </c>
     </row>
@@ -23762,6 +24433,16 @@
         </is>
       </c>
       <c r="K580" s="5" t="inlineStr"/>
+      <c r="L580" s="5" t="inlineStr">
+        <is>
+          <t>Probably none</t>
+        </is>
+      </c>
+      <c r="M580" s="5" t="inlineStr">
+        <is>
+          <t>Overview page with no Sources block. Its figures summarize the species guides, which carry their own sources, and a fact already on the site can stand unsourced. Add a source only for a figure no guide carries.</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
@@ -24214,6 +24895,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L592" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M592" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
@@ -24959,6 +25650,16 @@
         </is>
       </c>
       <c r="K611" s="5" t="inlineStr"/>
+      <c r="L611" s="5" t="inlineStr">
+        <is>
+          <t>Probably none</t>
+        </is>
+      </c>
+      <c r="M611" s="5" t="inlineStr">
+        <is>
+          <t>Overview page with no Sources block. Its figures summarize the species guides, which carry their own sources, and a fact already on the site can stand unsourced. Add a source only for a figure no guide carries.</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="5" t="inlineStr">
@@ -25037,6 +25738,16 @@
         </is>
       </c>
       <c r="K613" s="5" t="inlineStr"/>
+      <c r="L613" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M613" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="5" t="inlineStr">
@@ -25166,6 +25877,16 @@
           <t>2026-10-06: same-site entries combined, 2 to 1 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L616" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M616" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="5" t="inlineStr">
@@ -25326,6 +26047,16 @@
         </is>
       </c>
       <c r="K620" s="5" t="inlineStr"/>
+      <c r="L620" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M620" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="5" t="inlineStr">
@@ -25439,6 +26170,16 @@
         </is>
       </c>
       <c r="K623" s="5" t="inlineStr"/>
+      <c r="L623" s="5" t="inlineStr">
+        <is>
+          <t>Probably none</t>
+        </is>
+      </c>
+      <c r="M623" s="5" t="inlineStr">
+        <is>
+          <t>Overview page with no Sources block. Its figures summarize the species guides, which carry their own sources, and a fact already on the site can stand unsourced. Add a source only for a figure no guide carries.</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="5" t="inlineStr">
@@ -26203,6 +26944,16 @@
         </is>
       </c>
       <c r="K643" s="5" t="inlineStr"/>
+      <c r="L643" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M643" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: A T5 tube's wattage is not its length: a 24-watt tube is about 22 inches long, a 39-watt tube about 34 inches and a 54-watt tube about 46 inches, so go by the l | A well-kept Russian tortoise can live 40 years or more, with some individuals reaching 50-plus, all while staying small enough at 5 to 9 inches to spend that en | 40 years or more is typical, with some individuals reaching 50-plus.</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="5" t="inlineStr">
@@ -28246,6 +28997,16 @@
         </is>
       </c>
       <c r="K696" s="5" t="inlineStr"/>
+      <c r="L696" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M696" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="5" t="inlineStr">
@@ -28538,6 +29299,16 @@
         </is>
       </c>
       <c r="K704" s="5" t="inlineStr"/>
+      <c r="L704" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M704" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="5" t="inlineStr">
@@ -28944,6 +29715,16 @@
         </is>
       </c>
       <c r="K714" s="5" t="inlineStr"/>
+      <c r="L714" s="5" t="inlineStr">
+        <is>
+          <t>Needs sources</t>
+        </is>
+      </c>
+      <c r="M714" s="5" t="inlineStr">
+        <is>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" s="5" t="inlineStr">
@@ -29642,6 +30423,16 @@
         </is>
       </c>
       <c r="K732" s="5" t="inlineStr"/>
+      <c r="L732" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M732" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="5" t="inlineStr">
@@ -29857,6 +30648,16 @@
         </is>
       </c>
       <c r="K737" s="5" t="inlineStr"/>
+      <c r="L737" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M737" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" s="5" t="inlineStr">
@@ -29986,6 +30787,16 @@
         </is>
       </c>
       <c r="K740" s="5" t="inlineStr"/>
+      <c r="L740" s="5" t="inlineStr">
+        <is>
+          <t>No source needed</t>
+        </is>
+      </c>
+      <c r="M740" s="5" t="inlineStr">
+        <is>
+          <t>Every figure checked is in the listed sources, so there is no claim to add a source for. Fewer than 3 stands, reason stated.</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="5" t="inlineStr">
@@ -30345,6 +31156,16 @@
           <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
         </is>
       </c>
+      <c r="L749" s="5" t="inlineStr">
+        <is>
+          <t>Needs a source or a rewrite</t>
+        </is>
+      </c>
+      <c r="M749" s="5" t="inlineStr">
+        <is>
+          <t>Figures not found in any listed source: The genuine risk shows up years later: adrenal disease is common in US pet ferrets, with one widely cited estimate putting it at around 70%, and insulinoma is t | Ferrets are carnivores that need roughly 32 to 40% protein, with carbohydrate under 25% and fiber under 2.5%.</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="5" t="inlineStr">
@@ -31012,6 +31833,16 @@
         </is>
       </c>
       <c r="K766" s="5" t="inlineStr"/>
+      <c r="L766" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="M766" s="5" t="inlineStr">
+        <is>
+          <t>No figures; the one review paper covers the behavioral claims, but it is the only source for a 1,478 word article.</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="5" t="inlineStr">
@@ -31375,6 +32206,16 @@
         </is>
       </c>
       <c r="K775" s="5" t="inlineStr"/>
+      <c r="L775" s="5" t="inlineStr">
+        <is>
+          <t>Probably none</t>
+        </is>
+      </c>
+      <c r="M775" s="5" t="inlineStr">
+        <is>
+          <t>Overview page with no Sources block. Its figures summarize the species guides, which carry their own sources, and a fact already on the site can stand unsourced. Add a source only for a figure no guide carries.</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="5" t="inlineStr">
@@ -31864,7 +32705,7 @@
       <c r="K788" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K788"/>
+  <autoFilter ref="A1:M788"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>217</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -676,6 +676,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -868,12 +869,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -1003,12 +1008,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -1261,20 +1270,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: They can live 20 to 30 years or more in the wild.</t>
+          <t>Figures not found in any listed source: They can live 20 to 30 years or more in the wild. | 2026-10-06: Lifespan now "up to 30 years in the wild", what the NHM source says.</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1479,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -1777,24 +1794,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: The purchase price is the smallest number on this page, and the seller decides more about the next 15 to 20 years than the price does. | 15 to 20 years with proper housing and care.</t>
+          <t>Figures not found in any listed source: The purchase price is the smallest number on this page, and the seller decides more about the next 15 to 20 years than the price does. | 15 to 20 years with proper housing and care. | 2026-10-06: Lifespan now "15 years or more" (ReptiFiles: at least 15 with good care); hub too. No source backed 20.</t>
         </is>
       </c>
     </row>
@@ -1939,14 +1956,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2031,24 +2048,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 6 to 1 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: caption="Bigger, hotter, and deeper than most reptile setups, an ackie monitor enclosure runs 130-170°F on the basking surface and needs 12-24 inches of diggabl | ## Temperature: 130 to 170°F on the Basking Surface | Ackies bask at surface temperatures roughly 130 to 170°F, measured directly on the basking stone or stack with an infrared thermometer, not air temperature. | A basking surface reading below about 130°F is too cool for this species to properly synthesize vitamin D.</t>
+          <t>Figures not found in any listed source: caption="Bigger, hotter, and deeper than most reptile setups, an ackie monitor enclosure runs 130-170°F on the basking surface and needs 12-24 inches of diggabl | ## Temperature: 130 to 170°F on the Basking Surface | Ackies bask at surface temperatures roughly 130 to 170°F, measured directly on the basking stone or stack with an infrared thermometer, not air temperature. | A basking surface reading below about 130°F is too cool for this species to properly synthesize vitamin D. | 2026-10-06: Owner call: basking now 158 to 172F (ReptiFiles temperatures page) on the setup guide, overview and hub; the MBD page is named for the 130F too-cool floor.</t>
         </is>
       </c>
     </row>
@@ -2486,14 +2503,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -3209,24 +3226,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Move affected fish into a bare 10 to 20 gallon [hospital tank] where possible, and give any new angelfish 30 to 60 days there before it joins the display.</t>
+          <t>Figures not found in any listed source: Move affected fish into a bare 10 to 20 gallon [hospital tank] where possible, and give any new angelfish 30 to 60 days there before it joins the display. | 2026-10-06: Quarantine now "at least 30 days" (Merck Management of Aquarium Fish, named in the Merck entry); unsourced hospital tank size removed.</t>
         </is>
       </c>
     </row>
@@ -3709,14 +3726,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -3809,24 +3826,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Basking area 100 to 110F, which overlaps the published 95 to 100F and 100 to 115F ranges, warm ambient in the 90s, cool side around 80F, with nighttime allowed  | For an enclosure this large, a 46 inch T5 HO bulb in the 12 to 14% range, spanning a quarter to half the enclosure's length on the warm side, targeting a baskin</t>
+          <t>Figures not found in any listed source: Basking area 100 to 110F, which overlaps the published 95 to 100F and 100 to 115F ranges, warm ambient in the 90s, cool side around 80F, with nighttime allowed  | For an enclosure this large, a 46 inch T5 HO bulb in the 12 to 14% range, spanning a quarter to half the enclosure's length on the warm side, targeting a baskin | 2026-10-06: Owner call: LafeberVet numbers, basking 95 to 100F, warm side 85 to 95F, cool around 75F, nights no lower than 75F (setup guide and hub). UVB line backed by ReptiFiles Tegu Humidity, Lighting &amp; Heating, now named; bulb about half the enclosure length.</t>
         </is>
       </c>
     </row>
@@ -4630,20 +4647,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J93" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr"/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: - **Offer a shallow, lukewarm soak.** About 15 minutes, chest-deep at most, never unsupervised. | - **Shorten the light cycle.** Drop to 8 to 10 hours of light on a timer, or leave lights off entirely if the dragon is fully asleep in its hide and not coming  | - **Keep the room from dropping below 65°F (18°C).** Brumation is a slowdown, not a cold-tolerance test. | Through November and December you weigh weekly, offer a soak and fresh greens every few days, keep the light cycle at 9 hours, and watch the room thermometer to</t>
+          <t>Figures not found in any listed source: - **Offer a shallow, lukewarm soak.** About 15 minutes, chest-deep at most, never unsupervised. | - **Shorten the light cycle.** Drop to 8 to 10 hours of light on a timer, or leave lights off entirely if the dragon is fully asleep in its hide and not coming  | - **Keep the room from dropping below 65°F (18°C).** Brumation is a slowdown, not a cold-tolerance test. | Through November and December you weigh weekly, offer a soak and fresh greens every few days, keep the light cycle at 9 hours, and watch the room thermometer to | 2026-10-06: NC State (8 hours of winter light, weekly soak) and Merck (winter photoperiod) added; VCA entry also names the housing page for the 65F floor; soak loses its 15 minute figure.</t>
         </is>
       </c>
     </row>
@@ -4718,20 +4739,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J95" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="inlineStr"/>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: **Substrate depth:** 6 to 12 in (15 to 30 cm) of a 50/50 mix of organic topsoil and washed play sand, the same fill as a [dig box], only deeper. | - Digging and straining for more than 24 to 48 hours with no eggs produced, or a partial clutch followed by the dragon stopping and looking exhausted. | But by day three she's still digging and straining with nothing produced, and by the start of day two past that (about 48 hours of unproductive digging) she loo | When in doubt, especially past that 24 to 48 hour digging window, call a reptile vet rather than waiting it out.</t>
+          <t>Figures not found in any listed source: **Substrate depth:** 6 to 12 in (15 to 30 cm) of a 50/50 mix of organic topsoil and washed play sand, the same fill as a [dig box], only deeper. | - Digging and straining for more than 24 to 48 hours with no eggs produced, or a partial clutch followed by the dragon stopping and looking exhausted. | But by day three she's still digging and straining with nothing produced, and by the start of day two past that (about 48 hours of unproductive digging) she loo | When in doubt, especially past that 24 to 48 hour digging window, call a reptile vet rather than waiting it out. | 2026-10-06: Dig box depth stands (owner: keeper practice). Morel et al. 2025 (Veterinary Sciences) added: hormone treatment works best within about 48 hours, so the 24 to 48 hour vet line now says why.</t>
         </is>
       </c>
     </row>
@@ -5044,20 +5069,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J103" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: A home that stays above 65°F at night needs no night heat at all.</t>
+          <t>Figures not found in any listed source: A home that stays above 65°F at night needs no night heat at all. | 2026-10-06: Owner keeps 65F nights. VCA Bearded Dragons, Housing added (no extra night heat while the cool end stays 65 to 80F).</t>
         </is>
       </c>
     </row>
@@ -5587,24 +5616,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J116" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: The dragon still needs strong UVB (Arcadia 12 percent or similar), a basking surface of 95 to 110°F for an adult, checked with an infrared thermometer, and a co</t>
+          <t>Figures not found in any listed source: The dragon still needs strong UVB (Arcadia 12 percent or similar), a basking surface of 95 to 110°F for an adult, checked with an infrared thermometer, and a co | 2026-10-06: ReptiFiles temperatures page (108 to 113F surface) named and UC Davis (88 to 95F basking) added, the same pair the dragon setup guide uses for 95 to 110F.</t>
         </is>
       </c>
     </row>
@@ -6459,20 +6488,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J138" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: An adult boa eats every 10 to 14 days, stretching to every 2 to 4 weeks once mature, so it goes through one to three frozen rats a month. | Most boas won't reach that extreme, but 20 to 30 years is genuinely typical, part of why this species is such a serious long-term commitment. | 20 to 30 years is typical, and boas can exceed 40 with excellent care.</t>
+          <t>Figures not found in any listed source: An adult boa eats every 10 to 14 days, stretching to every 2 to 4 weeks once mature, so it goes through one to three frozen rats a month. | Most boas won't reach that extreme, but 20 to 30 years is genuinely typical, part of why this species is such a serious long-term commitment. | 20 to 30 years is typical, and boas can exceed 40 with excellent care. | 2026-10-06: Feeding backed by PetMD boa care sheet and the ReptiFiles feeding page (named); lifespan by PetMD (up to 30) and AnAge (40.4 years captive maximum).</t>
         </is>
       </c>
     </row>
@@ -6727,24 +6760,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J144" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 1 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 1 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Basking area 88 to 92°F, occasionally up to 95°F, ambient warm side 80 to 85°F, cool side 75 to 80°F, nighttime 70 to 80°F. | 60 to 70%, higher during shedding cycles.</t>
+          <t>Figures not found in any listed source: Basking area 88 to 92°F, occasionally up to 95°F, ambient warm side 80 to 85°F, cool side 75 to 80°F, nighttime 70 to 80°F. | 60 to 70%, higher during shedding cycles. | 2026-10-06: Owner call: Chicago Exotics Animal Hospital added (warm zone 80 to 85F, basking up to 95F, nights 70 to 80F, humidity 50 to 70%), which backs the site figures.</t>
         </is>
       </c>
     </row>
@@ -7018,24 +7051,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J151" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: A box turtle [brumates on its own numbers], warmer than a tortoise: a 10 to 14 day fast first, 45 to 50°F through the cold, weighed every two weeks, and woken f</t>
+          <t>Figures not found in any listed source: A box turtle [brumates on its own numbers], warmer than a tortoise: a 10 to 14 day fast first, 45 to 50°F through the cold, weighed every two weeks, and woken f | 2026-10-06: Chicago Exotics Box Turtle Care (10 to 14 day fast, 45 to 50F, weigh every two weeks) and TVMF (7% action point) added, both already on the tortoise brumation guide.</t>
         </is>
       </c>
     </row>
@@ -8607,14 +8640,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J192" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J192" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L192" s="5" t="inlineStr">
@@ -8911,12 +8944,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J198" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K198" s="5" t="inlineStr"/>
+      <c r="J198" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -10383,12 +10420,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J236" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K236" s="5" t="inlineStr"/>
+      <c r="J236" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -10436,20 +10477,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J237" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K237" s="5" t="inlineStr"/>
+      <c r="J237" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M237" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Bigger is always better, aim for 30 to 36 inches or more in multiple dimensions, or a genuine flight cage if you can manage it.</t>
+          <t>Figures not found in any listed source: Bigger is always better, aim for 30 to 36 inches or more in multiple dimensions, or a genuine flight cage if you can manage it. | 2026-10-06: Owner call: the 30 to 36 inch target is gone; PetMD gives 24x24x30 as the minimum and says go as large as possible.</t>
         </is>
       </c>
     </row>
@@ -11049,24 +11094,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J252" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J252" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M252" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: 72 to 78°F suits most commonly kept species, and the exceptions sit at both ends of it. | A tank held at 80°F suits a sterbai school and is too warm for pandas.</t>
+          <t>Figures not found in any listed source: 72 to 78°F suits most commonly kept species, and the exceptions sit at both ends of it. | A tank held at 80°F suits a sterbai school and is too warm for pandas. | 2026-10-06: Range now 72 to 82F (Aquarium Co-Op, listed) on the setup guide and hub; SeriouslyFish backs the panda and sterbai ends.</t>
         </is>
       </c>
     </row>
@@ -13052,20 +13097,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J303" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K303" s="5" t="inlineStr"/>
+      <c r="J303" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M303" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: For a pair, aim for at least 30 inches long by 24 inches wide by 48 inches tall, adding roughly 4 additional square feet of floor space for each ferret beyond t | Keep the room in the 50 to 75°F range, and treat anything above about 80 to 85°F as a real heatstroke risk.</t>
+          <t>Figures not found in any listed source: For a pair, aim for at least 30 inches long by 24 inches wide by 48 inches tall, adding roughly 4 additional square feet of floor space for each ferret beyond t | Keep the room in the 50 to 75°F range, and treat anything above about 80 to 85°F as a real heatstroke risk. | 2026-10-06: Both sources linked only to homepages; now Merck Providing a Home for a Ferret and PetMD Ferret Care Sheet. Room 65 to 75F (Merck), heat risk above 80F (PetMD); cage now 24x24x36 for one (PetMD), larger for a pair. Setup guide and hub; the buy list covers line is untouched.</t>
         </is>
       </c>
     </row>
@@ -13541,14 +13590,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J316" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J316" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K316" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L316" s="5" t="inlineStr">
@@ -14269,14 +14318,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J334" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J334" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K334" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L334" s="5" t="inlineStr">
@@ -14552,14 +14601,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J341" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J341" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K341" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L341" s="5" t="inlineStr">
@@ -15034,24 +15083,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J353" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J353" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M353" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Because this is a large breed, adult males run roughly 66 to 88 lbs and females 49 to 71 lbs, growth extends well past what smaller breeds need, some large-bree | For puppies, a large-breed growth formula that slows growth rate without capping final size has been shown to reduce the incidence or severity of hip dysplasia  | That window shrinks sharply the moment other symptoms appear, contact a vet within 8 to 12 hours if refusal comes with vomiting or diarrhea.</t>
+          <t>Figures not found in any listed source: Because this is a large breed, adult males run roughly 66 to 88 lbs and females 49 to 71 lbs, growth extends well past what smaller breeds need, some large-bree | For puppies, a large-breed growth formula that slows growth rate without capping final size has been shown to reduce the incidence or severity of hip dysplasia  | That window shrinks sharply the moment other symptoms appear, contact a vet within 8 to 12 hours if refusal comes with vomiting or diarrhea. | 2026-10-06: Weights now AKC (65 to 90 lbs male, 50 to 70 female), AKC entry names the breed page; dysplasia now about one in five (hips) and 12 to 22% (elbows) from UFAW; vet window "the same day" instead of 8 to 12 hours.</t>
         </is>
       </c>
     </row>
@@ -16214,12 +16263,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J383" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K383" s="5" t="inlineStr"/>
+      <c r="J383" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K383" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -16435,24 +16488,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J388" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J388" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K388" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L388" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M388" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: An estimated 70% of captive green iguanas die within their first year of life, and inadequate diet, lighting, and housing (the exact same three factors behind m</t>
+          <t>Figures not found in any listed source: An estimated 70% of captive green iguanas die within their first year of life, and inadequate diet, lighting, and housing (the exact same three factors behind m | 2026-10-06: The 70% first year figure keeps the citation the cost guide already uses (Wikipedia, citing de Vosjoli 1992). Weak source: the original book could not be checked.</t>
         </is>
       </c>
     </row>
@@ -16539,12 +16592,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J390" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K390" s="5" t="inlineStr"/>
+      <c r="J390" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K390" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L390" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -16592,12 +16649,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J391" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K391" s="5" t="inlineStr"/>
+      <c r="J391" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K391" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -16996,12 +17057,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J401" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K401" s="5" t="inlineStr"/>
+      <c r="J401" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K401" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -17907,20 +17972,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J424" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K424" s="5" t="inlineStr"/>
+      <c r="J424" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K424" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L424" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M424" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: A large, solid-surface exercise wheel, 10.5 to 12 inches in diameter, like an axle-free running wheel, is essential, not optional.</t>
+          <t>Figures not found in any listed source: A large, solid-surface exercise wheel, 10.5 to 12 inches in diameter, like an axle-free running wheel, is essential, not optional. | 2026-10-06: Wheel size stands (owner: keeper practice).</t>
         </is>
       </c>
     </row>
@@ -18178,14 +18247,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J431" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J431" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K431" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L431" s="5" t="inlineStr">
@@ -18559,14 +18628,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J440" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J440" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K440" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 5 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L440" s="5" t="inlineStr">
@@ -19056,20 +19125,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J451" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K451" s="5" t="inlineStr"/>
+      <c r="J451" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K451" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M451" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Resume feeding only after the new exoskeleton has visibly hardened - typically 7 to 14 days after a tarantula molt, a shorter window for smaller species like ju</t>
+          <t>Figures not found in any listed source: Resume feeding only after the new exoskeleton has visibly hardened - typically 7 to 14 days after a tarantula molt, a shorter window for smaller species like ju | 2026-10-06: Tree of Life Tarantula Care (7 to 14 days adults, 3 to 7 juveniles post-molt) joins the Tree of Life entry.</t>
         </is>
       </c>
     </row>
@@ -19562,12 +19635,16 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J463" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K463" s="5" t="inlineStr"/>
+      <c r="J463" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K463" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
           <t>Probably none</t>
@@ -19615,12 +19692,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J464" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K464" s="5" t="inlineStr"/>
+      <c r="J464" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K464" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L464" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -19824,14 +19905,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J469" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J469" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K469" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L469" s="5" t="inlineStr">
@@ -20382,14 +20463,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J483" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J483" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L483" s="5" t="inlineStr">
@@ -20439,14 +20520,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J484" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J484" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K484" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L484" s="5" t="inlineStr">
@@ -20496,24 +20577,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J485" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J485" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K485" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 6 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 6 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M485" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Genus-level care sheets give a basking area of 80 to 84F for Uroplatus as a whole; that figure is for the lowland species and does not apply to this montane one</t>
+          <t>Figures not found in any listed source: Genus-level care sheets give a basking area of 80 to 84F for Uroplatus as a whole; that figure is for the lowland species and does not apply to this montane one | 2026-10-06: The genus-wide 80 to 84F was a store care sheet the guide sets aside; the number is dropped, the point kept.</t>
         </is>
       </c>
     </row>
@@ -20553,12 +20634,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J486" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K486" s="5" t="inlineStr"/>
+      <c r="J486" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K486" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L486" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -21921,12 +22006,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J520" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K520" s="5" t="inlineStr"/>
+      <c r="J520" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K520" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L520" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -22360,14 +22449,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J531" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J531" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L531" s="5" t="inlineStr">
@@ -22979,20 +23068,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J546" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K546" s="5" t="inlineStr"/>
+      <c r="J546" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K546" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L546" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M546" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Prevention is the only tool available: [quarantine new fish] for at least 30 days before adding them to an established tank, buy from sources with healthy stock | Raise the temperature a couple of degrees a day, but only to about 81°F, the top of a neon's workable range. | The 86°F that kills ich on its own is [past what this fish tolerates], so a standard commercial ich medication, or aquarium salt at about a tablespoon per 5 gal</t>
+          <t>Figures not found in any listed source: Prevention is the only tool available: [quarantine new fish] for at least 30 days before adding them to an established tank, buy from sources with healthy stock | Raise the temperature a couple of degrees a day, but only to about 81°F, the top of a neon's workable range. | The 86°F that kills ich on its own is [past what this fish tolerates], so a standard commercial ich medication, or aquarium salt at about a tablespoon per 5 gal | 2026-10-06: VCA Fish White Spot Disease added (86F, a tablespoon of salt per 5 gallons, 30 day quarantine). The 81F top stands as a site fact (neon setup guide).</t>
         </is>
       </c>
     </row>
@@ -23383,12 +23476,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J556" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K556" s="5" t="inlineStr"/>
+      <c r="J556" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K556" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L556" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -23830,24 +23927,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J567" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J567" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K567" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M567" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: Short sessions, 5 to 10 minutes, two or three times a day, work better than one long forced session.</t>
+          <t>Figures not found in any listed source: Short sessions, 5 to 10 minutes, two or three times a day, work better than one long forced session. | 2026-10-06: Session length stands (owner: keeper practice).</t>
         </is>
       </c>
     </row>
@@ -23887,24 +23984,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J568" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J568" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K568" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 4 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L568" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M568" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Figures not found in any listed source: A new parrotlet spends 30 to 45 days in a separate room while it is screened for chlamydia, polyomavirus and PBFD, with the resident birds cared for first each </t>
+          <t>Figures not found in any listed source: A new parrotlet spends 30 to 45 days in a separate room while it is screened for chlamydia, polyomavirus and PBFD, with the resident birds cared for first each  | 2026-10-06: CDFA pet bird guide added for the 30 day quarantine floor; 30 to 45 stays as the site-wide bird figure.</t>
         </is>
       </c>
     </row>
@@ -23944,24 +24041,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J569" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J569" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K569" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M569" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Figures not found in any listed source: Minimum 18x18x24 inches for a single bird. | That's meaningfully narrower than the 3/8 to 5/8 inch range that's fine for a lovebird, and it comes down to size: a parrotlet's head is smaller, so spacing tha | Normal household range, roughly 65 to 80°F, works well. | A consistent day and night cycle also matters: roughly 10 to 12 hours of genuine, covered darkness supports both healthy sleep and a more stable hormonal cycle </t>
+          <t>Figures not found in any listed source: Minimum 18x18x24 inches for a single bird. | That's meaningfully narrower than the 3/8 to 5/8 inch range that's fine for a lovebird, and it comes down to size: a parrotlet's head is smaller, so spacing tha | Normal household range, roughly 65 to 80°F, works well. | A consistent day and night cycle also matters: roughly 10 to 12 hours of genuine, covered darkness supports both healthy sleep and a more stable hormonal cycle  | 2026-10-06: 18x18 floor (The Vet Desk) and 1/4 inch bars (Lafeber) are sourced; 65 to 80F and 10 to 12 hours of darkness stand as site-wide bird figures. Note: the bird sleep guide states 10 to 12 hours without a source that says it; check in step 5.</t>
         </is>
       </c>
     </row>
@@ -24427,12 +24524,16 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J580" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K580" s="5" t="inlineStr"/>
+      <c r="J580" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K580" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L580" s="5" t="inlineStr">
         <is>
           <t>Probably none</t>
@@ -24885,14 +24986,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J592" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J592" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K592" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L592" s="5" t="inlineStr">
@@ -25644,12 +25745,16 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J611" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K611" s="5" t="inlineStr"/>
+      <c r="J611" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K611" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
           <t>Probably none</t>
@@ -25732,12 +25837,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J613" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K613" s="5" t="inlineStr"/>
+      <c r="J613" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K613" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -25867,14 +25976,14 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J616" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J616" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K616" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 2 to 1 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 2 to 1 entries. Now under 3: step 4 adds a source. 2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
         </is>
       </c>
       <c r="L616" s="5" t="inlineStr">
@@ -26041,12 +26150,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J620" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K620" s="5" t="inlineStr"/>
+      <c r="J620" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K620" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L620" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -26164,12 +26277,16 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J623" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K623" s="5" t="inlineStr"/>
+      <c r="J623" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K623" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
           <t>Probably none</t>
@@ -26938,20 +27055,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J643" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K643" s="5" t="inlineStr"/>
+      <c r="J643" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K643" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
+        </is>
+      </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M643" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: A T5 tube's wattage is not its length: a 24-watt tube is about 22 inches long, a 39-watt tube about 34 inches and a 54-watt tube about 46 inches, so go by the l | A well-kept Russian tortoise can live 40 years or more, with some individuals reaching 50-plus, all while staying small enough at 5 to 9 inches to spend that en | 40 years or more is typical, with some individuals reaching 50-plus.</t>
+          <t>Figures not found in any listed source: A T5 tube's wattage is not its length: a 24-watt tube is about 22 inches long, a 39-watt tube about 34 inches and a 54-watt tube about 46 inches, so go by the l | A well-kept Russian tortoise can live 40 years or more, with some individuals reaching 50-plus, all while staying small enough at 5 to 9 inches to spend that en | 40 years or more is typical, with some individuals reaching 50-plus. | 2026-10-06: ReptiFiles care sheet added (up to 50 years or more); line now "40 years or more is typical, and with excellent care some reach 50 or beyond" (the 40 stays because the cost math uses it). Hub matched.</t>
         </is>
       </c>
     </row>
@@ -28991,12 +29112,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J696" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K696" s="5" t="inlineStr"/>
+      <c r="J696" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K696" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L696" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -29293,12 +29418,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J704" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K704" s="5" t="inlineStr"/>
+      <c r="J704" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K704" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L704" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -30417,12 +30546,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J732" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K732" s="5" t="inlineStr"/>
+      <c r="J732" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K732" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L732" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -30642,12 +30775,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J737" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K737" s="5" t="inlineStr"/>
+      <c r="J737" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K737" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L737" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -30781,12 +30918,16 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J740" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K740" s="5" t="inlineStr"/>
+      <c r="J740" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K740" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L740" s="5" t="inlineStr">
         <is>
           <t>No source needed</t>
@@ -31146,24 +31287,24 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J749" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J749" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K749" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source.</t>
+          <t>2026-10-06: same-site entries combined, 3 to 2 entries. Now under 3: step 4 adds a source. 2026-10-06: step 4, every figure now has a source or was rewritten to one.</t>
         </is>
       </c>
       <c r="L749" s="5" t="inlineStr">
         <is>
-          <t>Needs a source or a rewrite</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M749" s="5" t="inlineStr">
         <is>
-          <t>Figures not found in any listed source: The genuine risk shows up years later: adrenal disease is common in US pet ferrets, with one widely cited estimate putting it at around 70%, and insulinoma is t | Ferrets are carnivores that need roughly 32 to 40% protein, with carbohydrate under 25% and fiber under 2.5%.</t>
+          <t>Figures not found in any listed source: The genuine risk shows up years later: adrenal disease is common in US pet ferrets, with one widely cited estimate putting it at around 70%, and insulinoma is t | Ferrets are carnivores that need roughly 32 to 40% protein, with carbohydrate under 25% and fiber under 2.5%. | 2026-10-06: Adrenal 70% now cited (Simone-Freilicher 2008, 70% of US pet ferrets in 2003); insulinoma now "one of the three most common cancers" (VCA); diet now 32 to 40% protein, 10 to 15% fat, fiber under 4% (VCA Feeding Ferrets).</t>
         </is>
       </c>
     </row>
@@ -32200,12 +32341,16 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J775" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K775" s="5" t="inlineStr"/>
+      <c r="J775" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K775" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: kept under 3 with the reason stated in column M (owner OK).</t>
+        </is>
+      </c>
       <c r="L775" s="5" t="inlineStr">
         <is>
           <t>Probably none</t>

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>151</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1065,20 +1065,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>No Sources block; these figures have nothing behind them: Adult boas range from about 5 to 13 feet long, and it's almost always the females occupying the top end of that range. | A healthy wild boa constrictor can survive 20 to 30 years, hunting rodents, birds, bats, lizards, and other small mammals along the way.</t>
+          <t>No Sources block; these figures have nothing behind them: Adult boas range from about 5 to 13 feet long, and it's almost always the females occupying the top end of that range. | A healthy wild boa constrictor can survive 20 to 30 years, hunting rodents, birds, bats, lizards, and other small mammals along the way. | 2026-10-06: Sources: ADW, Smithsonian, Boback 2012 and 2015. Fact 6 was wrong (boa constrictors have no heat pits) and is rewritten; litter now 10 to 64, about 25; size now up to about 13 feet.</t>
         </is>
       </c>
     </row>
@@ -1583,20 +1583,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Sources: AKC, GRCA, Golden Retriever Lifetime Study. Origin now the Nous by Tweed Water Spaniel cross.</t>
         </is>
       </c>
     </row>
@@ -1671,20 +1671,20 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>No figures; the Cell paper covers the chemotactile claim only.</t>
+          <t>No figures; the Cell paper covers the chemotactile claim only. | 2026-10-06: Sources now Smithsonian Ocean, National Aquarium, Wells 1987 and the Cell paper.</t>
         </is>
       </c>
     </row>
@@ -3103,20 +3103,20 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>No source needed</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Only the 55 gallon tank figure is outside the two listed studies.</t>
+          <t>Only the 55 gallon tank figure is outside the two listed studies. | 2026-10-06: The 55 gallon figure stands as a site fact (angelfish setup guide, sourced).</t>
         </is>
       </c>
     </row>
@@ -3560,20 +3560,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>No Sources block; these figures have nothing behind them: A proper adult enclosure alone, custom built at 8 feet by 4 feet by 4 feet minimum, routinely runs into the thousands once you add powerful basking and radiant heat, a real thermostat, high output UVB, and 12 to 18 inche | Worth being upfront about the first enclosure line above: it's a ready made 8ft PVC modular unit, 8x2x2ft, a partial match on length only, well short of the full 8x4x4ft footprint an adult tegu needs. | The substrate line is similarly a starting point, not a total, reaching 12 to 18 inches of depth across an 8 by 4 foot floor takes considerably more than one or two packs.</t>
+          <t>No Sources block; these figures have nothing behind them: A proper adult enclosure alone, custom built at 8 feet by 4 feet by 4 feet minimum, routinely runs into the thousands once you add powerful basking and radiant heat, a real thermostat, high output UVB, and 12 to 18 inche | Worth being upfront about the first enclosure line above: it's a ready made 8ft PVC modular unit, 8x2x2ft, a partial match on length only, well short of the full 8x4x4ft footprint an adult tegu needs. | The substrate line is similarly a starting point, not a total, reaching 12 to 18 inches of depth across an 8 by 4 foot floor takes considerably more than one or two packs. | 2026-10-06: Sources: LafeberVet, ReptiFiles. Unsourced "past 30 years" removed here and on the hub; 15 to 20 years on average.</t>
         </is>
       </c>
     </row>
@@ -5563,20 +5563,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J115" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr"/>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>No Sources block; these figures have nothing behind them: ["Temperature", "78-80°F", "Bettas are tropical fish; cold water suppresses immune function and digestion"], | ["Ammonia", "0 ppm", "Even 0.25 ppm causes gill damage; any detectable reading is an emergency"], | ["Nitrate", "Under 20 ppm", "Byproduct of a healthy cycle; controlled with regular water changes"],</t>
+          <t>No Sources block; these figures have nothing behind them: ["Temperature", "78-80°F", "Bettas are tropical fish; cold water suppresses immune function and digestion"], | ["Ammonia", "0 ppm", "Even 0.25 ppm causes gill damage; any detectable reading is an emergency"], | ["Nitrate", "Under 20 ppm", "Byproduct of a healthy cycle; controlled with regular water changes"], | 2026-10-06: Sources added: PetMD (betta care, nitrate), UF/IFAS FA031, Merck. pH now 6.5 to 7.8 (PetMD) here and on the hub; 0.25 ppm figure now "even low levels damage the gills" (UF/IFAS); dashes fixed.</t>
         </is>
       </c>
     </row>
@@ -8697,20 +8697,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J193" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J193" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr"/>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Two vague entries replaced: Whitney and Mehlhaff 1987, Vnuk 2004, Sechzer 1984, all linked. The disputed "a couple of feet" claim removed.</t>
         </is>
       </c>
     </row>
@@ -8797,20 +8797,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J195" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J195" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr"/>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Sources: Long Island Bird and Exotics Veterinary Clinic, ReptiFiles. Casque water-channeling claim replaced (display, possible heat exchange); "most common preventable cause of death" softened; dashes fixed.</t>
         </is>
       </c>
     </row>
@@ -10885,20 +10885,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J247" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J247" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K247" s="5" t="inlineStr"/>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M247" s="5" t="inlineStr">
         <is>
-          <t>No Sources block; these figures have nothing behind them: Most live 5 to 10 years, and occasional reports have individuals reaching up to 15 years under genuinely ideal conditions, an unusually long lifespan for a fish this small and unassuming at the bottom of the tank. | 5 to 10 years is typical, with some individuals living well past that, occasional reports reach up to 15 years under genuinely ideal conditions.</t>
+          <t>No Sources block; these figures have nothing behind them: Most live 5 to 10 years, and occasional reports have individuals reaching up to 15 years under genuinely ideal conditions, an unusually long lifespan for a fish this small and unassuming at the bottom of the tank. | 5 to 10 years is typical, with some individuals living well past that, occasional reports reach up to 15 years under genuinely ideal conditions. | 2026-10-06: Sources: Chewy Education (reviewed), Aquarium Co-Op. Unsourced "up to 15 years" removed; 5 to 10 years varying by species.</t>
         </is>
       </c>
     </row>
@@ -11451,20 +11451,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J261" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J261" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K261" s="5" t="inlineStr"/>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M261" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Four papers verified and linked.</t>
         </is>
       </c>
     </row>
@@ -12198,20 +12198,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J280" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J280" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K280" s="5" t="inlineStr"/>
       <c r="L280" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M280" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Sources added: Merck GDV, ACVS, AKC, Glickman 2000. "Within an hour" of meals softened to "right before or after"; dashes fixed.</t>
         </is>
       </c>
     </row>
@@ -17297,20 +17297,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J407" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J407" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K407" s="5" t="inlineStr"/>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M407" s="5" t="inlineStr">
         <is>
-          <t>No Sources block; these figures have nothing behind them: Work by Klasing and colleagues showed that mealworms fed a diet containing around 8 percent calcium for 48 hours had their whole-body calcium content raised substantially, enough to shift the calcium to phosphorus ratio  | Twenty four to seventy two hours before feeding, with 48 hours the most commonly cited figure.</t>
+          <t>No Sources block; these figures have nothing behind them: Work by Klasing and colleagues showed that mealworms fed a diet containing around 8 percent calcium for 48 hours had their whole-body calcium content raised substantially, enough to shift the calcium to phosphorus ratio  | Twenty four to seventy two hours before feeding, with 48 hours the most commonly cited figure. | 2026-10-06: Its plain Sources list is now linked and verified. Klasing finding corrected (calcium rose within a day; 76% as bioavailable as oyster shell); the 48 hour timing now credited to Allen and Oftedal; Coslik paper is calcium and vitamin A, not E.</t>
         </is>
       </c>
     </row>
@@ -17775,20 +17775,20 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J419" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J419" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K419" s="5" t="inlineStr"/>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>No source needed</t>
         </is>
       </c>
       <c r="M419" s="5" t="inlineStr">
         <is>
-          <t>The 84, 68 and 17 percent figures come from the listed 2024 owner survey, so they are covered.</t>
+          <t>The 84, 68 and 17 percent figures come from the listed 2024 owner survey, so they are covered. | 2026-10-06: Survey figures are in the listed 2024 study; no change.</t>
         </is>
       </c>
     </row>
@@ -18822,20 +18822,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J444" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J444" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K444" s="5" t="inlineStr"/>
       <c r="L444" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M444" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Book and three papers verified and linked.</t>
         </is>
       </c>
     </row>
@@ -20071,20 +20071,20 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J473" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J473" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K473" s="5" t="inlineStr"/>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>No source needed</t>
         </is>
       </c>
       <c r="M473" s="5" t="inlineStr">
         <is>
-          <t>Koi feeding stopping below about 48 to 50F has no listed source; the Saxby group size study backs the welfare points.</t>
+          <t>Koi feeding stopping below about 48 to 50F has no listed source; the Saxby group size study backs the welfare points. | 2026-10-06: The 48 to 50F feeding cutoff stands as a site fact (koi feeding guide, sourced).</t>
         </is>
       </c>
     </row>
@@ -29838,20 +29838,20 @@
           <t>Add a Sources block with 3 to 5 sources for the main claims, reusing what the sibling guides already list.</t>
         </is>
       </c>
-      <c r="J714" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J714" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K714" s="5" t="inlineStr"/>
       <c r="L714" s="5" t="inlineStr">
         <is>
-          <t>Needs sources</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M714" s="5" t="inlineStr">
         <is>
-          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources.</t>
+          <t>No Sources block and no figures to match, but it makes factual claims (behavior, science or medical) that need 3 to 5 real sources. | 2026-10-06: Sources: VCA chew toys, Merck GI obstruction, Wooten and Smith 2013, Coppinger 2001, Panksepp 1998. The 15 minute puzzle claim removed, lead paint dropped, Coppinger and Panksepp overstatements trimmed.</t>
         </is>
       </c>
     </row>
@@ -31968,20 +31968,20 @@
           <t>Under 3: add a source for the claims that have none, reusing one already listed on a sibling guide.</t>
         </is>
       </c>
-      <c r="J766" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J766" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K766" s="5" t="inlineStr"/>
       <c r="L766" s="5" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M766" s="5" t="inlineStr">
         <is>
-          <t>No figures; the one review paper covers the behavioral claims, but it is the only source for a 1,478 word article.</t>
+          <t>No figures; the one review paper covers the behavioral claims, but it is the only source for a 1,478 word article. | 2026-10-06: Its one source had the wrong title (it is Barrios et al. 2025); AAFP/ISFM guidelines and Dantas 2016 added; stress hormone and 10 to 15 minute claims softened.</t>
         </is>
       </c>
     </row>

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M788"/>
+  <dimension ref="A1:N788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -721,6 +721,7 @@
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="90" customWidth="1" min="13" max="13"/>
+    <col width="90" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -789,6 +790,11 @@
           <t>Step 4 detail</t>
         </is>
       </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Step 5 result</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -826,12 +832,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Reptiles Magazine: Black and White Tegus Can Warm Their Bodies During Mating Season]; - [Phys.org: Lizard found to heat itself during mating season]. Now 4 linked. The paper itself carries the 10C, sixfold heart rate and burrow findings, so two news write-ups of it went.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2105,12 +2116,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Wikipedia: African Fat-Tailed Gecko]. Now 5 linked. Wikipedia added nothing ADW and Tree of Life do not.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2148,12 +2164,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the three studies carry the research section, PetMD the egg-binding claim, ADW the wild biology and Tree of Life the care figures.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2697,14 +2718,19 @@
           <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 11 to 10 entries. 2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept all ten: the Mech papers, his site (print history), Schenkel, NPS, the Ripple paper and the MacNulty comment plus its release (the "modest and patchy" framing could not be checked in the paywalled comment), and AVSAB each carry a distinct claim.</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2914,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Caridina multidentata - Wikipedia]. Now 5 linked. Wikipedia added nothing the others do not.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2935,12 +2966,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Caridina multidentata - Wikipedia]. Now 5 linked. Wikipedia added nothing; even the Japan and Taiwan range is in Aquarium Co-Op, Shrimp Science and Fishkeeping World.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3478,12 +3514,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -4008,12 +4049,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr"/>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [VCA Animal Hospitals: Axolotls as Pets]. Now 5 linked. LafeberVet covers everything VCA carried; the rest each carry their own claim (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -4261,12 +4307,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: PetMD care, EIA electricity, ARH cost data, the two spider-morph papers and the Zoo Med bulb specs each back a figure or claim.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4339,12 +4390,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -4421,12 +4477,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr"/>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -5442,14 +5503,19 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J112" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 7 to 6 entries.</t>
+        </is>
+      </c>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: Merck, UF/IFAS and the four papers each back a separate disease or finding.</t>
         </is>
       </c>
     </row>
@@ -6336,12 +6402,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J134" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr"/>
+      <c r="N134" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [PetMD: Blue-Tongued Skink (Tiliqua) Species Guide]. Now 5 linked. PetMD added nothing the others do not; the sexing study, ReptiFiles, LafeberVet, Australian Museum and Long Island each carry a section.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -6631,12 +6702,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J141" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr"/>
+      <c r="N141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: each entry backs its own section, from handling and restraint to wild behavior and bite wound bacteria.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -6887,14 +6963,19 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J147" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 8 to 6 entries.</t>
+        </is>
+      </c>
+      <c r="N147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: care sheet, lifespan (Indiana DNR), vet, produce prices, bulb specs and electricity each feed a figure.</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7279,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J154" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr"/>
+      <c r="N154" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: Cornell, the OFA grading scheme and four studies each back distinct findings.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -7876,12 +7962,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J172" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J172" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr"/>
+      <c r="N172" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Already 5: the first line is an evidence note, not a source.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -10003,12 +10094,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J225" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J225" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K225" s="5" t="inlineStr"/>
+      <c r="N225" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [PetMD: Cockatoo Bird Species, Types, Lifespan, and Care]. Now 6 linked. LafeberVet body language, Chicago Exotics care, VCA training, Clark on cockatoo needs, Humane World on leases and Miami-Dade on nuisance reports each carry a section.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -11644,12 +11740,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J266" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J266" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K266" s="5" t="inlineStr"/>
+      <c r="N266" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: each source carries a section the others do not (diet base, dental spurs, appetite causes, sugar rule, welfare guidance).</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
@@ -12155,12 +12256,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Keep journals.plos.org studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J279" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J279" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K279" s="5" t="inlineStr"/>
+      <c r="N279" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: research review, each study carries its own section (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
@@ -12746,12 +12852,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J294" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J294" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K294" s="5" t="inlineStr"/>
+      <c r="N294" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the staging guidelines, consensus guidelines, Cornell and three breed studies each back distinct claims.</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
@@ -13189,12 +13300,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J305" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J305" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K305" s="5" t="inlineStr"/>
+      <c r="N305" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Already 5: the first line is an evidence note, not a source.</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
@@ -14488,12 +14604,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J338" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J338" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K338" s="5" t="inlineStr"/>
+      <c r="N338" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Six real sources after the evidence note: four studies for the research section, ReptiFiles and PetMD for the cohabitation decision (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
@@ -15140,12 +15261,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J354" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J354" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K354" s="5" t="inlineStr"/>
+      <c r="N354" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
@@ -15288,12 +15414,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J358" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J358" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K358" s="5" t="inlineStr"/>
+      <c r="N358" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
@@ -15643,14 +15774,19 @@
           <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J367" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J367" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K367" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
+      <c r="N367" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: research review, each study backs its own section.</t>
         </is>
       </c>
     </row>
@@ -16320,12 +16456,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J384" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J384" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K384" s="5" t="inlineStr"/>
+      <c r="N384" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: VCA carries the first-visit workup and each other entry a price or lifespan claim (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
@@ -16445,12 +16586,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J387" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J387" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K387" s="5" t="inlineStr"/>
+      <c r="N387" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: ColumbiaDoctors carries the bite first aid and Chicago Exotics the adult weight; the testosterone study and Kaplan back the breeding aggression section.</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
@@ -16811,12 +16957,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J395" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J395" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K395" s="5" t="inlineStr"/>
+      <c r="N395" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Oxbow Animal Health: Guinea Pig Care Guide]. Now 5 linked. Oxbow added nothing the vet sources do not.</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
@@ -16889,12 +17040,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J397" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J397" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K397" s="5" t="inlineStr"/>
+      <c r="N397" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note covers RSPCA and Lafeber; MSPCA (urogenital) and Illinois (spaying) carry their own sections.</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="5" t="inlineStr">
@@ -17014,12 +17170,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J400" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J400" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K400" s="5" t="inlineStr"/>
+      <c r="N400" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: Humane World carries the footprint, RSPCA the heat figures, Lafeber the cleaning and sipper lines, VCA the only heavy-bowl option, NC State the pellet amount, Merck the housing basics.</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="5" t="inlineStr">
@@ -17467,12 +17628,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J411" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J411" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K411" s="5" t="inlineStr"/>
+      <c r="N411" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [RSPCA]. Now 5 linked. The RSPCA entry added nothing the others do not.</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="5" t="inlineStr">
@@ -17510,12 +17676,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J412" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J412" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K412" s="5" t="inlineStr"/>
+      <c r="N412" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="5" t="inlineStr">
@@ -17553,12 +17724,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J413" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J413" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K413" s="5" t="inlineStr"/>
+      <c r="N413" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the O'Neill study, Merck, Woodgreen, Chicago Exotics, Dial A Vet and CDC each carry a section.</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
@@ -18930,12 +19106,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J446" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J446" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K446" s="5" t="inlineStr"/>
+      <c r="N446" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - ["Immortal" Jellyfish Swarm World's Oceans (National Geographic)]; - [Genetic study of immortal jellyfish may help explain its longevity (Phys.org)]. Now 12 linked. Research piece: each remaining paper, the PNAS correction and the two news pieces with direct quotes (Science News, The Scientist) back a distinct claim; EBSCO carries the size.</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="5" t="inlineStr">
@@ -19221,12 +19402,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J453" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J453" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K453" s="5" t="inlineStr"/>
+      <c r="N453" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: each source carries its own section (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="5" t="inlineStr">
@@ -19315,12 +19501,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J455" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J455" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K455" s="5" t="inlineStr"/>
+      <c r="N455" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: Merck, Cornell and four studies each back distinct findings.</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="5" t="inlineStr">
@@ -20381,12 +20572,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J481" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J481" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K481" s="5" t="inlineStr"/>
+      <c r="N481" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Already 5: the first line is an evidence note, not a source.</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="5" t="inlineStr">
@@ -20691,12 +20887,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J487" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J487" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr"/>
+      <c r="N487" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [LafeberVet: Basic Information Sheet, Leopard Gecko]. Now 5 linked. LafeberVet added nothing the others do not here.</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="5" t="inlineStr">
@@ -20769,12 +20970,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J489" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J489" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K489" s="5" t="inlineStr"/>
+      <c r="N489" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Safarivet: Feeding Leopard Geckos]. Now 5 linked. Safarivet added nothing the others do not.</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="5" t="inlineStr">
@@ -20851,12 +21057,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J491" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J491" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K491" s="5" t="inlineStr"/>
+      <c r="N491" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: ReptiFiles alone has the respiratory signs and stick tail section, VCA the single-female line, and each study its own finding.</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
@@ -20941,12 +21152,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J493" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J493" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K493" s="5" t="inlineStr"/>
+      <c r="N493" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [ReptiFiles]. Now 3 linked. ReptiFiles added nothing PetMD, VCA and the UVB studies do not.</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="5" t="inlineStr">
@@ -21300,12 +21516,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J502" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J502" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K502" s="5" t="inlineStr"/>
+      <c r="N502" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: VCA, LafeberVet, PetMD egg binding, ADW, Merck nutrition and CDC psittacosis each cover a different condition.</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="5" t="inlineStr">
@@ -21807,12 +22028,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J515" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J515" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K515" s="5" t="inlineStr"/>
+      <c r="N515" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Already 5: the first line is an evidence note, not a source.</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="5" t="inlineStr">
@@ -22254,12 +22480,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J526" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J526" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K526" s="5" t="inlineStr"/>
+      <c r="N526" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: Merck, Aquarium Co-Op, the salt-myth article, the salt types page, the sailfin study and PetMD each carry a separate point.</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="5" t="inlineStr">
@@ -22834,14 +23065,19 @@
           <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J540" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J540" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K540" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
+      <c r="N540" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Secrets of naked mole-rat cancer resistance unearthed (University of Cambridge)]. Now 12 linked. Research piece: each remaining study backs its own section, and the eLife paper, comment and response are the aging debate itself.</t>
         </is>
       </c>
     </row>
@@ -23537,12 +23773,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J557" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J557" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K557" s="5" t="inlineStr"/>
+      <c r="N557" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Six real sources after the evidence note, each backing its own finding.</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="5" t="inlineStr">
@@ -23724,14 +23965,19 @@
           <t>Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J562" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J562" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K562" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 14 to 11 entries.</t>
+        </is>
+      </c>
+      <c r="N562" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [What is a pangolin? (Save Pangolins)]. Now 10 linked. Trade, legal and biology sections each rest on their own source (IUCN group and news, USFWS proposal and rule, Ingram, IFAW, Mongabay, WWF, ADW, Smithsonian).</t>
         </is>
       </c>
     </row>
@@ -23845,12 +24091,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J565" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J565" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K565" s="5" t="inlineStr"/>
+      <c r="N565" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Already 5: the first line is an evidence note, not a source.</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="5" t="inlineStr">
@@ -24251,12 +24502,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J573" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J573" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K573" s="5" t="inlineStr"/>
+      <c r="N573" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: six separate studies, each the basis for one section.</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="5" t="inlineStr">
@@ -25433,12 +25689,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J603" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J603" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K603" s="5" t="inlineStr"/>
+      <c r="N603" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
@@ -25511,12 +25772,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J605" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J605" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K605" s="5" t="inlineStr"/>
+      <c r="N605" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: HRS space standard, PetMD giant breeds, litter training, RSPCA welfare, Merck housing and PDSA flystrike each carry a section.</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
@@ -26107,12 +26373,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J619" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J619" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K619" s="5" t="inlineStr"/>
+      <c r="N619" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [LafeberVet: Care of Aquatic &amp; Semi-Aquatic Turtles]. Now 5 linked. LafeberVet added nothing VCA and the others do not; ReptiFiles eggs stays as the only nesting-area source (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="5" t="inlineStr">
@@ -26825,12 +27096,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J637" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J637" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K637" s="5" t="inlineStr"/>
+      <c r="N637" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Already 5: the first line is an evidence note, not a source.</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="5" t="inlineStr">
@@ -27221,12 +27497,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J647" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J647" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K647" s="5" t="inlineStr"/>
+      <c r="N647" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: the in-file note lists what each source alone carries.</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="5" t="inlineStr">
@@ -27486,12 +27767,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J654" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J654" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K654" s="5" t="inlineStr"/>
+      <c r="N654" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Robert G. Sprackland, Reptiles Magazine: 5 Tips for Keeping the Savannah Monitor]. Now 5 linked. The Reptiles Magazine tips page added nothing the vet sheets do not.</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="5" t="inlineStr">
@@ -27599,14 +27885,19 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J657" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J657" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K657" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 7 to 6 entries.</t>
+        </is>
+      </c>
+      <c r="N657" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: six sources for four species, each carrying claims no other one does (in-file note).</t>
         </is>
       </c>
     </row>
@@ -27685,12 +27976,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J659" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J659" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K659" s="5" t="inlineStr"/>
+      <c r="N659" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: research piece; each paper backs one mechanism, Konstanz the plain account, and the Fish Vet the stomachless-fish line.</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="5" t="inlineStr">
@@ -27923,12 +28219,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J665" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J665" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K665" s="5" t="inlineStr"/>
+      <c r="N665" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Lorises at risk from illegal trade (TRAFFIC)]. Now 7 linked. Bite cases, venom biochemistry, allergen structure, the prey study, trade and the Turkey case each need their own source.</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="5" t="inlineStr">
@@ -28894,12 +29195,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J690" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J690" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K690" s="5" t="inlineStr"/>
+      <c r="N690" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: care sheet, the surgery case, bladder stones, produce prices, the heat emitter specs and electricity each feed a figure.</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="5" t="inlineStr">
@@ -29475,12 +29781,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J705" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J705" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K705" s="5" t="inlineStr"/>
+      <c r="N705" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: each species lifespan needs its own zoo or university page (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="5" t="inlineStr">
@@ -29709,12 +30020,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J711" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J711" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K711" s="5" t="inlineStr"/>
+      <c r="N711" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: each species size needs its own page (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="5" t="inlineStr">
@@ -29895,12 +30211,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J715" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J715" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K715" s="5" t="inlineStr"/>
+      <c r="N715" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: each entry carries a claim no other supports (in-file note).</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="5" t="inlineStr">
@@ -30732,12 +31053,17 @@
           <t>Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing. Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J736" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J736" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K736" s="5" t="inlineStr"/>
+      <c r="N736" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Five Easy Ways to Help Prevent Bird Collisions, Cornellians, Cornell University]; - [Sick Birds and Bird Diseases, Project FeederWatch, The Cornell Lab of Ornithology]. Now 10 linked. Each remaining entry backs its own section: eagle counts, ID skills, ethics code, collision and decline studies, raptor vision, feeder hygiene.</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="5" t="inlineStr">
@@ -30975,12 +31301,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J741" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J741" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K741" s="5" t="inlineStr"/>
+      <c r="N741" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Reptile Direct: Uromastyx 101]. Now 5 linked. Reptile Direct added nothing the others do not.</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="5" t="inlineStr">
@@ -31488,14 +31819,19 @@
           <t>Keep, reason stated. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J754" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J754" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K754" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: reviewed in step 3, kept separate with the reason stated.</t>
+        </is>
+      </c>
+      <c r="N754" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Kept: one primary study per animal plus NOAA (in-file note).</t>
         </is>
       </c>
     </row>
@@ -31539,12 +31875,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Keep onlinelibrary.wiley.com studies separate, reason stated; drop any study whose claim another listed source already covers. Keep nature.com studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J755" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J755" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K755" s="5" t="inlineStr"/>
+      <c r="N755" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Amphiprion percula (Animal Diversity Web, University of Michigan Museum of Zoology)]. Now 8 linked. Research piece: each remaining study backs one finding (shrinking, lifespan, inheritance, non-breeders, mucus, microbiome, protein profiling).</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="5" t="inlineStr">
@@ -31773,12 +32114,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J761" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J761" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K761" s="5" t="inlineStr"/>
+      <c r="N761" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Chicago Exotics Animal Hospital: White's Tree Frog Care]. Now 5 linked. Chicago Exotics added nothing the others do not; Roscoe stays for the cleaner and disinfectant section.</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="5" t="inlineStr">
@@ -32099,12 +32445,17 @@
           <t>Keep pubmed.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J769" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J769" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K769" s="5" t="inlineStr"/>
+      <c r="N769" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Bare-nosed Wombat (The Australian Museum)]; - [Wombats (NSW Department of Climate Change, Energy, the Environment and Water)]. Now 7 linked. The two cube studies, the APS abstract, the Ig Nobel record, the drying paper, the biology review, the hindgut paper and Tasmania DNRE each back a distinct claim.</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="5" t="inlineStr">
@@ -32228,12 +32579,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Keep pubmed.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers. Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J772" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J772" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K772" s="5" t="inlineStr"/>
+      <c r="N772" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Wood Frog (Maine Department of Inland Fisheries and Wildlife)]. Now 8 linked. Research piece: each remaining paper backs one physiological finding; NPS carries the range.</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="5" t="inlineStr">
@@ -32542,12 +32898,17 @@
           <t>Over 5 after combining: check each entry's claims against the others and trim to 5, or state why more are needed.</t>
         </is>
       </c>
-      <c r="J780" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J780" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K780" s="5" t="inlineStr"/>
+      <c r="N780" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Dropped: - [Zebrafish, University of Oregon Research and Innovation]. Now 5 linked. The University of Oregon page added nothing the genome paper does not.</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="5" t="inlineStr">

--- a/SOURCE_OVERLAP.xlsx
+++ b/SOURCE_OVERLAP.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -976,12 +976,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1203,12 +1208,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1377,12 +1387,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1551,12 +1566,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2356,12 +2376,17 @@
           <t>Combine fws.gov into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Combined: two USFWS fact sheets combined into one entry, 5 to 4.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2403,12 +2428,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2671,12 +2701,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3928,12 +3963,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -5386,12 +5426,17 @@
           <t>Keep ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J109" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr"/>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -6620,12 +6665,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J139" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr"/>
+      <c r="N139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -7019,12 +7069,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J148" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr"/>
+      <c r="N148" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -7366,12 +7421,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J156" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr"/>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -8458,12 +8518,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J185" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr"/>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -8649,14 +8714,19 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J190" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J190" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K190" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 6 to 4 entries.</t>
+        </is>
+      </c>
+      <c r="N190" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8915,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J194" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J194" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K194" s="5" t="inlineStr"/>
+      <c r="N194" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -8945,12 +9020,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J196" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J196" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr"/>
+      <c r="N196" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -8992,12 +9072,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J197" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J197" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr"/>
+      <c r="N197" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -9739,12 +9824,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J216" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J216" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K216" s="5" t="inlineStr"/>
+      <c r="N216" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -9942,12 +10032,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J221" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J221" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K221" s="5" t="inlineStr"/>
+      <c r="N221" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -10704,12 +10799,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J240" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J240" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr"/>
+      <c r="N240" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -11038,12 +11138,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J248" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J248" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K248" s="5" t="inlineStr"/>
+      <c r="N248" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -12057,12 +12162,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J274" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J274" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K274" s="5" t="inlineStr"/>
+      <c r="N274" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
@@ -12431,12 +12541,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J283" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J283" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K283" s="5" t="inlineStr"/>
+      <c r="N283" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
@@ -13025,12 +13140,17 @@
           <t>Keep ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J298" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J298" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K298" s="5" t="inlineStr"/>
+      <c r="N298" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
@@ -14176,14 +14296,19 @@
           <t>Combine usgs.gov into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
-      <c r="J328" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J328" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K328" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
+      <c r="N328" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Combined: three USGS Water Science School pages combined into one entry, 4 to 2; every claim keeps the same pages behind it.</t>
         </is>
       </c>
     </row>
@@ -14227,12 +14352,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J329" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J329" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K329" s="5" t="inlineStr"/>
+      <c r="N329" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
@@ -14313,14 +14443,19 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J331" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J331" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K331" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
+      <c r="N331" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -15501,12 +15636,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J360" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J360" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K360" s="5" t="inlineStr"/>
+      <c r="N360" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
@@ -16013,12 +16153,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J373" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J373" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K373" s="5" t="inlineStr"/>
+      <c r="N373" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="5" t="inlineStr">
@@ -16204,12 +16349,17 @@
           <t>Keep cambridge.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J378" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J378" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K378" s="5" t="inlineStr"/>
+      <c r="N378" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
@@ -16508,12 +16658,17 @@
           <t>Keep link.springer.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J385" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J385" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K385" s="5" t="inlineStr"/>
+      <c r="N385" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="5" t="inlineStr">
@@ -17515,12 +17670,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J408" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J408" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K408" s="5" t="inlineStr"/>
+      <c r="N408" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="5" t="inlineStr">
@@ -18519,14 +18679,19 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J433" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J433" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K433" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
+      <c r="N433" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -18605,12 +18770,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J435" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J435" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K435" s="5" t="inlineStr"/>
+      <c r="N435" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="5" t="inlineStr">
@@ -18916,12 +19086,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J442" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J442" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K442" s="5" t="inlineStr"/>
+      <c r="N442" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="5" t="inlineStr">
@@ -19454,12 +19629,17 @@
           <t>Keep ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J454" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J454" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K454" s="5" t="inlineStr"/>
+      <c r="N454" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="5" t="inlineStr">
@@ -19592,12 +19772,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J457" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J457" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr"/>
+      <c r="N457" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="5" t="inlineStr">
@@ -19944,12 +20129,17 @@
           <t>Keep link.springer.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J465" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J465" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr"/>
+      <c r="N465" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="5" t="inlineStr">
@@ -21278,12 +21468,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J496" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J496" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K496" s="5" t="inlineStr"/>
+      <c r="N496" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
@@ -21325,14 +21520,19 @@
           <t>Keep animallaw.info entries separate, reason stated.</t>
         </is>
       </c>
-      <c r="J497" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J497" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K497" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
+      <c r="N497" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Combined: three Animal Legal &amp; Historical Center explainer pages (not statutes) combined, 4 to 2; every claim keeps the same pages behind it.</t>
         </is>
       </c>
     </row>
@@ -21673,12 +21873,17 @@
           <t>Keep ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J506" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J506" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K506" s="5" t="inlineStr"/>
+      <c r="N506" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="5" t="inlineStr">
@@ -21907,12 +22112,17 @@
           <t>Keep research-information.bris.ac.uk studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J512" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J512" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K512" s="5" t="inlineStr"/>
+      <c r="N512" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="5" t="inlineStr">
@@ -22602,12 +22812,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J529" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J529" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K529" s="5" t="inlineStr"/>
+      <c r="N529" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="5" t="inlineStr">
@@ -22854,12 +23069,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J535" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J535" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K535" s="5" t="inlineStr"/>
+      <c r="N535" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="5" t="inlineStr">
@@ -22901,12 +23121,17 @@
           <t>Keep jstage.jst.go.jp studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J536" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J536" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K536" s="5" t="inlineStr"/>
+      <c r="N536" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="5" t="inlineStr">
@@ -23191,12 +23416,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J543" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J543" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K543" s="5" t="inlineStr"/>
+      <c r="N543" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="5" t="inlineStr">
@@ -23482,12 +23712,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J550" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J550" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K550" s="5" t="inlineStr"/>
+      <c r="N550" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="5" t="inlineStr">
@@ -24353,12 +24588,17 @@
           <t>Combine antarctica.gov.au into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
-      <c r="J570" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J570" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K570" s="5" t="inlineStr"/>
+      <c r="N570" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Combined: two Australian Antarctic Program pages combined, 4 to 3.</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="5" t="inlineStr">
@@ -24400,14 +24640,19 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J571" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J571" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K571" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
+      <c r="N571" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -24554,14 +24799,19 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J574" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J574" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K574" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
+      <c r="N574" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25791,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J599" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J599" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K599" s="5" t="inlineStr"/>
+      <c r="N599" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
@@ -26164,12 +26419,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J614" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J614" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K614" s="5" t="inlineStr"/>
+      <c r="N614" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="5" t="inlineStr">
@@ -28462,12 +28722,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J671" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J671" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K671" s="5" t="inlineStr"/>
+      <c r="N671" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="5" t="inlineStr">
@@ -28681,12 +28946,17 @@
           <t>Combine aphis.usda.gov into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
-      <c r="J676" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J676" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K676" s="5" t="inlineStr"/>
+      <c r="N676" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Combined: two APHIS pages combined, 5 to 4.</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="5" t="inlineStr">
@@ -29833,12 +30103,17 @@
           <t>Keep journals.plos.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J706" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J706" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K706" s="5" t="inlineStr"/>
+      <c r="N706" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="5" t="inlineStr">
@@ -30111,12 +30386,17 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J713" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J713" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K713" s="5" t="inlineStr"/>
+      <c r="N713" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="5" t="inlineStr">
@@ -30298,12 +30578,17 @@
           <t>Keep pubmed.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J717" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J717" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K717" s="5" t="inlineStr"/>
+      <c r="N717" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="5" t="inlineStr">
@@ -30672,14 +30957,19 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J727" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J727" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K727" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 6 to 5 entries.</t>
+        </is>
+      </c>
+      <c r="N727" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -30963,14 +31253,19 @@
           <t>Keep pmc.ncbi.nlm.nih.gov studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J734" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J734" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K734" s="5" t="inlineStr">
         <is>
           <t>2026-10-06: same-site entries combined, 5 to 4 entries.</t>
+        </is>
+      </c>
+      <c r="N734" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
         </is>
       </c>
     </row>
@@ -31162,12 +31457,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J738" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J738" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K738" s="5" t="inlineStr"/>
+      <c r="N738" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="5" t="inlineStr">
@@ -31540,12 +31840,17 @@
           <t>Keep sciencedirect.com studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J747" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J747" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K747" s="5" t="inlineStr"/>
+      <c r="N747" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="5" t="inlineStr">
@@ -32201,12 +32506,17 @@
           <t>Keep doi.org studies separate, reason stated; drop any study whose claim another listed source already covers.</t>
         </is>
       </c>
-      <c r="J763" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J763" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K763" s="5" t="inlineStr"/>
+      <c r="N763" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Reason confirmed: the repeated site hosts separate studies or papers, each with its own authors and year, each backing its own claim; 3 to 5 sources, no change.</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="5" t="inlineStr">
@@ -32532,12 +32842,17 @@
           <t>Combine adfg.alaska.gov into one entry naming the pages unless each backs a distinct rule or listing.</t>
         </is>
       </c>
-      <c r="J771" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J771" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K771" s="5" t="inlineStr"/>
+      <c r="N771" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06: Combined: two Alaska Department of Fish and Game pages combined, 5 to 4.</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="5" t="inlineStr">
